--- a/config/mohccn_vocabulary_mapped_20250909_JL.xlsx
+++ b/config/mohccn_vocabulary_mapped_20250909_JL.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\serverfiles\projects\dhdp\dhdp-mohccn-etl\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\serverfiles\projects\dhdp\mohccn-omop-etl\config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{125265A5-B759-4B50-B64D-FBAD0F02EEBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7248AF13-A02B-48FE-8002-ABE8939FC52D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Vocabulary Mapping" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14114" uniqueCount="2003">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14114" uniqueCount="2004">
   <si>
     <t>Schema</t>
   </si>
@@ -6032,6 +6032,9 @@
   </si>
   <si>
     <t>Manual</t>
+  </si>
+  <si>
+    <t>Manual Map Type</t>
   </si>
 </sst>
 </file>
@@ -6420,16 +6423,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:T1072"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="32.7109375" customWidth="1"/>
+    <col min="2" max="2" width="32.7265625" customWidth="1"/>
     <col min="3" max="3" width="30" customWidth="1"/>
-    <col min="7" max="7" width="24.28515625" customWidth="1"/>
-    <col min="9" max="9" width="24.28515625" customWidth="1"/>
-    <col min="16" max="16" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="24.26953125" customWidth="1"/>
+    <col min="8" max="8" width="9.90625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="24.26953125" customWidth="1"/>
+    <col min="12" max="12" width="10.54296875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="16" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="10.26953125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -6476,7 +6482,7 @@
         <v>14</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>11</v>
+        <v>2003</v>
       </c>
       <c r="Q1" s="1" t="s">
         <v>15</v>
@@ -6491,7 +6497,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>19</v>
       </c>
@@ -6541,7 +6547,7 @@
       </c>
       <c r="T2" s="1"/>
     </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>19</v>
       </c>
@@ -6591,7 +6597,7 @@
       </c>
       <c r="T3" s="1"/>
     </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>19</v>
       </c>
@@ -6641,7 +6647,7 @@
       </c>
       <c r="T4" s="1"/>
     </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>19</v>
       </c>
@@ -6691,7 +6697,7 @@
       </c>
       <c r="T5" s="1"/>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>19</v>
       </c>
@@ -6725,7 +6731,7 @@
       </c>
       <c r="T6" s="1"/>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
         <v>19</v>
       </c>
@@ -6759,7 +6765,7 @@
       </c>
       <c r="T7" s="1"/>
     </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
         <v>19</v>
       </c>
@@ -6809,7 +6815,7 @@
       </c>
       <c r="T8" s="1"/>
     </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
         <v>19</v>
       </c>
@@ -6843,7 +6849,7 @@
       </c>
       <c r="T9" s="1"/>
     </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
         <v>19</v>
       </c>
@@ -6899,7 +6905,7 @@
         <v>1867</v>
       </c>
     </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
         <v>19</v>
       </c>
@@ -6949,7 +6955,7 @@
       </c>
       <c r="T11" s="1"/>
     </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
         <v>19</v>
       </c>
@@ -6999,7 +7005,7 @@
       </c>
       <c r="T12" s="1"/>
     </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
         <v>19</v>
       </c>
@@ -7049,7 +7055,7 @@
       </c>
       <c r="T13" s="1"/>
     </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
         <v>19</v>
       </c>
@@ -7099,7 +7105,7 @@
       </c>
       <c r="T14" s="1"/>
     </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A15" s="1" t="s">
         <v>19</v>
       </c>
@@ -7149,7 +7155,7 @@
       </c>
       <c r="T15" s="1"/>
     </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A16" s="1" t="s">
         <v>19</v>
       </c>
@@ -7199,7 +7205,7 @@
       </c>
       <c r="T16" s="1"/>
     </row>
-    <row r="17" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A17" s="1" t="s">
         <v>19</v>
       </c>
@@ -7249,7 +7255,7 @@
       </c>
       <c r="T17" s="1"/>
     </row>
-    <row r="18" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A18" s="1" t="s">
         <v>19</v>
       </c>
@@ -7299,7 +7305,7 @@
       </c>
       <c r="T18" s="1"/>
     </row>
-    <row r="19" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A19" s="1" t="s">
         <v>19</v>
       </c>
@@ -7349,7 +7355,7 @@
       </c>
       <c r="T19" s="1"/>
     </row>
-    <row r="20" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A20" s="1" t="s">
         <v>19</v>
       </c>
@@ -7399,7 +7405,7 @@
       </c>
       <c r="T20" s="1"/>
     </row>
-    <row r="21" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A21" s="1" t="s">
         <v>19</v>
       </c>
@@ -7449,7 +7455,7 @@
       </c>
       <c r="T21" s="1"/>
     </row>
-    <row r="22" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A22" s="1" t="s">
         <v>19</v>
       </c>
@@ -7499,7 +7505,7 @@
       </c>
       <c r="T22" s="1"/>
     </row>
-    <row r="23" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A23" s="1" t="s">
         <v>19</v>
       </c>
@@ -7549,7 +7555,7 @@
       </c>
       <c r="T23" s="1"/>
     </row>
-    <row r="24" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A24" s="1" t="s">
         <v>19</v>
       </c>
@@ -7599,7 +7605,7 @@
       </c>
       <c r="T24" s="1"/>
     </row>
-    <row r="25" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A25" s="1" t="s">
         <v>19</v>
       </c>
@@ -7649,7 +7655,7 @@
       </c>
       <c r="T25" s="1"/>
     </row>
-    <row r="26" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A26" s="1" t="s">
         <v>19</v>
       </c>
@@ -7699,7 +7705,7 @@
       </c>
       <c r="T26" s="1"/>
     </row>
-    <row r="27" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A27" s="1" t="s">
         <v>19</v>
       </c>
@@ -7749,7 +7755,7 @@
       </c>
       <c r="T27" s="1"/>
     </row>
-    <row r="28" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A28" s="1" t="s">
         <v>19</v>
       </c>
@@ -7799,7 +7805,7 @@
       </c>
       <c r="T28" s="1"/>
     </row>
-    <row r="29" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A29" s="1" t="s">
         <v>19</v>
       </c>
@@ -7833,7 +7839,7 @@
       </c>
       <c r="T29" s="1"/>
     </row>
-    <row r="30" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A30" s="1" t="s">
         <v>19</v>
       </c>
@@ -7883,7 +7889,7 @@
       </c>
       <c r="T30" s="1"/>
     </row>
-    <row r="31" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A31" s="1" t="s">
         <v>19</v>
       </c>
@@ -7933,7 +7939,7 @@
       </c>
       <c r="T31" s="1"/>
     </row>
-    <row r="32" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A32" s="1" t="s">
         <v>19</v>
       </c>
@@ -7983,7 +7989,7 @@
       </c>
       <c r="T32" s="1"/>
     </row>
-    <row r="33" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A33" s="1" t="s">
         <v>19</v>
       </c>
@@ -8033,7 +8039,7 @@
       </c>
       <c r="T33" s="1"/>
     </row>
-    <row r="34" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A34" s="1" t="s">
         <v>19</v>
       </c>
@@ -8083,7 +8089,7 @@
       </c>
       <c r="T34" s="1"/>
     </row>
-    <row r="35" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A35" s="1" t="s">
         <v>19</v>
       </c>
@@ -8133,7 +8139,7 @@
       </c>
       <c r="T35" s="1"/>
     </row>
-    <row r="36" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A36" s="1" t="s">
         <v>19</v>
       </c>
@@ -8185,7 +8191,7 @@
       </c>
       <c r="T36" s="1"/>
     </row>
-    <row r="37" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A37" s="1" t="s">
         <v>19</v>
       </c>
@@ -8235,7 +8241,7 @@
       </c>
       <c r="T37" s="1"/>
     </row>
-    <row r="38" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A38" s="1" t="s">
         <v>19</v>
       </c>
@@ -8285,7 +8291,7 @@
       </c>
       <c r="T38" s="1"/>
     </row>
-    <row r="39" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A39" s="1" t="s">
         <v>19</v>
       </c>
@@ -8319,7 +8325,7 @@
       </c>
       <c r="T39" s="1"/>
     </row>
-    <row r="40" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A40" s="1" t="s">
         <v>19</v>
       </c>
@@ -8353,7 +8359,7 @@
       </c>
       <c r="T40" s="1"/>
     </row>
-    <row r="41" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A41" s="1" t="s">
         <v>19</v>
       </c>
@@ -8387,7 +8393,7 @@
       </c>
       <c r="T41" s="1"/>
     </row>
-    <row r="42" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A42" s="1" t="s">
         <v>19</v>
       </c>
@@ -8421,7 +8427,7 @@
       </c>
       <c r="T42" s="1"/>
     </row>
-    <row r="43" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A43" s="1" t="s">
         <v>19</v>
       </c>
@@ -8475,7 +8481,7 @@
       </c>
       <c r="T43" s="1"/>
     </row>
-    <row r="44" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A44" s="1" t="s">
         <v>19</v>
       </c>
@@ -8529,7 +8535,7 @@
       </c>
       <c r="T44" s="1"/>
     </row>
-    <row r="45" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A45" s="1" t="s">
         <v>19</v>
       </c>
@@ -8583,7 +8589,7 @@
       </c>
       <c r="T45" s="1"/>
     </row>
-    <row r="46" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A46" s="1" t="s">
         <v>19</v>
       </c>
@@ -8633,7 +8639,7 @@
       </c>
       <c r="T46" s="1"/>
     </row>
-    <row r="47" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A47" s="1" t="s">
         <v>19</v>
       </c>
@@ -8687,7 +8693,7 @@
       </c>
       <c r="T47" s="1"/>
     </row>
-    <row r="48" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A48" s="1" t="s">
         <v>19</v>
       </c>
@@ -8737,7 +8743,7 @@
       </c>
       <c r="T48" s="1"/>
     </row>
-    <row r="49" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A49" s="1" t="s">
         <v>19</v>
       </c>
@@ -8791,7 +8797,7 @@
       </c>
       <c r="T49" s="1"/>
     </row>
-    <row r="50" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A50" s="1" t="s">
         <v>19</v>
       </c>
@@ -8845,7 +8851,7 @@
       </c>
       <c r="T50" s="1"/>
     </row>
-    <row r="51" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A51" s="1" t="s">
         <v>19</v>
       </c>
@@ -8895,7 +8901,7 @@
       </c>
       <c r="T51" s="1"/>
     </row>
-    <row r="52" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A52" s="1" t="s">
         <v>19</v>
       </c>
@@ -8945,7 +8951,7 @@
       </c>
       <c r="T52" s="1"/>
     </row>
-    <row r="53" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A53" s="1" t="s">
         <v>19</v>
       </c>
@@ -8979,7 +8985,7 @@
       </c>
       <c r="T53" s="1"/>
     </row>
-    <row r="54" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A54" s="1" t="s">
         <v>19</v>
       </c>
@@ -9033,7 +9039,7 @@
       </c>
       <c r="T54" s="1"/>
     </row>
-    <row r="55" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A55" s="1" t="s">
         <v>19</v>
       </c>
@@ -9087,7 +9093,7 @@
       </c>
       <c r="T55" s="1"/>
     </row>
-    <row r="56" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A56" s="1" t="s">
         <v>19</v>
       </c>
@@ -9141,7 +9147,7 @@
       </c>
       <c r="T56" s="1"/>
     </row>
-    <row r="57" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A57" s="1" t="s">
         <v>19</v>
       </c>
@@ -9175,7 +9181,7 @@
       </c>
       <c r="T57" s="1"/>
     </row>
-    <row r="58" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A58" s="1" t="s">
         <v>19</v>
       </c>
@@ -9209,7 +9215,7 @@
       </c>
       <c r="T58" s="1"/>
     </row>
-    <row r="59" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A59" s="1" t="s">
         <v>19</v>
       </c>
@@ -9243,7 +9249,7 @@
       </c>
       <c r="T59" s="1"/>
     </row>
-    <row r="60" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A60" s="1" t="s">
         <v>19</v>
       </c>
@@ -9277,7 +9283,7 @@
       </c>
       <c r="T60" s="1"/>
     </row>
-    <row r="61" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A61" s="1" t="s">
         <v>19</v>
       </c>
@@ -9311,7 +9317,7 @@
       </c>
       <c r="T61" s="1"/>
     </row>
-    <row r="62" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A62" s="1" t="s">
         <v>19</v>
       </c>
@@ -9361,7 +9367,7 @@
       </c>
       <c r="T62" s="1"/>
     </row>
-    <row r="63" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A63" s="1" t="s">
         <v>19</v>
       </c>
@@ -9395,7 +9401,7 @@
       </c>
       <c r="T63" s="1"/>
     </row>
-    <row r="64" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A64" s="1" t="s">
         <v>19</v>
       </c>
@@ -9429,7 +9435,7 @@
       </c>
       <c r="T64" s="1"/>
     </row>
-    <row r="65" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A65" s="1" t="s">
         <v>19</v>
       </c>
@@ -9463,7 +9469,7 @@
       </c>
       <c r="T65" s="1"/>
     </row>
-    <row r="66" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A66" s="1" t="s">
         <v>19</v>
       </c>
@@ -9497,7 +9503,7 @@
       </c>
       <c r="T66" s="1"/>
     </row>
-    <row r="67" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A67" s="1" t="s">
         <v>19</v>
       </c>
@@ -9531,7 +9537,7 @@
       </c>
       <c r="T67" s="1"/>
     </row>
-    <row r="68" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A68" s="1" t="s">
         <v>19</v>
       </c>
@@ -9565,7 +9571,7 @@
       </c>
       <c r="T68" s="1"/>
     </row>
-    <row r="69" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A69" s="1" t="s">
         <v>19</v>
       </c>
@@ -9599,7 +9605,7 @@
       </c>
       <c r="T69" s="1"/>
     </row>
-    <row r="70" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A70" s="1" t="s">
         <v>150</v>
       </c>
@@ -9651,7 +9657,7 @@
       </c>
       <c r="T70" s="1"/>
     </row>
-    <row r="71" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A71" s="1" t="s">
         <v>150</v>
       </c>
@@ -9703,7 +9709,7 @@
       </c>
       <c r="T71" s="1"/>
     </row>
-    <row r="72" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A72" s="1" t="s">
         <v>150</v>
       </c>
@@ -9755,7 +9761,7 @@
       </c>
       <c r="T72" s="1"/>
     </row>
-    <row r="73" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A73" s="1" t="s">
         <v>150</v>
       </c>
@@ -9807,7 +9813,7 @@
       </c>
       <c r="T73" s="1"/>
     </row>
-    <row r="74" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A74" s="1" t="s">
         <v>150</v>
       </c>
@@ -9859,7 +9865,7 @@
       </c>
       <c r="T74" s="1"/>
     </row>
-    <row r="75" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A75" s="1" t="s">
         <v>150</v>
       </c>
@@ -9911,7 +9917,7 @@
       </c>
       <c r="T75" s="1"/>
     </row>
-    <row r="76" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A76" s="1" t="s">
         <v>150</v>
       </c>
@@ -9965,7 +9971,7 @@
       </c>
       <c r="T76" s="1"/>
     </row>
-    <row r="77" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A77" s="1" t="s">
         <v>150</v>
       </c>
@@ -10019,7 +10025,7 @@
       </c>
       <c r="T77" s="1"/>
     </row>
-    <row r="78" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A78" s="1" t="s">
         <v>150</v>
       </c>
@@ -10073,7 +10079,7 @@
       </c>
       <c r="T78" s="1"/>
     </row>
-    <row r="79" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A79" s="1" t="s">
         <v>150</v>
       </c>
@@ -10127,7 +10133,7 @@
       </c>
       <c r="T79" s="1"/>
     </row>
-    <row r="80" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A80" s="1" t="s">
         <v>150</v>
       </c>
@@ -10177,7 +10183,7 @@
       </c>
       <c r="T80" s="1"/>
     </row>
-    <row r="81" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A81" s="1" t="s">
         <v>150</v>
       </c>
@@ -10227,7 +10233,7 @@
       </c>
       <c r="T81" s="1"/>
     </row>
-    <row r="82" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A82" s="1" t="s">
         <v>150</v>
       </c>
@@ -10277,7 +10283,7 @@
       </c>
       <c r="T82" s="1"/>
     </row>
-    <row r="83" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A83" s="1" t="s">
         <v>150</v>
       </c>
@@ -10327,7 +10333,7 @@
       </c>
       <c r="T83" s="1"/>
     </row>
-    <row r="84" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A84" s="1" t="s">
         <v>150</v>
       </c>
@@ -10381,7 +10387,7 @@
       </c>
       <c r="T84" s="1"/>
     </row>
-    <row r="85" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A85" s="1" t="s">
         <v>150</v>
       </c>
@@ -10435,7 +10441,7 @@
       </c>
       <c r="T85" s="1"/>
     </row>
-    <row r="86" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A86" s="1" t="s">
         <v>150</v>
       </c>
@@ -10487,7 +10493,7 @@
       </c>
       <c r="T86" s="1"/>
     </row>
-    <row r="87" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A87" s="1" t="s">
         <v>150</v>
       </c>
@@ -10539,7 +10545,7 @@
       </c>
       <c r="T87" s="1"/>
     </row>
-    <row r="88" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A88" s="1" t="s">
         <v>150</v>
       </c>
@@ -10593,7 +10599,7 @@
       </c>
       <c r="T88" s="1"/>
     </row>
-    <row r="89" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A89" s="1" t="s">
         <v>150</v>
       </c>
@@ -10643,7 +10649,7 @@
       </c>
       <c r="T89" s="1"/>
     </row>
-    <row r="90" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A90" s="1" t="s">
         <v>150</v>
       </c>
@@ -10693,7 +10699,7 @@
       </c>
       <c r="T90" s="1"/>
     </row>
-    <row r="91" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A91" s="1" t="s">
         <v>150</v>
       </c>
@@ -10743,7 +10749,7 @@
       </c>
       <c r="T91" s="1"/>
     </row>
-    <row r="92" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A92" s="1" t="s">
         <v>150</v>
       </c>
@@ -10797,7 +10803,7 @@
       </c>
       <c r="T92" s="1"/>
     </row>
-    <row r="93" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A93" s="1" t="s">
         <v>27</v>
       </c>
@@ -10847,7 +10853,7 @@
       </c>
       <c r="T93" s="1"/>
     </row>
-    <row r="94" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A94" s="1" t="s">
         <v>27</v>
       </c>
@@ -10897,7 +10903,7 @@
       </c>
       <c r="T94" s="1"/>
     </row>
-    <row r="95" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A95" s="1" t="s">
         <v>27</v>
       </c>
@@ -10947,7 +10953,7 @@
       </c>
       <c r="T95" s="1"/>
     </row>
-    <row r="96" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A96" s="1" t="s">
         <v>27</v>
       </c>
@@ -10997,7 +11003,7 @@
       </c>
       <c r="T96" s="1"/>
     </row>
-    <row r="97" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A97" s="1" t="s">
         <v>27</v>
       </c>
@@ -11047,7 +11053,7 @@
       </c>
       <c r="T97" s="1"/>
     </row>
-    <row r="98" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A98" s="1" t="s">
         <v>27</v>
       </c>
@@ -11097,7 +11103,7 @@
       </c>
       <c r="T98" s="1"/>
     </row>
-    <row r="99" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A99" s="1" t="s">
         <v>27</v>
       </c>
@@ -11147,7 +11153,7 @@
       </c>
       <c r="T99" s="1"/>
     </row>
-    <row r="100" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A100" s="1" t="s">
         <v>27</v>
       </c>
@@ -11197,7 +11203,7 @@
       </c>
       <c r="T100" s="1"/>
     </row>
-    <row r="101" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A101" s="1" t="s">
         <v>27</v>
       </c>
@@ -11247,7 +11253,7 @@
       </c>
       <c r="T101" s="1"/>
     </row>
-    <row r="102" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A102" s="1" t="s">
         <v>27</v>
       </c>
@@ -11281,7 +11287,7 @@
       </c>
       <c r="T102" s="1"/>
     </row>
-    <row r="103" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A103" s="1" t="s">
         <v>27</v>
       </c>
@@ -11333,7 +11339,7 @@
       </c>
       <c r="T103" s="1"/>
     </row>
-    <row r="104" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A104" s="1" t="s">
         <v>27</v>
       </c>
@@ -11367,7 +11373,7 @@
       </c>
       <c r="T104" s="1"/>
     </row>
-    <row r="105" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A105" s="1" t="s">
         <v>27</v>
       </c>
@@ -11401,7 +11407,7 @@
       </c>
       <c r="T105" s="1"/>
     </row>
-    <row r="106" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A106" s="1" t="s">
         <v>27</v>
       </c>
@@ -11435,7 +11441,7 @@
       </c>
       <c r="T106" s="1"/>
     </row>
-    <row r="107" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A107" s="1" t="s">
         <v>27</v>
       </c>
@@ -11485,7 +11491,7 @@
       </c>
       <c r="T107" s="1"/>
     </row>
-    <row r="108" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A108" s="1" t="s">
         <v>27</v>
       </c>
@@ -11535,7 +11541,7 @@
       </c>
       <c r="T108" s="1"/>
     </row>
-    <row r="109" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A109" s="1" t="s">
         <v>27</v>
       </c>
@@ -11587,7 +11593,7 @@
       </c>
       <c r="T109" s="1"/>
     </row>
-    <row r="110" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A110" s="1" t="s">
         <v>27</v>
       </c>
@@ -11621,7 +11627,7 @@
       </c>
       <c r="T110" s="1"/>
     </row>
-    <row r="111" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A111" s="1" t="s">
         <v>27</v>
       </c>
@@ -11655,7 +11661,7 @@
       </c>
       <c r="T111" s="1"/>
     </row>
-    <row r="112" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A112" s="1" t="s">
         <v>27</v>
       </c>
@@ -11689,7 +11695,7 @@
       </c>
       <c r="T112" s="1"/>
     </row>
-    <row r="113" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A113" s="1" t="s">
         <v>27</v>
       </c>
@@ -11741,7 +11747,7 @@
       </c>
       <c r="T113" s="1"/>
     </row>
-    <row r="114" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A114" s="1" t="s">
         <v>27</v>
       </c>
@@ -11791,7 +11797,7 @@
       </c>
       <c r="T114" s="1"/>
     </row>
-    <row r="115" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A115" s="1" t="s">
         <v>27</v>
       </c>
@@ -11841,7 +11847,7 @@
       </c>
       <c r="T115" s="1"/>
     </row>
-    <row r="116" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A116" s="1" t="s">
         <v>27</v>
       </c>
@@ -11891,7 +11897,7 @@
       </c>
       <c r="T116" s="1"/>
     </row>
-    <row r="117" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A117" s="1" t="s">
         <v>27</v>
       </c>
@@ -11941,7 +11947,7 @@
       </c>
       <c r="T117" s="1"/>
     </row>
-    <row r="118" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A118" s="1" t="s">
         <v>27</v>
       </c>
@@ -11991,7 +11997,7 @@
       </c>
       <c r="T118" s="1"/>
     </row>
-    <row r="119" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A119" s="1" t="s">
         <v>27</v>
       </c>
@@ -12041,7 +12047,7 @@
       </c>
       <c r="T119" s="1"/>
     </row>
-    <row r="120" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A120" s="1" t="s">
         <v>27</v>
       </c>
@@ -12091,7 +12097,7 @@
       </c>
       <c r="T120" s="1"/>
     </row>
-    <row r="121" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A121" s="1" t="s">
         <v>27</v>
       </c>
@@ -12141,7 +12147,7 @@
       </c>
       <c r="T121" s="1"/>
     </row>
-    <row r="122" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A122" s="1" t="s">
         <v>27</v>
       </c>
@@ -12191,7 +12197,7 @@
       </c>
       <c r="T122" s="1"/>
     </row>
-    <row r="123" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A123" s="1" t="s">
         <v>27</v>
       </c>
@@ -12241,7 +12247,7 @@
       </c>
       <c r="T123" s="1"/>
     </row>
-    <row r="124" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A124" s="1" t="s">
         <v>27</v>
       </c>
@@ -12291,7 +12297,7 @@
       </c>
       <c r="T124" s="1"/>
     </row>
-    <row r="125" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A125" s="1" t="s">
         <v>27</v>
       </c>
@@ -12341,7 +12347,7 @@
       </c>
       <c r="T125" s="1"/>
     </row>
-    <row r="126" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A126" s="1" t="s">
         <v>27</v>
       </c>
@@ -12391,7 +12397,7 @@
       </c>
       <c r="T126" s="1"/>
     </row>
-    <row r="127" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A127" s="1" t="s">
         <v>27</v>
       </c>
@@ -12441,7 +12447,7 @@
       </c>
       <c r="T127" s="1"/>
     </row>
-    <row r="128" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A128" s="1" t="s">
         <v>27</v>
       </c>
@@ -12491,7 +12497,7 @@
       </c>
       <c r="T128" s="1"/>
     </row>
-    <row r="129" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A129" s="1" t="s">
         <v>27</v>
       </c>
@@ -12541,7 +12547,7 @@
       </c>
       <c r="T129" s="1"/>
     </row>
-    <row r="130" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A130" s="1" t="s">
         <v>27</v>
       </c>
@@ -12591,7 +12597,7 @@
       </c>
       <c r="T130" s="1"/>
     </row>
-    <row r="131" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A131" s="1" t="s">
         <v>27</v>
       </c>
@@ -12641,7 +12647,7 @@
       </c>
       <c r="T131" s="1"/>
     </row>
-    <row r="132" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A132" s="1" t="s">
         <v>27</v>
       </c>
@@ -12691,7 +12697,7 @@
       </c>
       <c r="T132" s="1"/>
     </row>
-    <row r="133" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A133" s="1" t="s">
         <v>27</v>
       </c>
@@ -12741,7 +12747,7 @@
       </c>
       <c r="T133" s="1"/>
     </row>
-    <row r="134" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A134" s="1" t="s">
         <v>27</v>
       </c>
@@ -12791,7 +12797,7 @@
       </c>
       <c r="T134" s="1"/>
     </row>
-    <row r="135" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A135" s="1" t="s">
         <v>27</v>
       </c>
@@ -12841,7 +12847,7 @@
       </c>
       <c r="T135" s="1"/>
     </row>
-    <row r="136" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A136" s="1" t="s">
         <v>27</v>
       </c>
@@ -12891,7 +12897,7 @@
       </c>
       <c r="T136" s="1"/>
     </row>
-    <row r="137" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A137" s="1" t="s">
         <v>27</v>
       </c>
@@ -12941,7 +12947,7 @@
       </c>
       <c r="T137" s="1"/>
     </row>
-    <row r="138" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A138" s="1" t="s">
         <v>27</v>
       </c>
@@ -12973,7 +12979,7 @@
       </c>
       <c r="T138" s="1"/>
     </row>
-    <row r="139" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A139" s="1" t="s">
         <v>27</v>
       </c>
@@ -13005,7 +13011,7 @@
       </c>
       <c r="T139" s="1"/>
     </row>
-    <row r="140" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A140" s="1" t="s">
         <v>27</v>
       </c>
@@ -13037,7 +13043,7 @@
       </c>
       <c r="T140" s="1"/>
     </row>
-    <row r="141" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A141" s="1" t="s">
         <v>27</v>
       </c>
@@ -13087,7 +13093,7 @@
       </c>
       <c r="T141" s="1"/>
     </row>
-    <row r="142" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A142" s="1" t="s">
         <v>27</v>
       </c>
@@ -13137,7 +13143,7 @@
       </c>
       <c r="T142" s="1"/>
     </row>
-    <row r="143" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A143" s="1" t="s">
         <v>27</v>
       </c>
@@ -13187,7 +13193,7 @@
       </c>
       <c r="T143" s="1"/>
     </row>
-    <row r="144" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A144" s="1" t="s">
         <v>27</v>
       </c>
@@ -13219,7 +13225,7 @@
       </c>
       <c r="T144" s="1"/>
     </row>
-    <row r="145" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A145" s="1" t="s">
         <v>27</v>
       </c>
@@ -13269,7 +13275,7 @@
       </c>
       <c r="T145" s="1"/>
     </row>
-    <row r="146" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A146" s="1" t="s">
         <v>27</v>
       </c>
@@ -13319,7 +13325,7 @@
       </c>
       <c r="T146" s="1"/>
     </row>
-    <row r="147" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A147" s="1" t="s">
         <v>27</v>
       </c>
@@ -13351,7 +13357,7 @@
       </c>
       <c r="T147" s="1"/>
     </row>
-    <row r="148" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A148" s="1" t="s">
         <v>27</v>
       </c>
@@ -13383,7 +13389,7 @@
       </c>
       <c r="T148" s="1"/>
     </row>
-    <row r="149" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A149" s="1" t="s">
         <v>27</v>
       </c>
@@ -13415,7 +13421,7 @@
       </c>
       <c r="T149" s="1"/>
     </row>
-    <row r="150" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A150" s="1" t="s">
         <v>27</v>
       </c>
@@ -13447,7 +13453,7 @@
       </c>
       <c r="T150" s="1"/>
     </row>
-    <row r="151" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A151" s="1" t="s">
         <v>27</v>
       </c>
@@ -13497,7 +13503,7 @@
       </c>
       <c r="T151" s="1"/>
     </row>
-    <row r="152" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A152" s="1" t="s">
         <v>27</v>
       </c>
@@ -13529,7 +13535,7 @@
       </c>
       <c r="T152" s="1"/>
     </row>
-    <row r="153" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A153" s="1" t="s">
         <v>27</v>
       </c>
@@ -13579,7 +13585,7 @@
       </c>
       <c r="T153" s="1"/>
     </row>
-    <row r="154" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A154" s="1" t="s">
         <v>27</v>
       </c>
@@ -13611,7 +13617,7 @@
       </c>
       <c r="T154" s="1"/>
     </row>
-    <row r="155" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A155" s="1" t="s">
         <v>27</v>
       </c>
@@ -13643,7 +13649,7 @@
       </c>
       <c r="T155" s="1"/>
     </row>
-    <row r="156" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A156" s="1" t="s">
         <v>27</v>
       </c>
@@ -13693,7 +13699,7 @@
       </c>
       <c r="T156" s="1"/>
     </row>
-    <row r="157" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A157" s="1" t="s">
         <v>27</v>
       </c>
@@ -13745,7 +13751,7 @@
       </c>
       <c r="T157" s="1"/>
     </row>
-    <row r="158" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A158" s="1" t="s">
         <v>27</v>
       </c>
@@ -13797,7 +13803,7 @@
       </c>
       <c r="T158" s="1"/>
     </row>
-    <row r="159" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A159" s="1" t="s">
         <v>27</v>
       </c>
@@ -13849,7 +13855,7 @@
       </c>
       <c r="T159" s="1"/>
     </row>
-    <row r="160" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A160" s="1" t="s">
         <v>27</v>
       </c>
@@ -13901,7 +13907,7 @@
       </c>
       <c r="T160" s="1"/>
     </row>
-    <row r="161" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A161" s="1" t="s">
         <v>27</v>
       </c>
@@ -13951,7 +13957,7 @@
       </c>
       <c r="T161" s="1"/>
     </row>
-    <row r="162" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A162" s="1" t="s">
         <v>27</v>
       </c>
@@ -14005,7 +14011,7 @@
         <v>2001</v>
       </c>
     </row>
-    <row r="163" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A163" s="1" t="s">
         <v>27</v>
       </c>
@@ -14059,7 +14065,7 @@
         <v>2001</v>
       </c>
     </row>
-    <row r="164" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A164" s="1" t="s">
         <v>27</v>
       </c>
@@ -14109,7 +14115,7 @@
       </c>
       <c r="T164" s="1"/>
     </row>
-    <row r="165" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A165" s="1" t="s">
         <v>27</v>
       </c>
@@ -14159,7 +14165,7 @@
       </c>
       <c r="T165" s="1"/>
     </row>
-    <row r="166" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A166" s="1" t="s">
         <v>27</v>
       </c>
@@ -14209,7 +14215,7 @@
       </c>
       <c r="T166" s="1"/>
     </row>
-    <row r="167" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A167" s="1" t="s">
         <v>27</v>
       </c>
@@ -14259,7 +14265,7 @@
       </c>
       <c r="T167" s="1"/>
     </row>
-    <row r="168" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A168" s="1" t="s">
         <v>27</v>
       </c>
@@ -14309,7 +14315,7 @@
       </c>
       <c r="T168" s="1"/>
     </row>
-    <row r="169" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A169" s="1" t="s">
         <v>27</v>
       </c>
@@ -14359,7 +14365,7 @@
       </c>
       <c r="T169" s="1"/>
     </row>
-    <row r="170" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A170" s="1" t="s">
         <v>27</v>
       </c>
@@ -14409,7 +14415,7 @@
       </c>
       <c r="T170" s="1"/>
     </row>
-    <row r="171" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A171" s="1" t="s">
         <v>332</v>
       </c>
@@ -14461,7 +14467,7 @@
       </c>
       <c r="T171" s="1"/>
     </row>
-    <row r="172" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A172" s="1" t="s">
         <v>332</v>
       </c>
@@ -14513,7 +14519,7 @@
       </c>
       <c r="T172" s="1"/>
     </row>
-    <row r="173" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A173" s="1" t="s">
         <v>332</v>
       </c>
@@ -14565,7 +14571,7 @@
       </c>
       <c r="T173" s="1"/>
     </row>
-    <row r="174" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A174" s="1" t="s">
         <v>332</v>
       </c>
@@ -14617,7 +14623,7 @@
       </c>
       <c r="T174" s="1"/>
     </row>
-    <row r="175" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A175" s="1" t="s">
         <v>332</v>
       </c>
@@ -14669,7 +14675,7 @@
       </c>
       <c r="T175" s="1"/>
     </row>
-    <row r="176" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A176" s="1" t="s">
         <v>332</v>
       </c>
@@ -14721,7 +14727,7 @@
       </c>
       <c r="T176" s="1"/>
     </row>
-    <row r="177" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A177" s="1" t="s">
         <v>332</v>
       </c>
@@ -14773,7 +14779,7 @@
       </c>
       <c r="T177" s="1"/>
     </row>
-    <row r="178" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A178" s="1" t="s">
         <v>332</v>
       </c>
@@ -14825,7 +14831,7 @@
       </c>
       <c r="T178" s="1"/>
     </row>
-    <row r="179" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A179" s="1" t="s">
         <v>332</v>
       </c>
@@ -14877,7 +14883,7 @@
       </c>
       <c r="T179" s="1"/>
     </row>
-    <row r="180" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A180" s="1" t="s">
         <v>332</v>
       </c>
@@ -14929,7 +14935,7 @@
       </c>
       <c r="T180" s="1"/>
     </row>
-    <row r="181" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A181" s="1" t="s">
         <v>332</v>
       </c>
@@ -14981,7 +14987,7 @@
       </c>
       <c r="T181" s="1"/>
     </row>
-    <row r="182" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A182" s="1" t="s">
         <v>332</v>
       </c>
@@ -15033,7 +15039,7 @@
       </c>
       <c r="T182" s="1"/>
     </row>
-    <row r="183" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A183" s="1" t="s">
         <v>332</v>
       </c>
@@ -15085,7 +15091,7 @@
       </c>
       <c r="T183" s="1"/>
     </row>
-    <row r="184" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A184" s="1" t="s">
         <v>332</v>
       </c>
@@ -15137,7 +15143,7 @@
       </c>
       <c r="T184" s="1"/>
     </row>
-    <row r="185" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A185" s="1" t="s">
         <v>332</v>
       </c>
@@ -15189,7 +15195,7 @@
       </c>
       <c r="T185" s="1"/>
     </row>
-    <row r="186" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A186" s="1" t="s">
         <v>332</v>
       </c>
@@ -15241,7 +15247,7 @@
       </c>
       <c r="T186" s="1"/>
     </row>
-    <row r="187" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A187" s="1" t="s">
         <v>332</v>
       </c>
@@ -15293,7 +15299,7 @@
       </c>
       <c r="T187" s="1"/>
     </row>
-    <row r="188" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A188" s="1" t="s">
         <v>332</v>
       </c>
@@ -15345,7 +15351,7 @@
       </c>
       <c r="T188" s="1"/>
     </row>
-    <row r="189" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A189" s="1" t="s">
         <v>332</v>
       </c>
@@ -15397,7 +15403,7 @@
       </c>
       <c r="T189" s="1"/>
     </row>
-    <row r="190" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A190" s="1" t="s">
         <v>332</v>
       </c>
@@ -15449,7 +15455,7 @@
       </c>
       <c r="T190" s="1"/>
     </row>
-    <row r="191" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A191" s="1" t="s">
         <v>332</v>
       </c>
@@ -15501,7 +15507,7 @@
       </c>
       <c r="T191" s="1"/>
     </row>
-    <row r="192" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A192" s="1" t="s">
         <v>332</v>
       </c>
@@ -15553,7 +15559,7 @@
       </c>
       <c r="T192" s="1"/>
     </row>
-    <row r="193" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A193" s="1" t="s">
         <v>332</v>
       </c>
@@ -15605,7 +15611,7 @@
       </c>
       <c r="T193" s="1"/>
     </row>
-    <row r="194" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A194" s="1" t="s">
         <v>332</v>
       </c>
@@ -15657,7 +15663,7 @@
       </c>
       <c r="T194" s="1"/>
     </row>
-    <row r="195" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A195" s="1" t="s">
         <v>332</v>
       </c>
@@ -15709,7 +15715,7 @@
       </c>
       <c r="T195" s="1"/>
     </row>
-    <row r="196" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A196" s="1" t="s">
         <v>332</v>
       </c>
@@ -15761,7 +15767,7 @@
       </c>
       <c r="T196" s="1"/>
     </row>
-    <row r="197" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A197" s="1" t="s">
         <v>332</v>
       </c>
@@ -15813,7 +15819,7 @@
       </c>
       <c r="T197" s="1"/>
     </row>
-    <row r="198" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A198" s="1" t="s">
         <v>332</v>
       </c>
@@ -15865,7 +15871,7 @@
       </c>
       <c r="T198" s="1"/>
     </row>
-    <row r="199" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A199" s="1" t="s">
         <v>332</v>
       </c>
@@ -15917,7 +15923,7 @@
       </c>
       <c r="T199" s="1"/>
     </row>
-    <row r="200" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A200" s="1" t="s">
         <v>332</v>
       </c>
@@ -15969,7 +15975,7 @@
       </c>
       <c r="T200" s="1"/>
     </row>
-    <row r="201" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A201" s="1" t="s">
         <v>332</v>
       </c>
@@ -16021,7 +16027,7 @@
       </c>
       <c r="T201" s="1"/>
     </row>
-    <row r="202" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A202" s="1" t="s">
         <v>332</v>
       </c>
@@ -16073,7 +16079,7 @@
       </c>
       <c r="T202" s="1"/>
     </row>
-    <row r="203" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A203" s="1" t="s">
         <v>332</v>
       </c>
@@ -16125,7 +16131,7 @@
       </c>
       <c r="T203" s="1"/>
     </row>
-    <row r="204" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A204" s="1" t="s">
         <v>332</v>
       </c>
@@ -16177,7 +16183,7 @@
       </c>
       <c r="T204" s="1"/>
     </row>
-    <row r="205" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A205" s="1" t="s">
         <v>332</v>
       </c>
@@ -16231,7 +16237,7 @@
       </c>
       <c r="T205" s="1"/>
     </row>
-    <row r="206" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A206" s="1" t="s">
         <v>332</v>
       </c>
@@ -16285,7 +16291,7 @@
       </c>
       <c r="T206" s="1"/>
     </row>
-    <row r="207" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A207" s="1" t="s">
         <v>332</v>
       </c>
@@ -16337,7 +16343,7 @@
       </c>
       <c r="T207" s="1"/>
     </row>
-    <row r="208" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A208" s="1" t="s">
         <v>332</v>
       </c>
@@ -16389,7 +16395,7 @@
       </c>
       <c r="T208" s="1"/>
     </row>
-    <row r="209" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A209" s="1" t="s">
         <v>332</v>
       </c>
@@ -16441,7 +16447,7 @@
       </c>
       <c r="T209" s="1"/>
     </row>
-    <row r="210" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A210" s="1" t="s">
         <v>332</v>
       </c>
@@ -16493,7 +16499,7 @@
       </c>
       <c r="T210" s="1"/>
     </row>
-    <row r="211" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A211" s="1" t="s">
         <v>332</v>
       </c>
@@ -16545,7 +16551,7 @@
       </c>
       <c r="T211" s="1"/>
     </row>
-    <row r="212" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A212" s="1" t="s">
         <v>332</v>
       </c>
@@ -16597,7 +16603,7 @@
       </c>
       <c r="T212" s="1"/>
     </row>
-    <row r="213" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A213" s="1" t="s">
         <v>332</v>
       </c>
@@ -16649,7 +16655,7 @@
       </c>
       <c r="T213" s="1"/>
     </row>
-    <row r="214" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A214" s="1" t="s">
         <v>332</v>
       </c>
@@ -16701,7 +16707,7 @@
       </c>
       <c r="T214" s="1"/>
     </row>
-    <row r="215" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A215" s="1" t="s">
         <v>332</v>
       </c>
@@ -16753,7 +16759,7 @@
       </c>
       <c r="T215" s="1"/>
     </row>
-    <row r="216" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A216" s="1" t="s">
         <v>332</v>
       </c>
@@ -16805,7 +16811,7 @@
       </c>
       <c r="T216" s="1"/>
     </row>
-    <row r="217" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A217" s="1" t="s">
         <v>332</v>
       </c>
@@ -16857,7 +16863,7 @@
       </c>
       <c r="T217" s="1"/>
     </row>
-    <row r="218" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A218" s="1" t="s">
         <v>332</v>
       </c>
@@ -16909,7 +16915,7 @@
       </c>
       <c r="T218" s="1"/>
     </row>
-    <row r="219" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A219" s="1" t="s">
         <v>332</v>
       </c>
@@ -16961,7 +16967,7 @@
       </c>
       <c r="T219" s="1"/>
     </row>
-    <row r="220" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A220" s="1" t="s">
         <v>332</v>
       </c>
@@ -17013,7 +17019,7 @@
       </c>
       <c r="T220" s="1"/>
     </row>
-    <row r="221" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A221" s="1" t="s">
         <v>332</v>
       </c>
@@ -17065,7 +17071,7 @@
       </c>
       <c r="T221" s="1"/>
     </row>
-    <row r="222" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A222" s="1" t="s">
         <v>332</v>
       </c>
@@ -17117,7 +17123,7 @@
       </c>
       <c r="T222" s="1"/>
     </row>
-    <row r="223" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A223" s="1" t="s">
         <v>332</v>
       </c>
@@ -17169,7 +17175,7 @@
       </c>
       <c r="T223" s="1"/>
     </row>
-    <row r="224" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A224" s="1" t="s">
         <v>332</v>
       </c>
@@ -17221,7 +17227,7 @@
       </c>
       <c r="T224" s="1"/>
     </row>
-    <row r="225" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A225" s="1" t="s">
         <v>332</v>
       </c>
@@ -17273,7 +17279,7 @@
       </c>
       <c r="T225" s="1"/>
     </row>
-    <row r="226" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A226" s="1" t="s">
         <v>332</v>
       </c>
@@ -17325,7 +17331,7 @@
       </c>
       <c r="T226" s="1"/>
     </row>
-    <row r="227" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A227" s="1" t="s">
         <v>332</v>
       </c>
@@ -17377,7 +17383,7 @@
       </c>
       <c r="T227" s="1"/>
     </row>
-    <row r="228" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A228" s="1" t="s">
         <v>332</v>
       </c>
@@ -17429,7 +17435,7 @@
       </c>
       <c r="T228" s="1"/>
     </row>
-    <row r="229" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A229" s="1" t="s">
         <v>332</v>
       </c>
@@ -17481,7 +17487,7 @@
       </c>
       <c r="T229" s="1"/>
     </row>
-    <row r="230" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A230" s="1" t="s">
         <v>332</v>
       </c>
@@ -17533,7 +17539,7 @@
       </c>
       <c r="T230" s="1"/>
     </row>
-    <row r="231" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A231" s="1" t="s">
         <v>332</v>
       </c>
@@ -17585,7 +17591,7 @@
       </c>
       <c r="T231" s="1"/>
     </row>
-    <row r="232" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A232" s="1" t="s">
         <v>332</v>
       </c>
@@ -17637,7 +17643,7 @@
       </c>
       <c r="T232" s="1"/>
     </row>
-    <row r="233" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A233" s="1" t="s">
         <v>332</v>
       </c>
@@ -17689,7 +17695,7 @@
       </c>
       <c r="T233" s="1"/>
     </row>
-    <row r="234" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A234" s="1" t="s">
         <v>332</v>
       </c>
@@ -17741,7 +17747,7 @@
       </c>
       <c r="T234" s="1"/>
     </row>
-    <row r="235" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A235" s="1" t="s">
         <v>332</v>
       </c>
@@ -17793,7 +17799,7 @@
       </c>
       <c r="T235" s="1"/>
     </row>
-    <row r="236" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A236" s="1" t="s">
         <v>332</v>
       </c>
@@ -17845,7 +17851,7 @@
       </c>
       <c r="T236" s="1"/>
     </row>
-    <row r="237" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A237" s="1" t="s">
         <v>332</v>
       </c>
@@ -17897,7 +17903,7 @@
       </c>
       <c r="T237" s="1"/>
     </row>
-    <row r="238" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A238" s="1" t="s">
         <v>332</v>
       </c>
@@ -17949,7 +17955,7 @@
       </c>
       <c r="T238" s="1"/>
     </row>
-    <row r="239" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A239" s="1" t="s">
         <v>332</v>
       </c>
@@ -18001,7 +18007,7 @@
       </c>
       <c r="T239" s="1"/>
     </row>
-    <row r="240" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A240" s="1" t="s">
         <v>332</v>
       </c>
@@ -18053,7 +18059,7 @@
       </c>
       <c r="T240" s="1"/>
     </row>
-    <row r="241" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A241" s="1" t="s">
         <v>332</v>
       </c>
@@ -18107,7 +18113,7 @@
       </c>
       <c r="T241" s="1"/>
     </row>
-    <row r="242" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A242" s="1" t="s">
         <v>332</v>
       </c>
@@ -18161,7 +18167,7 @@
       </c>
       <c r="T242" s="1"/>
     </row>
-    <row r="243" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A243" s="1" t="s">
         <v>332</v>
       </c>
@@ -18213,7 +18219,7 @@
       </c>
       <c r="T243" s="1"/>
     </row>
-    <row r="244" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A244" s="1" t="s">
         <v>332</v>
       </c>
@@ -18265,7 +18271,7 @@
       </c>
       <c r="T244" s="1"/>
     </row>
-    <row r="245" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A245" s="1" t="s">
         <v>332</v>
       </c>
@@ -18317,7 +18323,7 @@
       </c>
       <c r="T245" s="1"/>
     </row>
-    <row r="246" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A246" s="1" t="s">
         <v>332</v>
       </c>
@@ -18369,7 +18375,7 @@
       </c>
       <c r="T246" s="1"/>
     </row>
-    <row r="247" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A247" s="1" t="s">
         <v>332</v>
       </c>
@@ -18419,7 +18425,7 @@
       </c>
       <c r="T247" s="1"/>
     </row>
-    <row r="248" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A248" s="1" t="s">
         <v>332</v>
       </c>
@@ -18469,7 +18475,7 @@
       </c>
       <c r="T248" s="1"/>
     </row>
-    <row r="249" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A249" s="1" t="s">
         <v>332</v>
       </c>
@@ -18519,7 +18525,7 @@
       </c>
       <c r="T249" s="1"/>
     </row>
-    <row r="250" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A250" s="1" t="s">
         <v>332</v>
       </c>
@@ -18569,7 +18575,7 @@
       </c>
       <c r="T250" s="1"/>
     </row>
-    <row r="251" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A251" s="1" t="s">
         <v>332</v>
       </c>
@@ -18619,7 +18625,7 @@
       </c>
       <c r="T251" s="1"/>
     </row>
-    <row r="252" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A252" s="1" t="s">
         <v>332</v>
       </c>
@@ -18671,7 +18677,7 @@
       </c>
       <c r="T252" s="1"/>
     </row>
-    <row r="253" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A253" s="1" t="s">
         <v>332</v>
       </c>
@@ -18721,7 +18727,7 @@
       </c>
       <c r="T253" s="1"/>
     </row>
-    <row r="254" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A254" s="1" t="s">
         <v>332</v>
       </c>
@@ -18773,7 +18779,7 @@
       </c>
       <c r="T254" s="1"/>
     </row>
-    <row r="255" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A255" s="1" t="s">
         <v>332</v>
       </c>
@@ -18823,7 +18829,7 @@
       </c>
       <c r="T255" s="1"/>
     </row>
-    <row r="256" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A256" s="1" t="s">
         <v>332</v>
       </c>
@@ -18873,7 +18879,7 @@
       </c>
       <c r="T256" s="1"/>
     </row>
-    <row r="257" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A257" s="1" t="s">
         <v>332</v>
       </c>
@@ -18925,7 +18931,7 @@
       </c>
       <c r="T257" s="1"/>
     </row>
-    <row r="258" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A258" s="1" t="s">
         <v>332</v>
       </c>
@@ -18977,7 +18983,7 @@
       </c>
       <c r="T258" s="1"/>
     </row>
-    <row r="259" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A259" s="1" t="s">
         <v>332</v>
       </c>
@@ -19026,7 +19032,7 @@
       </c>
       <c r="T259" s="1"/>
     </row>
-    <row r="260" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A260" s="1" t="s">
         <v>332</v>
       </c>
@@ -19076,7 +19082,7 @@
       </c>
       <c r="T260" s="1"/>
     </row>
-    <row r="261" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A261" s="1" t="s">
         <v>332</v>
       </c>
@@ -19125,7 +19131,7 @@
       </c>
       <c r="T261" s="1"/>
     </row>
-    <row r="262" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A262" s="1" t="s">
         <v>332</v>
       </c>
@@ -19175,7 +19181,7 @@
       </c>
       <c r="T262" s="1"/>
     </row>
-    <row r="263" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A263" s="1" t="s">
         <v>332</v>
       </c>
@@ -19227,7 +19233,7 @@
       </c>
       <c r="T263" s="1"/>
     </row>
-    <row r="264" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A264" s="1" t="s">
         <v>332</v>
       </c>
@@ -19277,7 +19283,7 @@
       </c>
       <c r="T264" s="1"/>
     </row>
-    <row r="265" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A265" s="1" t="s">
         <v>332</v>
       </c>
@@ -19327,7 +19333,7 @@
       </c>
       <c r="T265" s="1"/>
     </row>
-    <row r="266" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A266" s="1" t="s">
         <v>332</v>
       </c>
@@ -19379,7 +19385,7 @@
       </c>
       <c r="T266" s="1"/>
     </row>
-    <row r="267" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A267" s="1" t="s">
         <v>332</v>
       </c>
@@ -19429,7 +19435,7 @@
       </c>
       <c r="T267" s="1"/>
     </row>
-    <row r="268" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A268" s="1" t="s">
         <v>332</v>
       </c>
@@ -19479,7 +19485,7 @@
       </c>
       <c r="T268" s="1"/>
     </row>
-    <row r="269" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A269" s="1" t="s">
         <v>332</v>
       </c>
@@ -19529,7 +19535,7 @@
       </c>
       <c r="T269" s="1"/>
     </row>
-    <row r="270" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A270" s="1" t="s">
         <v>332</v>
       </c>
@@ -19579,7 +19585,7 @@
       </c>
       <c r="T270" s="1"/>
     </row>
-    <row r="271" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A271" s="1" t="s">
         <v>332</v>
       </c>
@@ -19629,7 +19635,7 @@
       </c>
       <c r="T271" s="1"/>
     </row>
-    <row r="272" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A272" s="1" t="s">
         <v>332</v>
       </c>
@@ -19679,7 +19685,7 @@
       </c>
       <c r="T272" s="1"/>
     </row>
-    <row r="273" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A273" s="1" t="s">
         <v>332</v>
       </c>
@@ -19729,7 +19735,7 @@
       </c>
       <c r="T273" s="1"/>
     </row>
-    <row r="274" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A274" s="1" t="s">
         <v>332</v>
       </c>
@@ -19785,7 +19791,7 @@
         <v>1862</v>
       </c>
     </row>
-    <row r="275" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A275" s="1" t="s">
         <v>332</v>
       </c>
@@ -19841,7 +19847,7 @@
         <v>1862</v>
       </c>
     </row>
-    <row r="276" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A276" s="1" t="s">
         <v>332</v>
       </c>
@@ -19891,7 +19897,7 @@
       </c>
       <c r="T276" s="1"/>
     </row>
-    <row r="277" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A277" s="1" t="s">
         <v>332</v>
       </c>
@@ -19941,7 +19947,7 @@
       </c>
       <c r="T277" s="1"/>
     </row>
-    <row r="278" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A278" s="1" t="s">
         <v>332</v>
       </c>
@@ -19991,7 +19997,7 @@
       </c>
       <c r="T278" s="1"/>
     </row>
-    <row r="279" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A279" s="1" t="s">
         <v>332</v>
       </c>
@@ -20047,7 +20053,7 @@
         <v>1862</v>
       </c>
     </row>
-    <row r="280" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A280" s="1" t="s">
         <v>332</v>
       </c>
@@ -20103,7 +20109,7 @@
         <v>1862</v>
       </c>
     </row>
-    <row r="281" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A281" s="1" t="s">
         <v>332</v>
       </c>
@@ -20153,7 +20159,7 @@
       </c>
       <c r="T281" s="1"/>
     </row>
-    <row r="282" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A282" s="1" t="s">
         <v>332</v>
       </c>
@@ -20203,7 +20209,7 @@
       </c>
       <c r="T282" s="1"/>
     </row>
-    <row r="283" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A283" s="1" t="s">
         <v>332</v>
       </c>
@@ -20253,7 +20259,7 @@
       </c>
       <c r="T283" s="1"/>
     </row>
-    <row r="284" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A284" s="1" t="s">
         <v>332</v>
       </c>
@@ -20303,7 +20309,7 @@
       </c>
       <c r="T284" s="1"/>
     </row>
-    <row r="285" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A285" s="1" t="s">
         <v>332</v>
       </c>
@@ -20353,7 +20359,7 @@
       </c>
       <c r="T285" s="1"/>
     </row>
-    <row r="286" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A286" s="1" t="s">
         <v>332</v>
       </c>
@@ -20403,7 +20409,7 @@
       </c>
       <c r="T286" s="1"/>
     </row>
-    <row r="287" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A287" s="1" t="s">
         <v>332</v>
       </c>
@@ -20459,7 +20465,7 @@
         <v>1862</v>
       </c>
     </row>
-    <row r="288" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A288" s="1" t="s">
         <v>332</v>
       </c>
@@ -20515,7 +20521,7 @@
         <v>1862</v>
       </c>
     </row>
-    <row r="289" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A289" s="1" t="s">
         <v>332</v>
       </c>
@@ -20565,7 +20571,7 @@
       </c>
       <c r="T289" s="1"/>
     </row>
-    <row r="290" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A290" s="1" t="s">
         <v>332</v>
       </c>
@@ -20615,7 +20621,7 @@
       </c>
       <c r="T290" s="1"/>
     </row>
-    <row r="291" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A291" s="1" t="s">
         <v>332</v>
       </c>
@@ -20665,7 +20671,7 @@
       </c>
       <c r="T291" s="1"/>
     </row>
-    <row r="292" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A292" s="1" t="s">
         <v>332</v>
       </c>
@@ -20715,7 +20721,7 @@
       </c>
       <c r="T292" s="1"/>
     </row>
-    <row r="293" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A293" s="1" t="s">
         <v>332</v>
       </c>
@@ -20765,7 +20771,7 @@
       </c>
       <c r="T293" s="1"/>
     </row>
-    <row r="294" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A294" s="1" t="s">
         <v>332</v>
       </c>
@@ -20815,7 +20821,7 @@
       </c>
       <c r="T294" s="1"/>
     </row>
-    <row r="295" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A295" s="1" t="s">
         <v>332</v>
       </c>
@@ -20865,7 +20871,7 @@
       </c>
       <c r="T295" s="1"/>
     </row>
-    <row r="296" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A296" s="1" t="s">
         <v>332</v>
       </c>
@@ -20921,7 +20927,7 @@
         <v>1862</v>
       </c>
     </row>
-    <row r="297" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A297" s="1" t="s">
         <v>332</v>
       </c>
@@ -20977,7 +20983,7 @@
         <v>1862</v>
       </c>
     </row>
-    <row r="298" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A298" s="1" t="s">
         <v>332</v>
       </c>
@@ -21027,7 +21033,7 @@
       </c>
       <c r="T298" s="1"/>
     </row>
-    <row r="299" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A299" s="1" t="s">
         <v>332</v>
       </c>
@@ -21077,7 +21083,7 @@
       </c>
       <c r="T299" s="1"/>
     </row>
-    <row r="300" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A300" s="1" t="s">
         <v>332</v>
       </c>
@@ -21127,7 +21133,7 @@
       </c>
       <c r="T300" s="1"/>
     </row>
-    <row r="301" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A301" s="1" t="s">
         <v>332</v>
       </c>
@@ -21177,7 +21183,7 @@
       </c>
       <c r="T301" s="1"/>
     </row>
-    <row r="302" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A302" s="1" t="s">
         <v>332</v>
       </c>
@@ -21227,7 +21233,7 @@
       </c>
       <c r="T302" s="1"/>
     </row>
-    <row r="303" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A303" s="1" t="s">
         <v>332</v>
       </c>
@@ -21277,7 +21283,7 @@
       </c>
       <c r="T303" s="1"/>
     </row>
-    <row r="304" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A304" s="1" t="s">
         <v>332</v>
       </c>
@@ -21327,7 +21333,7 @@
       </c>
       <c r="T304" s="1"/>
     </row>
-    <row r="305" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A305" s="1" t="s">
         <v>332</v>
       </c>
@@ -21383,7 +21389,7 @@
         <v>1862</v>
       </c>
     </row>
-    <row r="306" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A306" s="1" t="s">
         <v>332</v>
       </c>
@@ -21439,7 +21445,7 @@
         <v>1862</v>
       </c>
     </row>
-    <row r="307" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A307" s="1" t="s">
         <v>332</v>
       </c>
@@ -21489,7 +21495,7 @@
       </c>
       <c r="T307" s="1"/>
     </row>
-    <row r="308" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A308" s="1" t="s">
         <v>332</v>
       </c>
@@ -21545,7 +21551,7 @@
         <v>1862</v>
       </c>
     </row>
-    <row r="309" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A309" s="1" t="s">
         <v>332</v>
       </c>
@@ -21601,7 +21607,7 @@
         <v>1862</v>
       </c>
     </row>
-    <row r="310" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A310" s="1" t="s">
         <v>332</v>
       </c>
@@ -21651,7 +21657,7 @@
       </c>
       <c r="T310" s="1"/>
     </row>
-    <row r="311" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A311" s="1" t="s">
         <v>332</v>
       </c>
@@ -21701,7 +21707,7 @@
       </c>
       <c r="T311" s="1"/>
     </row>
-    <row r="312" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A312" s="1" t="s">
         <v>332</v>
       </c>
@@ -21751,7 +21757,7 @@
       </c>
       <c r="T312" s="1"/>
     </row>
-    <row r="313" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A313" s="1" t="s">
         <v>332</v>
       </c>
@@ -21801,7 +21807,7 @@
       </c>
       <c r="T313" s="1"/>
     </row>
-    <row r="314" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A314" s="1" t="s">
         <v>332</v>
       </c>
@@ -21851,7 +21857,7 @@
       </c>
       <c r="T314" s="1"/>
     </row>
-    <row r="315" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A315" s="1" t="s">
         <v>332</v>
       </c>
@@ -21907,7 +21913,7 @@
         <v>1862</v>
       </c>
     </row>
-    <row r="316" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A316" s="1" t="s">
         <v>332</v>
       </c>
@@ -21963,7 +21969,7 @@
         <v>1862</v>
       </c>
     </row>
-    <row r="317" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A317" s="1" t="s">
         <v>332</v>
       </c>
@@ -22019,7 +22025,7 @@
         <v>1862</v>
       </c>
     </row>
-    <row r="318" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A318" s="1" t="s">
         <v>332</v>
       </c>
@@ -22075,7 +22081,7 @@
         <v>1862</v>
       </c>
     </row>
-    <row r="319" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A319" s="1" t="s">
         <v>332</v>
       </c>
@@ -22131,7 +22137,7 @@
         <v>1862</v>
       </c>
     </row>
-    <row r="320" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A320" s="1" t="s">
         <v>332</v>
       </c>
@@ -22181,7 +22187,7 @@
       </c>
       <c r="T320" s="1"/>
     </row>
-    <row r="321" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A321" s="1" t="s">
         <v>332</v>
       </c>
@@ -22231,7 +22237,7 @@
       </c>
       <c r="T321" s="1"/>
     </row>
-    <row r="322" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A322" s="1" t="s">
         <v>332</v>
       </c>
@@ -22281,7 +22287,7 @@
       </c>
       <c r="T322" s="1"/>
     </row>
-    <row r="323" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A323" s="1" t="s">
         <v>332</v>
       </c>
@@ -22331,7 +22337,7 @@
       </c>
       <c r="T323" s="1"/>
     </row>
-    <row r="324" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A324" s="1" t="s">
         <v>332</v>
       </c>
@@ -22381,7 +22387,7 @@
       </c>
       <c r="T324" s="1"/>
     </row>
-    <row r="325" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A325" s="1" t="s">
         <v>332</v>
       </c>
@@ -22437,7 +22443,7 @@
         <v>1862</v>
       </c>
     </row>
-    <row r="326" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A326" s="1" t="s">
         <v>332</v>
       </c>
@@ -22487,7 +22493,7 @@
       </c>
       <c r="T326" s="1"/>
     </row>
-    <row r="327" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A327" s="1" t="s">
         <v>332</v>
       </c>
@@ -22543,7 +22549,7 @@
         <v>1862</v>
       </c>
     </row>
-    <row r="328" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A328" s="1" t="s">
         <v>332</v>
       </c>
@@ -22593,7 +22599,7 @@
       </c>
       <c r="T328" s="1"/>
     </row>
-    <row r="329" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A329" s="1" t="s">
         <v>332</v>
       </c>
@@ -22643,7 +22649,7 @@
       </c>
       <c r="T329" s="1"/>
     </row>
-    <row r="330" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A330" s="1" t="s">
         <v>332</v>
       </c>
@@ -22699,7 +22705,7 @@
         <v>1862</v>
       </c>
     </row>
-    <row r="331" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A331" s="1" t="s">
         <v>332</v>
       </c>
@@ -22755,7 +22761,7 @@
         <v>1862</v>
       </c>
     </row>
-    <row r="332" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A332" s="1" t="s">
         <v>332</v>
       </c>
@@ -22805,7 +22811,7 @@
       </c>
       <c r="T332" s="1"/>
     </row>
-    <row r="333" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A333" s="1" t="s">
         <v>332</v>
       </c>
@@ -22855,7 +22861,7 @@
       </c>
       <c r="T333" s="1"/>
     </row>
-    <row r="334" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A334" s="1" t="s">
         <v>332</v>
       </c>
@@ -22911,7 +22917,7 @@
         <v>1862</v>
       </c>
     </row>
-    <row r="335" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A335" s="1" t="s">
         <v>332</v>
       </c>
@@ -22961,7 +22967,7 @@
       </c>
       <c r="T335" s="1"/>
     </row>
-    <row r="336" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A336" s="1" t="s">
         <v>332</v>
       </c>
@@ -23011,7 +23017,7 @@
       </c>
       <c r="T336" s="1"/>
     </row>
-    <row r="337" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A337" s="1" t="s">
         <v>332</v>
       </c>
@@ -23061,7 +23067,7 @@
       </c>
       <c r="T337" s="1"/>
     </row>
-    <row r="338" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A338" s="1" t="s">
         <v>332</v>
       </c>
@@ -23111,7 +23117,7 @@
       </c>
       <c r="T338" s="1"/>
     </row>
-    <row r="339" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A339" s="1" t="s">
         <v>332</v>
       </c>
@@ -23161,7 +23167,7 @@
       </c>
       <c r="T339" s="1"/>
     </row>
-    <row r="340" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A340" s="1" t="s">
         <v>332</v>
       </c>
@@ -23211,7 +23217,7 @@
       </c>
       <c r="T340" s="1"/>
     </row>
-    <row r="341" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A341" s="1" t="s">
         <v>332</v>
       </c>
@@ -23261,7 +23267,7 @@
       </c>
       <c r="T341" s="1"/>
     </row>
-    <row r="342" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A342" s="1" t="s">
         <v>332</v>
       </c>
@@ -23311,7 +23317,7 @@
       </c>
       <c r="T342" s="1"/>
     </row>
-    <row r="343" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A343" s="1" t="s">
         <v>332</v>
       </c>
@@ -23361,7 +23367,7 @@
       </c>
       <c r="T343" s="1"/>
     </row>
-    <row r="344" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A344" s="1" t="s">
         <v>332</v>
       </c>
@@ -23411,7 +23417,7 @@
       </c>
       <c r="T344" s="1"/>
     </row>
-    <row r="345" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A345" s="1" t="s">
         <v>332</v>
       </c>
@@ -23461,7 +23467,7 @@
       </c>
       <c r="T345" s="1"/>
     </row>
-    <row r="346" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A346" s="1" t="s">
         <v>332</v>
       </c>
@@ -23511,7 +23517,7 @@
       </c>
       <c r="T346" s="1"/>
     </row>
-    <row r="347" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A347" s="1" t="s">
         <v>332</v>
       </c>
@@ -23561,7 +23567,7 @@
       </c>
       <c r="T347" s="1"/>
     </row>
-    <row r="348" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A348" s="1" t="s">
         <v>332</v>
       </c>
@@ -23611,7 +23617,7 @@
       </c>
       <c r="T348" s="1"/>
     </row>
-    <row r="349" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A349" s="1" t="s">
         <v>332</v>
       </c>
@@ -23661,7 +23667,7 @@
       </c>
       <c r="T349" s="1"/>
     </row>
-    <row r="350" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A350" s="1" t="s">
         <v>332</v>
       </c>
@@ -23711,7 +23717,7 @@
       </c>
       <c r="T350" s="1"/>
     </row>
-    <row r="351" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A351" s="1" t="s">
         <v>332</v>
       </c>
@@ -23761,7 +23767,7 @@
       </c>
       <c r="T351" s="1"/>
     </row>
-    <row r="352" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A352" s="1" t="s">
         <v>332</v>
       </c>
@@ -23811,7 +23817,7 @@
       </c>
       <c r="T352" s="1"/>
     </row>
-    <row r="353" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A353" s="1" t="s">
         <v>332</v>
       </c>
@@ -23867,7 +23873,7 @@
         <v>1862</v>
       </c>
     </row>
-    <row r="354" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A354" s="1" t="s">
         <v>332</v>
       </c>
@@ -23923,7 +23929,7 @@
         <v>1862</v>
       </c>
     </row>
-    <row r="355" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A355" s="1" t="s">
         <v>332</v>
       </c>
@@ -23973,7 +23979,7 @@
       </c>
       <c r="T355" s="1"/>
     </row>
-    <row r="356" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A356" s="1" t="s">
         <v>332</v>
       </c>
@@ -24029,7 +24035,7 @@
         <v>1862</v>
       </c>
     </row>
-    <row r="357" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A357" s="1" t="s">
         <v>332</v>
       </c>
@@ -24085,7 +24091,7 @@
         <v>1862</v>
       </c>
     </row>
-    <row r="358" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A358" s="1" t="s">
         <v>332</v>
       </c>
@@ -24135,7 +24141,7 @@
       </c>
       <c r="T358" s="1"/>
     </row>
-    <row r="359" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A359" s="1" t="s">
         <v>332</v>
       </c>
@@ -24191,7 +24197,7 @@
         <v>1862</v>
       </c>
     </row>
-    <row r="360" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A360" s="1" t="s">
         <v>332</v>
       </c>
@@ -24247,7 +24253,7 @@
         <v>1862</v>
       </c>
     </row>
-    <row r="361" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A361" s="1" t="s">
         <v>332</v>
       </c>
@@ -24297,7 +24303,7 @@
       </c>
       <c r="T361" s="1"/>
     </row>
-    <row r="362" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A362" s="1" t="s">
         <v>332</v>
       </c>
@@ -24353,7 +24359,7 @@
         <v>1862</v>
       </c>
     </row>
-    <row r="363" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A363" s="1" t="s">
         <v>332</v>
       </c>
@@ -24409,7 +24415,7 @@
         <v>1862</v>
       </c>
     </row>
-    <row r="364" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A364" s="1" t="s">
         <v>332</v>
       </c>
@@ -24459,7 +24465,7 @@
       </c>
       <c r="T364" s="1"/>
     </row>
-    <row r="365" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A365" s="1" t="s">
         <v>332</v>
       </c>
@@ -24509,7 +24515,7 @@
       </c>
       <c r="T365" s="1"/>
     </row>
-    <row r="366" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A366" s="1" t="s">
         <v>332</v>
       </c>
@@ -24559,7 +24565,7 @@
       </c>
       <c r="T366" s="1"/>
     </row>
-    <row r="367" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A367" s="1" t="s">
         <v>332</v>
       </c>
@@ -24609,7 +24615,7 @@
       </c>
       <c r="T367" s="1"/>
     </row>
-    <row r="368" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A368" s="1" t="s">
         <v>332</v>
       </c>
@@ -24659,7 +24665,7 @@
       </c>
       <c r="T368" s="1"/>
     </row>
-    <row r="369" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A369" s="1" t="s">
         <v>332</v>
       </c>
@@ -24709,7 +24715,7 @@
       </c>
       <c r="T369" s="1"/>
     </row>
-    <row r="370" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A370" s="1" t="s">
         <v>332</v>
       </c>
@@ -24759,7 +24765,7 @@
       </c>
       <c r="T370" s="1"/>
     </row>
-    <row r="371" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A371" s="1" t="s">
         <v>332</v>
       </c>
@@ -24809,7 +24815,7 @@
       </c>
       <c r="T371" s="1"/>
     </row>
-    <row r="372" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A372" s="1" t="s">
         <v>332</v>
       </c>
@@ -24859,7 +24865,7 @@
       </c>
       <c r="T372" s="1"/>
     </row>
-    <row r="373" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A373" s="1" t="s">
         <v>332</v>
       </c>
@@ -24909,7 +24915,7 @@
       </c>
       <c r="T373" s="1"/>
     </row>
-    <row r="374" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A374" s="1" t="s">
         <v>332</v>
       </c>
@@ -24959,7 +24965,7 @@
       </c>
       <c r="T374" s="1"/>
     </row>
-    <row r="375" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A375" s="1" t="s">
         <v>332</v>
       </c>
@@ -25009,7 +25015,7 @@
       </c>
       <c r="T375" s="1"/>
     </row>
-    <row r="376" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A376" s="1" t="s">
         <v>332</v>
       </c>
@@ -25059,7 +25065,7 @@
       </c>
       <c r="T376" s="1"/>
     </row>
-    <row r="377" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A377" s="1" t="s">
         <v>332</v>
       </c>
@@ -25109,7 +25115,7 @@
       </c>
       <c r="T377" s="1"/>
     </row>
-    <row r="378" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A378" s="1" t="s">
         <v>332</v>
       </c>
@@ -25159,7 +25165,7 @@
       </c>
       <c r="T378" s="1"/>
     </row>
-    <row r="379" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A379" s="1" t="s">
         <v>332</v>
       </c>
@@ -25209,7 +25215,7 @@
       </c>
       <c r="T379" s="1"/>
     </row>
-    <row r="380" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A380" s="1" t="s">
         <v>332</v>
       </c>
@@ -25259,7 +25265,7 @@
       </c>
       <c r="T380" s="1"/>
     </row>
-    <row r="381" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A381" s="1" t="s">
         <v>332</v>
       </c>
@@ -25315,7 +25321,7 @@
         <v>1862</v>
       </c>
     </row>
-    <row r="382" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A382" s="1" t="s">
         <v>332</v>
       </c>
@@ -25371,7 +25377,7 @@
         <v>1862</v>
       </c>
     </row>
-    <row r="383" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A383" s="1" t="s">
         <v>332</v>
       </c>
@@ -25427,7 +25433,7 @@
         <v>1862</v>
       </c>
     </row>
-    <row r="384" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A384" s="1" t="s">
         <v>332</v>
       </c>
@@ -25483,7 +25489,7 @@
         <v>1862</v>
       </c>
     </row>
-    <row r="385" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A385" s="1" t="s">
         <v>332</v>
       </c>
@@ -25533,7 +25539,7 @@
       </c>
       <c r="T385" s="1"/>
     </row>
-    <row r="386" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A386" s="1" t="s">
         <v>332</v>
       </c>
@@ -25583,7 +25589,7 @@
       </c>
       <c r="T386" s="1"/>
     </row>
-    <row r="387" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A387" s="1" t="s">
         <v>332</v>
       </c>
@@ -25633,7 +25639,7 @@
       </c>
       <c r="T387" s="1"/>
     </row>
-    <row r="388" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A388" s="1" t="s">
         <v>332</v>
       </c>
@@ -25689,7 +25695,7 @@
         <v>1862</v>
       </c>
     </row>
-    <row r="389" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A389" s="1" t="s">
         <v>332</v>
       </c>
@@ -25745,7 +25751,7 @@
         <v>1862</v>
       </c>
     </row>
-    <row r="390" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A390" s="1" t="s">
         <v>332</v>
       </c>
@@ -25801,7 +25807,7 @@
         <v>1862</v>
       </c>
     </row>
-    <row r="391" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A391" s="1" t="s">
         <v>332</v>
       </c>
@@ -25851,7 +25857,7 @@
       </c>
       <c r="T391" s="1"/>
     </row>
-    <row r="392" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A392" s="1" t="s">
         <v>332</v>
       </c>
@@ -25901,7 +25907,7 @@
       </c>
       <c r="T392" s="1"/>
     </row>
-    <row r="393" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A393" s="1" t="s">
         <v>332</v>
       </c>
@@ -25957,7 +25963,7 @@
         <v>1862</v>
       </c>
     </row>
-    <row r="394" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A394" s="1" t="s">
         <v>332</v>
       </c>
@@ -26013,7 +26019,7 @@
         <v>1862</v>
       </c>
     </row>
-    <row r="395" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A395" s="1" t="s">
         <v>332</v>
       </c>
@@ -26069,7 +26075,7 @@
         <v>1862</v>
       </c>
     </row>
-    <row r="396" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A396" s="1" t="s">
         <v>332</v>
       </c>
@@ -26119,7 +26125,7 @@
       </c>
       <c r="T396" s="1"/>
     </row>
-    <row r="397" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A397" s="1" t="s">
         <v>332</v>
       </c>
@@ -26169,7 +26175,7 @@
       </c>
       <c r="T397" s="1"/>
     </row>
-    <row r="398" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A398" s="1" t="s">
         <v>332</v>
       </c>
@@ -26219,7 +26225,7 @@
       </c>
       <c r="T398" s="1"/>
     </row>
-    <row r="399" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A399" s="1" t="s">
         <v>332</v>
       </c>
@@ -26269,7 +26275,7 @@
       </c>
       <c r="T399" s="1"/>
     </row>
-    <row r="400" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A400" s="1" t="s">
         <v>332</v>
       </c>
@@ -26319,7 +26325,7 @@
       </c>
       <c r="T400" s="1"/>
     </row>
-    <row r="401" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A401" s="1" t="s">
         <v>332</v>
       </c>
@@ -26375,7 +26381,7 @@
         <v>1862</v>
       </c>
     </row>
-    <row r="402" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A402" s="1" t="s">
         <v>332</v>
       </c>
@@ -26431,7 +26437,7 @@
         <v>1862</v>
       </c>
     </row>
-    <row r="403" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A403" s="1" t="s">
         <v>332</v>
       </c>
@@ -26487,7 +26493,7 @@
         <v>1862</v>
       </c>
     </row>
-    <row r="404" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A404" s="1" t="s">
         <v>332</v>
       </c>
@@ -26537,7 +26543,7 @@
       </c>
       <c r="T404" s="1"/>
     </row>
-    <row r="405" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A405" s="1" t="s">
         <v>332</v>
       </c>
@@ -26593,7 +26599,7 @@
         <v>1862</v>
       </c>
     </row>
-    <row r="406" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A406" s="1" t="s">
         <v>332</v>
       </c>
@@ -26649,7 +26655,7 @@
         <v>1862</v>
       </c>
     </row>
-    <row r="407" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A407" s="1" t="s">
         <v>332</v>
       </c>
@@ -26705,7 +26711,7 @@
         <v>1862</v>
       </c>
     </row>
-    <row r="408" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A408" s="1" t="s">
         <v>332</v>
       </c>
@@ -26755,7 +26761,7 @@
       </c>
       <c r="T408" s="1"/>
     </row>
-    <row r="409" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A409" s="1" t="s">
         <v>332</v>
       </c>
@@ -26805,7 +26811,7 @@
       </c>
       <c r="T409" s="1"/>
     </row>
-    <row r="410" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A410" s="1" t="s">
         <v>332</v>
       </c>
@@ -26861,7 +26867,7 @@
         <v>1862</v>
       </c>
     </row>
-    <row r="411" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A411" s="1" t="s">
         <v>332</v>
       </c>
@@ -26917,7 +26923,7 @@
         <v>1862</v>
       </c>
     </row>
-    <row r="412" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A412" s="1" t="s">
         <v>332</v>
       </c>
@@ -26973,7 +26979,7 @@
         <v>1862</v>
       </c>
     </row>
-    <row r="413" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A413" s="1" t="s">
         <v>332</v>
       </c>
@@ -27023,7 +27029,7 @@
       </c>
       <c r="T413" s="1"/>
     </row>
-    <row r="414" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A414" s="1" t="s">
         <v>332</v>
       </c>
@@ -27073,7 +27079,7 @@
       </c>
       <c r="T414" s="1"/>
     </row>
-    <row r="415" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A415" s="1" t="s">
         <v>332</v>
       </c>
@@ -27123,7 +27129,7 @@
       </c>
       <c r="T415" s="1"/>
     </row>
-    <row r="416" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A416" s="1" t="s">
         <v>332</v>
       </c>
@@ -27173,7 +27179,7 @@
       </c>
       <c r="T416" s="1"/>
     </row>
-    <row r="417" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A417" s="1" t="s">
         <v>332</v>
       </c>
@@ -27229,7 +27235,7 @@
         <v>1862</v>
       </c>
     </row>
-    <row r="418" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A418" s="1" t="s">
         <v>332</v>
       </c>
@@ -27285,7 +27291,7 @@
         <v>1862</v>
       </c>
     </row>
-    <row r="419" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A419" s="1" t="s">
         <v>332</v>
       </c>
@@ -27341,7 +27347,7 @@
         <v>1862</v>
       </c>
     </row>
-    <row r="420" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A420" s="1" t="s">
         <v>332</v>
       </c>
@@ -27391,7 +27397,7 @@
       </c>
       <c r="T420" s="1"/>
     </row>
-    <row r="421" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A421" s="1" t="s">
         <v>332</v>
       </c>
@@ -27447,7 +27453,7 @@
         <v>1862</v>
       </c>
     </row>
-    <row r="422" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A422" s="1" t="s">
         <v>332</v>
       </c>
@@ -27503,7 +27509,7 @@
         <v>1862</v>
       </c>
     </row>
-    <row r="423" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A423" s="1" t="s">
         <v>332</v>
       </c>
@@ -27559,7 +27565,7 @@
         <v>1862</v>
       </c>
     </row>
-    <row r="424" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A424" s="1" t="s">
         <v>332</v>
       </c>
@@ -27609,7 +27615,7 @@
       </c>
       <c r="T424" s="1"/>
     </row>
-    <row r="425" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A425" s="1" t="s">
         <v>332</v>
       </c>
@@ -27659,7 +27665,7 @@
       </c>
       <c r="T425" s="1"/>
     </row>
-    <row r="426" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A426" s="1" t="s">
         <v>332</v>
       </c>
@@ -27709,7 +27715,7 @@
       </c>
       <c r="T426" s="1"/>
     </row>
-    <row r="427" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A427" s="1" t="s">
         <v>332</v>
       </c>
@@ -27759,7 +27765,7 @@
       </c>
       <c r="T427" s="1"/>
     </row>
-    <row r="428" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A428" s="1" t="s">
         <v>332</v>
       </c>
@@ -27809,7 +27815,7 @@
       </c>
       <c r="T428" s="1"/>
     </row>
-    <row r="429" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A429" s="1" t="s">
         <v>332</v>
       </c>
@@ -27865,7 +27871,7 @@
         <v>1862</v>
       </c>
     </row>
-    <row r="430" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A430" s="1" t="s">
         <v>332</v>
       </c>
@@ -27915,7 +27921,7 @@
       </c>
       <c r="T430" s="1"/>
     </row>
-    <row r="431" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A431" s="1" t="s">
         <v>332</v>
       </c>
@@ -27965,7 +27971,7 @@
       </c>
       <c r="T431" s="1"/>
     </row>
-    <row r="432" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A432" s="1" t="s">
         <v>332</v>
       </c>
@@ -28015,7 +28021,7 @@
       </c>
       <c r="T432" s="1"/>
     </row>
-    <row r="433" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A433" s="1" t="s">
         <v>332</v>
       </c>
@@ -28065,7 +28071,7 @@
       </c>
       <c r="T433" s="1"/>
     </row>
-    <row r="434" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A434" s="1" t="s">
         <v>332</v>
       </c>
@@ -28115,7 +28121,7 @@
       </c>
       <c r="T434" s="1"/>
     </row>
-    <row r="435" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A435" s="1" t="s">
         <v>332</v>
       </c>
@@ -28165,7 +28171,7 @@
       </c>
       <c r="T435" s="1"/>
     </row>
-    <row r="436" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A436" s="1" t="s">
         <v>332</v>
       </c>
@@ -28215,7 +28221,7 @@
       </c>
       <c r="T436" s="1"/>
     </row>
-    <row r="437" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A437" s="1" t="s">
         <v>332</v>
       </c>
@@ -28271,7 +28277,7 @@
         <v>1862</v>
       </c>
     </row>
-    <row r="438" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A438" s="1" t="s">
         <v>332</v>
       </c>
@@ -28327,7 +28333,7 @@
         <v>1862</v>
       </c>
     </row>
-    <row r="439" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A439" s="1" t="s">
         <v>332</v>
       </c>
@@ -28383,7 +28389,7 @@
         <v>1862</v>
       </c>
     </row>
-    <row r="440" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A440" s="1" t="s">
         <v>332</v>
       </c>
@@ -28433,7 +28439,7 @@
       </c>
       <c r="T440" s="1"/>
     </row>
-    <row r="441" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A441" s="1" t="s">
         <v>332</v>
       </c>
@@ -28489,7 +28495,7 @@
         <v>1862</v>
       </c>
     </row>
-    <row r="442" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A442" s="1" t="s">
         <v>332</v>
       </c>
@@ -28545,7 +28551,7 @@
         <v>1862</v>
       </c>
     </row>
-    <row r="443" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A443" s="1" t="s">
         <v>332</v>
       </c>
@@ -28601,7 +28607,7 @@
         <v>1862</v>
       </c>
     </row>
-    <row r="444" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A444" s="1" t="s">
         <v>332</v>
       </c>
@@ -28651,7 +28657,7 @@
       </c>
       <c r="T444" s="1"/>
     </row>
-    <row r="445" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A445" s="1" t="s">
         <v>332</v>
       </c>
@@ -28701,7 +28707,7 @@
       </c>
       <c r="T445" s="1"/>
     </row>
-    <row r="446" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="446" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A446" s="1" t="s">
         <v>332</v>
       </c>
@@ -28757,7 +28763,7 @@
         <v>1862</v>
       </c>
     </row>
-    <row r="447" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="447" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A447" s="1" t="s">
         <v>332</v>
       </c>
@@ -28807,7 +28813,7 @@
       </c>
       <c r="T447" s="1"/>
     </row>
-    <row r="448" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="448" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A448" s="1" t="s">
         <v>332</v>
       </c>
@@ -28857,7 +28863,7 @@
       </c>
       <c r="T448" s="1"/>
     </row>
-    <row r="449" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A449" s="1" t="s">
         <v>332</v>
       </c>
@@ -28907,7 +28913,7 @@
       </c>
       <c r="T449" s="1"/>
     </row>
-    <row r="450" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="450" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A450" s="1" t="s">
         <v>332</v>
       </c>
@@ -28941,7 +28947,7 @@
       </c>
       <c r="T450" s="1"/>
     </row>
-    <row r="451" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="451" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A451" s="1" t="s">
         <v>332</v>
       </c>
@@ -28991,7 +28997,7 @@
       </c>
       <c r="T451" s="1"/>
     </row>
-    <row r="452" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="452" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A452" s="1" t="s">
         <v>332</v>
       </c>
@@ -29041,7 +29047,7 @@
       </c>
       <c r="T452" s="1"/>
     </row>
-    <row r="453" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="453" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A453" s="1" t="s">
         <v>332</v>
       </c>
@@ -29091,7 +29097,7 @@
       </c>
       <c r="T453" s="1"/>
     </row>
-    <row r="454" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="454" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A454" s="1" t="s">
         <v>332</v>
       </c>
@@ -29141,7 +29147,7 @@
       </c>
       <c r="T454" s="1"/>
     </row>
-    <row r="455" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="455" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A455" s="1" t="s">
         <v>332</v>
       </c>
@@ -29191,7 +29197,7 @@
       </c>
       <c r="T455" s="1"/>
     </row>
-    <row r="456" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="456" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A456" s="1" t="s">
         <v>332</v>
       </c>
@@ -29241,7 +29247,7 @@
       </c>
       <c r="T456" s="1"/>
     </row>
-    <row r="457" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="457" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A457" s="1" t="s">
         <v>332</v>
       </c>
@@ -29293,7 +29299,7 @@
       </c>
       <c r="T457" s="1"/>
     </row>
-    <row r="458" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="458" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A458" s="1" t="s">
         <v>332</v>
       </c>
@@ -29345,7 +29351,7 @@
       </c>
       <c r="T458" s="1"/>
     </row>
-    <row r="459" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="459" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A459" s="1" t="s">
         <v>332</v>
       </c>
@@ -29397,7 +29403,7 @@
       </c>
       <c r="T459" s="1"/>
     </row>
-    <row r="460" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="460" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A460" s="1" t="s">
         <v>332</v>
       </c>
@@ -29449,7 +29455,7 @@
       </c>
       <c r="T460" s="1"/>
     </row>
-    <row r="461" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="461" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A461" s="1" t="s">
         <v>332</v>
       </c>
@@ -29501,7 +29507,7 @@
       </c>
       <c r="T461" s="1"/>
     </row>
-    <row r="462" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="462" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A462" s="1" t="s">
         <v>332</v>
       </c>
@@ -29551,7 +29557,7 @@
       </c>
       <c r="T462" s="1"/>
     </row>
-    <row r="463" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="463" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A463" s="1" t="s">
         <v>332</v>
       </c>
@@ -29601,7 +29607,7 @@
       </c>
       <c r="T463" s="1"/>
     </row>
-    <row r="464" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="464" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A464" s="1" t="s">
         <v>332</v>
       </c>
@@ -29651,7 +29657,7 @@
       </c>
       <c r="T464" s="1"/>
     </row>
-    <row r="465" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="465" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A465" s="1" t="s">
         <v>332</v>
       </c>
@@ -29703,7 +29709,7 @@
       </c>
       <c r="T465" s="1"/>
     </row>
-    <row r="466" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="466" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A466" s="1" t="s">
         <v>332</v>
       </c>
@@ -29755,7 +29761,7 @@
       </c>
       <c r="T466" s="1"/>
     </row>
-    <row r="467" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="467" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A467" s="1" t="s">
         <v>332</v>
       </c>
@@ -29804,7 +29810,7 @@
       </c>
       <c r="T467" s="1"/>
     </row>
-    <row r="468" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="468" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A468" s="1" t="s">
         <v>332</v>
       </c>
@@ -29854,7 +29860,7 @@
       </c>
       <c r="T468" s="1"/>
     </row>
-    <row r="469" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="469" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A469" s="1" t="s">
         <v>332</v>
       </c>
@@ -29903,7 +29909,7 @@
       </c>
       <c r="T469" s="1"/>
     </row>
-    <row r="470" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="470" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A470" s="1" t="s">
         <v>332</v>
       </c>
@@ -29953,7 +29959,7 @@
       </c>
       <c r="T470" s="1"/>
     </row>
-    <row r="471" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="471" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A471" s="1" t="s">
         <v>332</v>
       </c>
@@ -30005,7 +30011,7 @@
       </c>
       <c r="T471" s="1"/>
     </row>
-    <row r="472" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="472" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A472" s="1" t="s">
         <v>332</v>
       </c>
@@ -30055,7 +30061,7 @@
       </c>
       <c r="T472" s="1"/>
     </row>
-    <row r="473" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="473" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A473" s="1" t="s">
         <v>332</v>
       </c>
@@ -30105,7 +30111,7 @@
       </c>
       <c r="T473" s="1"/>
     </row>
-    <row r="474" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="474" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A474" s="1" t="s">
         <v>332</v>
       </c>
@@ -30157,7 +30163,7 @@
       </c>
       <c r="T474" s="1"/>
     </row>
-    <row r="475" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="475" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A475" s="1" t="s">
         <v>332</v>
       </c>
@@ -30207,7 +30213,7 @@
       </c>
       <c r="T475" s="1"/>
     </row>
-    <row r="476" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="476" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A476" s="1" t="s">
         <v>332</v>
       </c>
@@ -30257,7 +30263,7 @@
       </c>
       <c r="T476" s="1"/>
     </row>
-    <row r="477" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="477" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A477" s="1" t="s">
         <v>332</v>
       </c>
@@ -30307,7 +30313,7 @@
       </c>
       <c r="T477" s="1"/>
     </row>
-    <row r="478" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="478" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A478" s="1" t="s">
         <v>332</v>
       </c>
@@ -30357,7 +30363,7 @@
       </c>
       <c r="T478" s="1"/>
     </row>
-    <row r="479" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="479" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A479" s="1" t="s">
         <v>332</v>
       </c>
@@ -30407,7 +30413,7 @@
       </c>
       <c r="T479" s="1"/>
     </row>
-    <row r="480" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="480" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A480" s="1" t="s">
         <v>332</v>
       </c>
@@ -30457,7 +30463,7 @@
       </c>
       <c r="T480" s="1"/>
     </row>
-    <row r="481" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="481" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A481" s="1" t="s">
         <v>332</v>
       </c>
@@ -30507,7 +30513,7 @@
       </c>
       <c r="T481" s="1"/>
     </row>
-    <row r="482" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="482" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A482" s="1" t="s">
         <v>332</v>
       </c>
@@ -30563,7 +30569,7 @@
         <v>1862</v>
       </c>
     </row>
-    <row r="483" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="483" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A483" s="1" t="s">
         <v>332</v>
       </c>
@@ -30619,7 +30625,7 @@
         <v>1862</v>
       </c>
     </row>
-    <row r="484" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="484" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A484" s="1" t="s">
         <v>332</v>
       </c>
@@ -30669,7 +30675,7 @@
       </c>
       <c r="T484" s="1"/>
     </row>
-    <row r="485" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="485" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A485" s="1" t="s">
         <v>332</v>
       </c>
@@ -30719,7 +30725,7 @@
       </c>
       <c r="T485" s="1"/>
     </row>
-    <row r="486" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="486" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A486" s="1" t="s">
         <v>332</v>
       </c>
@@ -30769,7 +30775,7 @@
       </c>
       <c r="T486" s="1"/>
     </row>
-    <row r="487" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="487" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A487" s="1" t="s">
         <v>332</v>
       </c>
@@ -30825,7 +30831,7 @@
         <v>1862</v>
       </c>
     </row>
-    <row r="488" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="488" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A488" s="1" t="s">
         <v>332</v>
       </c>
@@ -30881,7 +30887,7 @@
         <v>1862</v>
       </c>
     </row>
-    <row r="489" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="489" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A489" s="1" t="s">
         <v>332</v>
       </c>
@@ -30931,7 +30937,7 @@
       </c>
       <c r="T489" s="1"/>
     </row>
-    <row r="490" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="490" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A490" s="1" t="s">
         <v>332</v>
       </c>
@@ -30981,7 +30987,7 @@
       </c>
       <c r="T490" s="1"/>
     </row>
-    <row r="491" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="491" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A491" s="1" t="s">
         <v>332</v>
       </c>
@@ -31031,7 +31037,7 @@
       </c>
       <c r="T491" s="1"/>
     </row>
-    <row r="492" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="492" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A492" s="1" t="s">
         <v>332</v>
       </c>
@@ -31081,7 +31087,7 @@
       </c>
       <c r="T492" s="1"/>
     </row>
-    <row r="493" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="493" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A493" s="1" t="s">
         <v>332</v>
       </c>
@@ -31131,7 +31137,7 @@
       </c>
       <c r="T493" s="1"/>
     </row>
-    <row r="494" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="494" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A494" s="1" t="s">
         <v>332</v>
       </c>
@@ -31181,7 +31187,7 @@
       </c>
       <c r="T494" s="1"/>
     </row>
-    <row r="495" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="495" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A495" s="1" t="s">
         <v>332</v>
       </c>
@@ -31237,7 +31243,7 @@
         <v>1862</v>
       </c>
     </row>
-    <row r="496" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="496" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A496" s="1" t="s">
         <v>332</v>
       </c>
@@ -31293,7 +31299,7 @@
         <v>1862</v>
       </c>
     </row>
-    <row r="497" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="497" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A497" s="1" t="s">
         <v>332</v>
       </c>
@@ -31343,7 +31349,7 @@
       </c>
       <c r="T497" s="1"/>
     </row>
-    <row r="498" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="498" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A498" s="1" t="s">
         <v>332</v>
       </c>
@@ -31393,7 +31399,7 @@
       </c>
       <c r="T498" s="1"/>
     </row>
-    <row r="499" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="499" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A499" s="1" t="s">
         <v>332</v>
       </c>
@@ -31443,7 +31449,7 @@
       </c>
       <c r="T499" s="1"/>
     </row>
-    <row r="500" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="500" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A500" s="1" t="s">
         <v>332</v>
       </c>
@@ -31493,7 +31499,7 @@
       </c>
       <c r="T500" s="1"/>
     </row>
-    <row r="501" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="501" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A501" s="1" t="s">
         <v>332</v>
       </c>
@@ -31543,7 +31549,7 @@
       </c>
       <c r="T501" s="1"/>
     </row>
-    <row r="502" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="502" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A502" s="1" t="s">
         <v>332</v>
       </c>
@@ -31593,7 +31599,7 @@
       </c>
       <c r="T502" s="1"/>
     </row>
-    <row r="503" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="503" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A503" s="1" t="s">
         <v>332</v>
       </c>
@@ -31643,7 +31649,7 @@
       </c>
       <c r="T503" s="1"/>
     </row>
-    <row r="504" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="504" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A504" s="1" t="s">
         <v>332</v>
       </c>
@@ -31699,7 +31705,7 @@
         <v>1862</v>
       </c>
     </row>
-    <row r="505" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="505" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A505" s="1" t="s">
         <v>332</v>
       </c>
@@ -31755,7 +31761,7 @@
         <v>1862</v>
       </c>
     </row>
-    <row r="506" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="506" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A506" s="1" t="s">
         <v>332</v>
       </c>
@@ -31805,7 +31811,7 @@
       </c>
       <c r="T506" s="1"/>
     </row>
-    <row r="507" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="507" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A507" s="1" t="s">
         <v>332</v>
       </c>
@@ -31855,7 +31861,7 @@
       </c>
       <c r="T507" s="1"/>
     </row>
-    <row r="508" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="508" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A508" s="1" t="s">
         <v>332</v>
       </c>
@@ -31905,7 +31911,7 @@
       </c>
       <c r="T508" s="1"/>
     </row>
-    <row r="509" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="509" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A509" s="1" t="s">
         <v>332</v>
       </c>
@@ -31955,7 +31961,7 @@
       </c>
       <c r="T509" s="1"/>
     </row>
-    <row r="510" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="510" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A510" s="1" t="s">
         <v>332</v>
       </c>
@@ -32005,7 +32011,7 @@
       </c>
       <c r="T510" s="1"/>
     </row>
-    <row r="511" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="511" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A511" s="1" t="s">
         <v>332</v>
       </c>
@@ -32055,7 +32061,7 @@
       </c>
       <c r="T511" s="1"/>
     </row>
-    <row r="512" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="512" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A512" s="1" t="s">
         <v>332</v>
       </c>
@@ -32105,7 +32111,7 @@
       </c>
       <c r="T512" s="1"/>
     </row>
-    <row r="513" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="513" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A513" s="1" t="s">
         <v>332</v>
       </c>
@@ -32161,7 +32167,7 @@
         <v>1862</v>
       </c>
     </row>
-    <row r="514" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="514" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A514" s="1" t="s">
         <v>332</v>
       </c>
@@ -32217,7 +32223,7 @@
         <v>1862</v>
       </c>
     </row>
-    <row r="515" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="515" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A515" s="1" t="s">
         <v>332</v>
       </c>
@@ -32267,7 +32273,7 @@
       </c>
       <c r="T515" s="1"/>
     </row>
-    <row r="516" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="516" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A516" s="1" t="s">
         <v>332</v>
       </c>
@@ -32323,7 +32329,7 @@
         <v>1862</v>
       </c>
     </row>
-    <row r="517" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="517" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A517" s="1" t="s">
         <v>332</v>
       </c>
@@ -32379,7 +32385,7 @@
         <v>1862</v>
       </c>
     </row>
-    <row r="518" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="518" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A518" s="1" t="s">
         <v>332</v>
       </c>
@@ -32429,7 +32435,7 @@
       </c>
       <c r="T518" s="1"/>
     </row>
-    <row r="519" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="519" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A519" s="1" t="s">
         <v>332</v>
       </c>
@@ -32479,7 +32485,7 @@
       </c>
       <c r="T519" s="1"/>
     </row>
-    <row r="520" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="520" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A520" s="1" t="s">
         <v>332</v>
       </c>
@@ -32529,7 +32535,7 @@
       </c>
       <c r="T520" s="1"/>
     </row>
-    <row r="521" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="521" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A521" s="1" t="s">
         <v>332</v>
       </c>
@@ -32579,7 +32585,7 @@
       </c>
       <c r="T521" s="1"/>
     </row>
-    <row r="522" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="522" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A522" s="1" t="s">
         <v>332</v>
       </c>
@@ -32629,7 +32635,7 @@
       </c>
       <c r="T522" s="1"/>
     </row>
-    <row r="523" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="523" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A523" s="1" t="s">
         <v>332</v>
       </c>
@@ -32685,7 +32691,7 @@
         <v>1862</v>
       </c>
     </row>
-    <row r="524" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="524" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A524" s="1" t="s">
         <v>332</v>
       </c>
@@ -32741,7 +32747,7 @@
         <v>1862</v>
       </c>
     </row>
-    <row r="525" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="525" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A525" s="1" t="s">
         <v>332</v>
       </c>
@@ -32797,7 +32803,7 @@
         <v>1862</v>
       </c>
     </row>
-    <row r="526" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="526" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A526" s="1" t="s">
         <v>332</v>
       </c>
@@ -32853,7 +32859,7 @@
         <v>1862</v>
       </c>
     </row>
-    <row r="527" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="527" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A527" s="1" t="s">
         <v>332</v>
       </c>
@@ -32909,7 +32915,7 @@
         <v>1862</v>
       </c>
     </row>
-    <row r="528" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="528" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A528" s="1" t="s">
         <v>332</v>
       </c>
@@ -32959,7 +32965,7 @@
       </c>
       <c r="T528" s="1"/>
     </row>
-    <row r="529" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="529" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A529" s="1" t="s">
         <v>332</v>
       </c>
@@ -33009,7 +33015,7 @@
       </c>
       <c r="T529" s="1"/>
     </row>
-    <row r="530" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="530" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A530" s="1" t="s">
         <v>332</v>
       </c>
@@ -33059,7 +33065,7 @@
       </c>
       <c r="T530" s="1"/>
     </row>
-    <row r="531" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="531" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A531" s="1" t="s">
         <v>332</v>
       </c>
@@ -33109,7 +33115,7 @@
       </c>
       <c r="T531" s="1"/>
     </row>
-    <row r="532" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="532" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A532" s="1" t="s">
         <v>332</v>
       </c>
@@ -33159,7 +33165,7 @@
       </c>
       <c r="T532" s="1"/>
     </row>
-    <row r="533" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="533" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A533" s="1" t="s">
         <v>332</v>
       </c>
@@ -33215,7 +33221,7 @@
         <v>1862</v>
       </c>
     </row>
-    <row r="534" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="534" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A534" s="1" t="s">
         <v>332</v>
       </c>
@@ -33265,7 +33271,7 @@
       </c>
       <c r="T534" s="1"/>
     </row>
-    <row r="535" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="535" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A535" s="1" t="s">
         <v>332</v>
       </c>
@@ -33321,7 +33327,7 @@
         <v>1862</v>
       </c>
     </row>
-    <row r="536" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="536" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A536" s="1" t="s">
         <v>332</v>
       </c>
@@ -33371,7 +33377,7 @@
       </c>
       <c r="T536" s="1"/>
     </row>
-    <row r="537" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="537" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A537" s="1" t="s">
         <v>332</v>
       </c>
@@ -33421,7 +33427,7 @@
       </c>
       <c r="T537" s="1"/>
     </row>
-    <row r="538" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="538" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A538" s="1" t="s">
         <v>332</v>
       </c>
@@ -33477,7 +33483,7 @@
         <v>1862</v>
       </c>
     </row>
-    <row r="539" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="539" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A539" s="1" t="s">
         <v>332</v>
       </c>
@@ -33533,7 +33539,7 @@
         <v>1862</v>
       </c>
     </row>
-    <row r="540" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="540" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A540" s="1" t="s">
         <v>332</v>
       </c>
@@ -33583,7 +33589,7 @@
       </c>
       <c r="T540" s="1"/>
     </row>
-    <row r="541" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="541" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A541" s="1" t="s">
         <v>332</v>
       </c>
@@ -33633,7 +33639,7 @@
       </c>
       <c r="T541" s="1"/>
     </row>
-    <row r="542" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="542" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A542" s="1" t="s">
         <v>332</v>
       </c>
@@ -33689,7 +33695,7 @@
         <v>1862</v>
       </c>
     </row>
-    <row r="543" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="543" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A543" s="1" t="s">
         <v>332</v>
       </c>
@@ -33739,7 +33745,7 @@
       </c>
       <c r="T543" s="1"/>
     </row>
-    <row r="544" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="544" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A544" s="1" t="s">
         <v>332</v>
       </c>
@@ -33789,7 +33795,7 @@
       </c>
       <c r="T544" s="1"/>
     </row>
-    <row r="545" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="545" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A545" s="1" t="s">
         <v>332</v>
       </c>
@@ -33839,7 +33845,7 @@
       </c>
       <c r="T545" s="1"/>
     </row>
-    <row r="546" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="546" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A546" s="1" t="s">
         <v>332</v>
       </c>
@@ -33889,7 +33895,7 @@
       </c>
       <c r="T546" s="1"/>
     </row>
-    <row r="547" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="547" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A547" s="1" t="s">
         <v>332</v>
       </c>
@@ -33939,7 +33945,7 @@
       </c>
       <c r="T547" s="1"/>
     </row>
-    <row r="548" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="548" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A548" s="1" t="s">
         <v>332</v>
       </c>
@@ -33989,7 +33995,7 @@
       </c>
       <c r="T548" s="1"/>
     </row>
-    <row r="549" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="549" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A549" s="1" t="s">
         <v>332</v>
       </c>
@@ -34039,7 +34045,7 @@
       </c>
       <c r="T549" s="1"/>
     </row>
-    <row r="550" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="550" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A550" s="1" t="s">
         <v>332</v>
       </c>
@@ -34089,7 +34095,7 @@
       </c>
       <c r="T550" s="1"/>
     </row>
-    <row r="551" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="551" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A551" s="1" t="s">
         <v>332</v>
       </c>
@@ -34139,7 +34145,7 @@
       </c>
       <c r="T551" s="1"/>
     </row>
-    <row r="552" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="552" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A552" s="1" t="s">
         <v>332</v>
       </c>
@@ -34189,7 +34195,7 @@
       </c>
       <c r="T552" s="1"/>
     </row>
-    <row r="553" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="553" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A553" s="1" t="s">
         <v>332</v>
       </c>
@@ -34239,7 +34245,7 @@
       </c>
       <c r="T553" s="1"/>
     </row>
-    <row r="554" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="554" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A554" s="1" t="s">
         <v>332</v>
       </c>
@@ -34289,7 +34295,7 @@
       </c>
       <c r="T554" s="1"/>
     </row>
-    <row r="555" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="555" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A555" s="1" t="s">
         <v>332</v>
       </c>
@@ -34339,7 +34345,7 @@
       </c>
       <c r="T555" s="1"/>
     </row>
-    <row r="556" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="556" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A556" s="1" t="s">
         <v>332</v>
       </c>
@@ -34389,7 +34395,7 @@
       </c>
       <c r="T556" s="1"/>
     </row>
-    <row r="557" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="557" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A557" s="1" t="s">
         <v>332</v>
       </c>
@@ -34439,7 +34445,7 @@
       </c>
       <c r="T557" s="1"/>
     </row>
-    <row r="558" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="558" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A558" s="1" t="s">
         <v>332</v>
       </c>
@@ -34489,7 +34495,7 @@
       </c>
       <c r="T558" s="1"/>
     </row>
-    <row r="559" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="559" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A559" s="1" t="s">
         <v>332</v>
       </c>
@@ -34539,7 +34545,7 @@
       </c>
       <c r="T559" s="1"/>
     </row>
-    <row r="560" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="560" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A560" s="1" t="s">
         <v>332</v>
       </c>
@@ -34589,7 +34595,7 @@
       </c>
       <c r="T560" s="1"/>
     </row>
-    <row r="561" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="561" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A561" s="1" t="s">
         <v>332</v>
       </c>
@@ -34645,7 +34651,7 @@
         <v>1862</v>
       </c>
     </row>
-    <row r="562" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="562" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A562" s="1" t="s">
         <v>332</v>
       </c>
@@ -34701,7 +34707,7 @@
         <v>1862</v>
       </c>
     </row>
-    <row r="563" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="563" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A563" s="1" t="s">
         <v>332</v>
       </c>
@@ -34751,7 +34757,7 @@
       </c>
       <c r="T563" s="1"/>
     </row>
-    <row r="564" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="564" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A564" s="1" t="s">
         <v>332</v>
       </c>
@@ -34807,7 +34813,7 @@
         <v>1862</v>
       </c>
     </row>
-    <row r="565" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="565" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A565" s="1" t="s">
         <v>332</v>
       </c>
@@ -34863,7 +34869,7 @@
         <v>1862</v>
       </c>
     </row>
-    <row r="566" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="566" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A566" s="1" t="s">
         <v>332</v>
       </c>
@@ -34913,7 +34919,7 @@
       </c>
       <c r="T566" s="1"/>
     </row>
-    <row r="567" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="567" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A567" s="1" t="s">
         <v>332</v>
       </c>
@@ -34969,7 +34975,7 @@
         <v>1862</v>
       </c>
     </row>
-    <row r="568" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="568" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A568" s="1" t="s">
         <v>332</v>
       </c>
@@ -35025,7 +35031,7 @@
         <v>1862</v>
       </c>
     </row>
-    <row r="569" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="569" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A569" s="1" t="s">
         <v>332</v>
       </c>
@@ -35075,7 +35081,7 @@
       </c>
       <c r="T569" s="1"/>
     </row>
-    <row r="570" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="570" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A570" s="1" t="s">
         <v>332</v>
       </c>
@@ -35131,7 +35137,7 @@
         <v>1862</v>
       </c>
     </row>
-    <row r="571" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="571" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A571" s="1" t="s">
         <v>332</v>
       </c>
@@ -35187,7 +35193,7 @@
         <v>1862</v>
       </c>
     </row>
-    <row r="572" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="572" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A572" s="1" t="s">
         <v>332</v>
       </c>
@@ -35237,7 +35243,7 @@
       </c>
       <c r="T572" s="1"/>
     </row>
-    <row r="573" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="573" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A573" s="1" t="s">
         <v>332</v>
       </c>
@@ -35287,7 +35293,7 @@
       </c>
       <c r="T573" s="1"/>
     </row>
-    <row r="574" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="574" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A574" s="1" t="s">
         <v>332</v>
       </c>
@@ -35337,7 +35343,7 @@
       </c>
       <c r="T574" s="1"/>
     </row>
-    <row r="575" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="575" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A575" s="1" t="s">
         <v>893</v>
       </c>
@@ -35387,7 +35393,7 @@
       </c>
       <c r="T575" s="1"/>
     </row>
-    <row r="576" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="576" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A576" s="1" t="s">
         <v>893</v>
       </c>
@@ -35437,7 +35443,7 @@
       </c>
       <c r="T576" s="1"/>
     </row>
-    <row r="577" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="577" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A577" s="1" t="s">
         <v>893</v>
       </c>
@@ -35487,7 +35493,7 @@
       </c>
       <c r="T577" s="1"/>
     </row>
-    <row r="578" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="578" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A578" s="1" t="s">
         <v>893</v>
       </c>
@@ -35537,7 +35543,7 @@
       </c>
       <c r="T578" s="1"/>
     </row>
-    <row r="579" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="579" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A579" s="1" t="s">
         <v>893</v>
       </c>
@@ -35587,7 +35593,7 @@
       </c>
       <c r="T579" s="1"/>
     </row>
-    <row r="580" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="580" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A580" s="1" t="s">
         <v>893</v>
       </c>
@@ -35637,7 +35643,7 @@
       </c>
       <c r="T580" s="1"/>
     </row>
-    <row r="581" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="581" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A581" s="1" t="s">
         <v>893</v>
       </c>
@@ -35687,7 +35693,7 @@
       </c>
       <c r="T581" s="1"/>
     </row>
-    <row r="582" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="582" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A582" s="1" t="s">
         <v>893</v>
       </c>
@@ -35721,7 +35727,7 @@
       </c>
       <c r="T582" s="1"/>
     </row>
-    <row r="583" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="583" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A583" s="1" t="s">
         <v>893</v>
       </c>
@@ -35755,7 +35761,7 @@
       </c>
       <c r="T583" s="1"/>
     </row>
-    <row r="584" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="584" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A584" s="1" t="s">
         <v>893</v>
       </c>
@@ -35805,7 +35811,7 @@
       </c>
       <c r="T584" s="1"/>
     </row>
-    <row r="585" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="585" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A585" s="1" t="s">
         <v>893</v>
       </c>
@@ -35855,7 +35861,7 @@
       </c>
       <c r="T585" s="1"/>
     </row>
-    <row r="586" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="586" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A586" s="1" t="s">
         <v>893</v>
       </c>
@@ -35905,7 +35911,7 @@
       </c>
       <c r="T586" s="1"/>
     </row>
-    <row r="587" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="587" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A587" s="1" t="s">
         <v>893</v>
       </c>
@@ -35955,7 +35961,7 @@
       </c>
       <c r="T587" s="1"/>
     </row>
-    <row r="588" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="588" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A588" s="1" t="s">
         <v>893</v>
       </c>
@@ -36005,7 +36011,7 @@
       </c>
       <c r="T588" s="1"/>
     </row>
-    <row r="589" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="589" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A589" s="1" t="s">
         <v>893</v>
       </c>
@@ -36055,7 +36061,7 @@
       </c>
       <c r="T589" s="1"/>
     </row>
-    <row r="590" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="590" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A590" s="1" t="s">
         <v>893</v>
       </c>
@@ -36105,7 +36111,7 @@
       </c>
       <c r="T590" s="1"/>
     </row>
-    <row r="591" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="591" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A591" s="1" t="s">
         <v>893</v>
       </c>
@@ -36155,7 +36161,7 @@
       </c>
       <c r="T591" s="1"/>
     </row>
-    <row r="592" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="592" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A592" s="1" t="s">
         <v>893</v>
       </c>
@@ -36205,7 +36211,7 @@
       </c>
       <c r="T592" s="1"/>
     </row>
-    <row r="593" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="593" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A593" s="1" t="s">
         <v>893</v>
       </c>
@@ -36255,7 +36261,7 @@
       </c>
       <c r="T593" s="1"/>
     </row>
-    <row r="594" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="594" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A594" s="1" t="s">
         <v>893</v>
       </c>
@@ -36305,7 +36311,7 @@
       </c>
       <c r="T594" s="1"/>
     </row>
-    <row r="595" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="595" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A595" s="1" t="s">
         <v>893</v>
       </c>
@@ -36355,7 +36361,7 @@
       </c>
       <c r="T595" s="1"/>
     </row>
-    <row r="596" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="596" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A596" s="1" t="s">
         <v>893</v>
       </c>
@@ -36387,7 +36393,7 @@
       </c>
       <c r="T596" s="1"/>
     </row>
-    <row r="597" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="597" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A597" s="1" t="s">
         <v>893</v>
       </c>
@@ -36419,7 +36425,7 @@
       </c>
       <c r="T597" s="1"/>
     </row>
-    <row r="598" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="598" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A598" s="1" t="s">
         <v>893</v>
       </c>
@@ -36451,7 +36457,7 @@
       </c>
       <c r="T598" s="1"/>
     </row>
-    <row r="599" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="599" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A599" s="1" t="s">
         <v>893</v>
       </c>
@@ -36483,7 +36489,7 @@
       </c>
       <c r="T599" s="1"/>
     </row>
-    <row r="600" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="600" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A600" s="1" t="s">
         <v>893</v>
       </c>
@@ -36515,7 +36521,7 @@
       </c>
       <c r="T600" s="1"/>
     </row>
-    <row r="601" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="601" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A601" s="1" t="s">
         <v>893</v>
       </c>
@@ -36547,7 +36553,7 @@
       </c>
       <c r="T601" s="1"/>
     </row>
-    <row r="602" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="602" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A602" s="1" t="s">
         <v>893</v>
       </c>
@@ -36579,7 +36585,7 @@
       </c>
       <c r="T602" s="1"/>
     </row>
-    <row r="603" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="603" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A603" s="1" t="s">
         <v>893</v>
       </c>
@@ -36629,7 +36635,7 @@
       </c>
       <c r="T603" s="1"/>
     </row>
-    <row r="604" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="604" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A604" s="1" t="s">
         <v>893</v>
       </c>
@@ -36679,7 +36685,7 @@
       </c>
       <c r="T604" s="1"/>
     </row>
-    <row r="605" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="605" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A605" s="1" t="s">
         <v>893</v>
       </c>
@@ -36729,7 +36735,7 @@
       </c>
       <c r="T605" s="1"/>
     </row>
-    <row r="606" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="606" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A606" s="1" t="s">
         <v>893</v>
       </c>
@@ -36779,7 +36785,7 @@
       </c>
       <c r="T606" s="1"/>
     </row>
-    <row r="607" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="607" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A607" s="1" t="s">
         <v>893</v>
       </c>
@@ -36831,7 +36837,7 @@
       </c>
       <c r="T607" s="1"/>
     </row>
-    <row r="608" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="608" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A608" s="1" t="s">
         <v>893</v>
       </c>
@@ -36883,7 +36889,7 @@
       </c>
       <c r="T608" s="1"/>
     </row>
-    <row r="609" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="609" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A609" s="1" t="s">
         <v>893</v>
       </c>
@@ -36915,7 +36921,7 @@
       </c>
       <c r="T609" s="1"/>
     </row>
-    <row r="610" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="610" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A610" s="1" t="s">
         <v>893</v>
       </c>
@@ -36947,7 +36953,7 @@
       </c>
       <c r="T610" s="1"/>
     </row>
-    <row r="611" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="611" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A611" s="1" t="s">
         <v>893</v>
       </c>
@@ -36999,7 +37005,7 @@
       </c>
       <c r="T611" s="1"/>
     </row>
-    <row r="612" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="612" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A612" s="1" t="s">
         <v>893</v>
       </c>
@@ -37051,7 +37057,7 @@
       </c>
       <c r="T612" s="1"/>
     </row>
-    <row r="613" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="613" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A613" s="1" t="s">
         <v>893</v>
       </c>
@@ -37103,7 +37109,7 @@
       </c>
       <c r="T613" s="1"/>
     </row>
-    <row r="614" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="614" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A614" s="1" t="s">
         <v>893</v>
       </c>
@@ -37151,7 +37157,7 @@
       </c>
       <c r="T614" s="1"/>
     </row>
-    <row r="615" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="615" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A615" s="1" t="s">
         <v>893</v>
       </c>
@@ -37183,7 +37189,7 @@
       </c>
       <c r="T615" s="1"/>
     </row>
-    <row r="616" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="616" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A616" s="1" t="s">
         <v>893</v>
       </c>
@@ -37235,7 +37241,7 @@
       </c>
       <c r="T616" s="1"/>
     </row>
-    <row r="617" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="617" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A617" s="1" t="s">
         <v>893</v>
       </c>
@@ -37287,7 +37293,7 @@
       </c>
       <c r="T617" s="1"/>
     </row>
-    <row r="618" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="618" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A618" s="1" t="s">
         <v>893</v>
       </c>
@@ -37319,7 +37325,7 @@
       </c>
       <c r="T618" s="1"/>
     </row>
-    <row r="619" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="619" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A619" s="1" t="s">
         <v>893</v>
       </c>
@@ -37351,7 +37357,7 @@
       </c>
       <c r="T619" s="1"/>
     </row>
-    <row r="620" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="620" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A620" s="1" t="s">
         <v>893</v>
       </c>
@@ -37383,7 +37389,7 @@
       </c>
       <c r="T620" s="1"/>
     </row>
-    <row r="621" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="621" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A621" s="1" t="s">
         <v>893</v>
       </c>
@@ -37415,7 +37421,7 @@
       </c>
       <c r="T621" s="1"/>
     </row>
-    <row r="622" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="622" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A622" s="1" t="s">
         <v>893</v>
       </c>
@@ -37467,7 +37473,7 @@
       </c>
       <c r="T622" s="1"/>
     </row>
-    <row r="623" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="623" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A623" s="1" t="s">
         <v>893</v>
       </c>
@@ -37519,7 +37525,7 @@
       </c>
       <c r="T623" s="1"/>
     </row>
-    <row r="624" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="624" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A624" s="1" t="s">
         <v>893</v>
       </c>
@@ -37571,7 +37577,7 @@
       </c>
       <c r="T624" s="1"/>
     </row>
-    <row r="625" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="625" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A625" s="1" t="s">
         <v>893</v>
       </c>
@@ -37623,7 +37629,7 @@
       </c>
       <c r="T625" s="1"/>
     </row>
-    <row r="626" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="626" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A626" s="1" t="s">
         <v>893</v>
       </c>
@@ -37673,7 +37679,7 @@
       </c>
       <c r="T626" s="1"/>
     </row>
-    <row r="627" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="627" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A627" s="1" t="s">
         <v>893</v>
       </c>
@@ -37723,7 +37729,7 @@
       </c>
       <c r="T627" s="1"/>
     </row>
-    <row r="628" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="628" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A628" s="1" t="s">
         <v>893</v>
       </c>
@@ -37773,7 +37779,7 @@
       </c>
       <c r="T628" s="1"/>
     </row>
-    <row r="629" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="629" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A629" s="1" t="s">
         <v>893</v>
       </c>
@@ -37827,7 +37833,7 @@
       </c>
       <c r="T629" s="1"/>
     </row>
-    <row r="630" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="630" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A630" s="1" t="s">
         <v>893</v>
       </c>
@@ -37881,7 +37887,7 @@
       </c>
       <c r="T630" s="1"/>
     </row>
-    <row r="631" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="631" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A631" s="1" t="s">
         <v>893</v>
       </c>
@@ -37935,7 +37941,7 @@
       </c>
       <c r="T631" s="1"/>
     </row>
-    <row r="632" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="632" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A632" s="1" t="s">
         <v>893</v>
       </c>
@@ -37989,7 +37995,7 @@
       </c>
       <c r="T632" s="1"/>
     </row>
-    <row r="633" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="633" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A633" s="1" t="s">
         <v>893</v>
       </c>
@@ -38043,7 +38049,7 @@
       </c>
       <c r="T633" s="1"/>
     </row>
-    <row r="634" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="634" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A634" s="1" t="s">
         <v>893</v>
       </c>
@@ -38079,7 +38085,7 @@
       </c>
       <c r="T634" s="1"/>
     </row>
-    <row r="635" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="635" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A635" s="1" t="s">
         <v>893</v>
       </c>
@@ -38133,7 +38139,7 @@
       </c>
       <c r="T635" s="1"/>
     </row>
-    <row r="636" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="636" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A636" s="1" t="s">
         <v>893</v>
       </c>
@@ -38187,7 +38193,7 @@
       </c>
       <c r="T636" s="1"/>
     </row>
-    <row r="637" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="637" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A637" s="1" t="s">
         <v>982</v>
       </c>
@@ -38237,7 +38243,7 @@
       </c>
       <c r="T637" s="1"/>
     </row>
-    <row r="638" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="638" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A638" s="1" t="s">
         <v>982</v>
       </c>
@@ -38287,7 +38293,7 @@
       </c>
       <c r="T638" s="1"/>
     </row>
-    <row r="639" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="639" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A639" s="1" t="s">
         <v>982</v>
       </c>
@@ -38337,7 +38343,7 @@
       </c>
       <c r="T639" s="1"/>
     </row>
-    <row r="640" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="640" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A640" s="1" t="s">
         <v>982</v>
       </c>
@@ -38387,7 +38393,7 @@
       </c>
       <c r="T640" s="1"/>
     </row>
-    <row r="641" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="641" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A641" s="1" t="s">
         <v>982</v>
       </c>
@@ -38419,7 +38425,7 @@
       </c>
       <c r="T641" s="1"/>
     </row>
-    <row r="642" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="642" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A642" s="1" t="s">
         <v>982</v>
       </c>
@@ -38469,7 +38475,7 @@
       </c>
       <c r="T642" s="1"/>
     </row>
-    <row r="643" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="643" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A643" s="1" t="s">
         <v>982</v>
       </c>
@@ -38519,7 +38525,7 @@
       </c>
       <c r="T643" s="1"/>
     </row>
-    <row r="644" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="644" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A644" s="1" t="s">
         <v>982</v>
       </c>
@@ -38569,7 +38575,7 @@
       </c>
       <c r="T644" s="1"/>
     </row>
-    <row r="645" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="645" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A645" s="1" t="s">
         <v>982</v>
       </c>
@@ -38619,7 +38625,7 @@
       </c>
       <c r="T645" s="1"/>
     </row>
-    <row r="646" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="646" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A646" s="1" t="s">
         <v>982</v>
       </c>
@@ -38669,7 +38675,7 @@
       </c>
       <c r="T646" s="1"/>
     </row>
-    <row r="647" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="647" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A647" s="1" t="s">
         <v>982</v>
       </c>
@@ -38719,7 +38725,7 @@
       </c>
       <c r="T647" s="1"/>
     </row>
-    <row r="648" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="648" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A648" s="1" t="s">
         <v>982</v>
       </c>
@@ -38769,7 +38775,7 @@
       </c>
       <c r="T648" s="1"/>
     </row>
-    <row r="649" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="649" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A649" s="1" t="s">
         <v>982</v>
       </c>
@@ -38819,7 +38825,7 @@
       </c>
       <c r="T649" s="1"/>
     </row>
-    <row r="650" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="650" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A650" s="1" t="s">
         <v>982</v>
       </c>
@@ -38869,7 +38875,7 @@
       </c>
       <c r="T650" s="1"/>
     </row>
-    <row r="651" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="651" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A651" s="1" t="s">
         <v>1012</v>
       </c>
@@ -38919,7 +38925,7 @@
       </c>
       <c r="T651" s="1"/>
     </row>
-    <row r="652" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="652" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A652" s="1" t="s">
         <v>1012</v>
       </c>
@@ -38973,7 +38979,7 @@
       </c>
       <c r="T652" s="1"/>
     </row>
-    <row r="653" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="653" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A653" s="1" t="s">
         <v>1012</v>
       </c>
@@ -39027,7 +39033,7 @@
       </c>
       <c r="T653" s="1"/>
     </row>
-    <row r="654" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="654" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A654" s="1" t="s">
         <v>1012</v>
       </c>
@@ -39081,7 +39087,7 @@
       </c>
       <c r="T654" s="1"/>
     </row>
-    <row r="655" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="655" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A655" s="1" t="s">
         <v>1012</v>
       </c>
@@ -39131,7 +39137,7 @@
       </c>
       <c r="T655" s="1"/>
     </row>
-    <row r="656" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="656" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A656" s="1" t="s">
         <v>1012</v>
       </c>
@@ -39165,7 +39171,7 @@
       </c>
       <c r="T656" s="1"/>
     </row>
-    <row r="657" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="657" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A657" s="1" t="s">
         <v>1012</v>
       </c>
@@ -39215,7 +39221,7 @@
       </c>
       <c r="T657" s="1"/>
     </row>
-    <row r="658" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="658" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A658" s="1" t="s">
         <v>1012</v>
       </c>
@@ -39265,7 +39271,7 @@
       </c>
       <c r="T658" s="1"/>
     </row>
-    <row r="659" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="659" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A659" s="1" t="s">
         <v>1012</v>
       </c>
@@ -39315,7 +39321,7 @@
       </c>
       <c r="T659" s="1"/>
     </row>
-    <row r="660" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="660" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A660" s="1" t="s">
         <v>1012</v>
       </c>
@@ -39365,7 +39371,7 @@
       </c>
       <c r="T660" s="1"/>
     </row>
-    <row r="661" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="661" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A661" s="1" t="s">
         <v>1012</v>
       </c>
@@ -39415,7 +39421,7 @@
       </c>
       <c r="T661" s="1"/>
     </row>
-    <row r="662" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="662" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A662" s="1" t="s">
         <v>1012</v>
       </c>
@@ -39465,7 +39471,7 @@
       </c>
       <c r="T662" s="1"/>
     </row>
-    <row r="663" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="663" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A663" s="1" t="s">
         <v>1012</v>
       </c>
@@ -39515,7 +39521,7 @@
       </c>
       <c r="T663" s="1"/>
     </row>
-    <row r="664" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="664" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A664" s="1" t="s">
         <v>1012</v>
       </c>
@@ -39565,7 +39571,7 @@
       </c>
       <c r="T664" s="1"/>
     </row>
-    <row r="665" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="665" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A665" s="1" t="s">
         <v>1012</v>
       </c>
@@ -39615,7 +39621,7 @@
       </c>
       <c r="T665" s="1"/>
     </row>
-    <row r="666" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="666" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A666" s="1" t="s">
         <v>1012</v>
       </c>
@@ -39665,7 +39671,7 @@
       </c>
       <c r="T666" s="1"/>
     </row>
-    <row r="667" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="667" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A667" s="1" t="s">
         <v>1012</v>
       </c>
@@ -39715,7 +39721,7 @@
       </c>
       <c r="T667" s="1"/>
     </row>
-    <row r="668" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="668" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A668" s="1" t="s">
         <v>1012</v>
       </c>
@@ -39765,7 +39771,7 @@
       </c>
       <c r="T668" s="1"/>
     </row>
-    <row r="669" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="669" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A669" s="1" t="s">
         <v>1012</v>
       </c>
@@ -39815,7 +39821,7 @@
       </c>
       <c r="T669" s="1"/>
     </row>
-    <row r="670" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="670" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A670" s="1" t="s">
         <v>1012</v>
       </c>
@@ -39865,7 +39871,7 @@
       </c>
       <c r="T670" s="1"/>
     </row>
-    <row r="671" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="671" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A671" s="1" t="s">
         <v>1012</v>
       </c>
@@ -39921,7 +39927,7 @@
         <v>1863</v>
       </c>
     </row>
-    <row r="672" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="672" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A672" s="1" t="s">
         <v>1012</v>
       </c>
@@ -39977,7 +39983,7 @@
         <v>1863</v>
       </c>
     </row>
-    <row r="673" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="673" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A673" s="1" t="s">
         <v>1012</v>
       </c>
@@ -40027,7 +40033,7 @@
       </c>
       <c r="T673" s="1"/>
     </row>
-    <row r="674" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="674" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A674" s="1" t="s">
         <v>1012</v>
       </c>
@@ -40077,7 +40083,7 @@
       </c>
       <c r="T674" s="1"/>
     </row>
-    <row r="675" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="675" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A675" s="1" t="s">
         <v>1012</v>
       </c>
@@ -40127,7 +40133,7 @@
       </c>
       <c r="T675" s="1"/>
     </row>
-    <row r="676" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="676" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A676" s="1" t="s">
         <v>1012</v>
       </c>
@@ -40163,7 +40169,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="677" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="677" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A677" s="1" t="s">
         <v>1012</v>
       </c>
@@ -40199,7 +40205,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="678" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="678" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A678" s="1" t="s">
         <v>1012</v>
       </c>
@@ -40235,7 +40241,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="679" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="679" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A679" s="1" t="s">
         <v>1012</v>
       </c>
@@ -40285,7 +40291,7 @@
       </c>
       <c r="T679" s="1"/>
     </row>
-    <row r="680" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="680" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A680" s="1" t="s">
         <v>1012</v>
       </c>
@@ -40337,7 +40343,7 @@
       </c>
       <c r="T680" s="1"/>
     </row>
-    <row r="681" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="681" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A681" s="1" t="s">
         <v>1012</v>
       </c>
@@ -40389,7 +40395,7 @@
       </c>
       <c r="T681" s="1"/>
     </row>
-    <row r="682" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="682" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A682" s="1" t="s">
         <v>1012</v>
       </c>
@@ -40439,7 +40445,7 @@
       </c>
       <c r="T682" s="1"/>
     </row>
-    <row r="683" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="683" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A683" s="1" t="s">
         <v>1012</v>
       </c>
@@ -40489,7 +40495,7 @@
       </c>
       <c r="T683" s="1"/>
     </row>
-    <row r="684" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="684" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A684" s="1" t="s">
         <v>1012</v>
       </c>
@@ -40539,7 +40545,7 @@
       </c>
       <c r="T684" s="1"/>
     </row>
-    <row r="685" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="685" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A685" s="1" t="s">
         <v>1012</v>
       </c>
@@ -40589,7 +40595,7 @@
       </c>
       <c r="T685" s="1"/>
     </row>
-    <row r="686" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="686" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A686" s="1" t="s">
         <v>1012</v>
       </c>
@@ -40639,7 +40645,7 @@
       </c>
       <c r="T686" s="1"/>
     </row>
-    <row r="687" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="687" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A687" s="1" t="s">
         <v>1012</v>
       </c>
@@ -40691,7 +40697,7 @@
       </c>
       <c r="T687" s="1"/>
     </row>
-    <row r="688" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="688" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A688" s="1" t="s">
         <v>1012</v>
       </c>
@@ -40743,7 +40749,7 @@
       </c>
       <c r="T688" s="1"/>
     </row>
-    <row r="689" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="689" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A689" s="1" t="s">
         <v>1012</v>
       </c>
@@ -40777,7 +40783,7 @@
       </c>
       <c r="T689" s="1"/>
     </row>
-    <row r="690" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="690" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A690" s="1" t="s">
         <v>1012</v>
       </c>
@@ -40827,7 +40833,7 @@
       </c>
       <c r="T690" s="1"/>
     </row>
-    <row r="691" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="691" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A691" s="1" t="s">
         <v>1012</v>
       </c>
@@ -40877,7 +40883,7 @@
       </c>
       <c r="T691" s="1"/>
     </row>
-    <row r="692" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="692" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A692" s="1" t="s">
         <v>1012</v>
       </c>
@@ -40927,7 +40933,7 @@
       </c>
       <c r="T692" s="1"/>
     </row>
-    <row r="693" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="693" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A693" s="1" t="s">
         <v>1012</v>
       </c>
@@ -40983,7 +40989,7 @@
         <v>1863</v>
       </c>
     </row>
-    <row r="694" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="694" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A694" s="1" t="s">
         <v>1012</v>
       </c>
@@ -41033,7 +41039,7 @@
       </c>
       <c r="T694" s="1"/>
     </row>
-    <row r="695" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="695" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A695" s="1" t="s">
         <v>1012</v>
       </c>
@@ -41083,7 +41089,7 @@
       </c>
       <c r="T695" s="1"/>
     </row>
-    <row r="696" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="696" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A696" s="1" t="s">
         <v>1012</v>
       </c>
@@ -41117,7 +41123,7 @@
       </c>
       <c r="T696" s="1"/>
     </row>
-    <row r="697" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="697" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A697" s="1" t="s">
         <v>1012</v>
       </c>
@@ -41167,7 +41173,7 @@
       </c>
       <c r="T697" s="1"/>
     </row>
-    <row r="698" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="698" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A698" s="1" t="s">
         <v>1012</v>
       </c>
@@ -41221,7 +41227,7 @@
       </c>
       <c r="T698" s="1"/>
     </row>
-    <row r="699" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="699" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A699" s="1" t="s">
         <v>1012</v>
       </c>
@@ -41275,7 +41281,7 @@
       </c>
       <c r="T699" s="1"/>
     </row>
-    <row r="700" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="700" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A700" s="1" t="s">
         <v>1012</v>
       </c>
@@ -41325,7 +41331,7 @@
       </c>
       <c r="T700" s="1"/>
     </row>
-    <row r="701" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="701" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A701" s="1" t="s">
         <v>1012</v>
       </c>
@@ -41375,7 +41381,7 @@
       </c>
       <c r="T701" s="1"/>
     </row>
-    <row r="702" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="702" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A702" s="1" t="s">
         <v>1012</v>
       </c>
@@ -41425,7 +41431,7 @@
       </c>
       <c r="T702" s="1"/>
     </row>
-    <row r="703" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="703" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A703" s="1" t="s">
         <v>1012</v>
       </c>
@@ -41479,7 +41485,7 @@
       </c>
       <c r="T703" s="1"/>
     </row>
-    <row r="704" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="704" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A704" s="1" t="s">
         <v>1012</v>
       </c>
@@ -41533,7 +41539,7 @@
       </c>
       <c r="T704" s="1"/>
     </row>
-    <row r="705" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="705" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A705" s="1" t="s">
         <v>1012</v>
       </c>
@@ -41587,7 +41593,7 @@
       </c>
       <c r="T705" s="1"/>
     </row>
-    <row r="706" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="706" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A706" s="1" t="s">
         <v>1012</v>
       </c>
@@ -41637,7 +41643,7 @@
       </c>
       <c r="T706" s="1"/>
     </row>
-    <row r="707" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="707" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A707" s="1" t="s">
         <v>1012</v>
       </c>
@@ -41687,7 +41693,7 @@
       </c>
       <c r="T707" s="1"/>
     </row>
-    <row r="708" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="708" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A708" s="1" t="s">
         <v>1012</v>
       </c>
@@ -41737,7 +41743,7 @@
       </c>
       <c r="T708" s="1"/>
     </row>
-    <row r="709" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="709" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A709" s="1" t="s">
         <v>1012</v>
       </c>
@@ -41791,7 +41797,7 @@
       </c>
       <c r="T709" s="1"/>
     </row>
-    <row r="710" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="710" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A710" s="1" t="s">
         <v>1012</v>
       </c>
@@ -41845,7 +41851,7 @@
       </c>
       <c r="T710" s="1"/>
     </row>
-    <row r="711" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="711" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A711" s="1" t="s">
         <v>1012</v>
       </c>
@@ -41895,7 +41901,7 @@
       </c>
       <c r="T711" s="1"/>
     </row>
-    <row r="712" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="712" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A712" s="1" t="s">
         <v>1012</v>
       </c>
@@ -41929,7 +41935,7 @@
       </c>
       <c r="T712" s="1"/>
     </row>
-    <row r="713" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="713" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A713" s="1" t="s">
         <v>1012</v>
       </c>
@@ -41981,7 +41987,7 @@
       </c>
       <c r="T713" s="1"/>
     </row>
-    <row r="714" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="714" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A714" s="1" t="s">
         <v>1012</v>
       </c>
@@ -42033,7 +42039,7 @@
       </c>
       <c r="T714" s="1"/>
     </row>
-    <row r="715" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="715" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A715" s="1" t="s">
         <v>1012</v>
       </c>
@@ -42083,7 +42089,7 @@
       </c>
       <c r="T715" s="1"/>
     </row>
-    <row r="716" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="716" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A716" s="1" t="s">
         <v>1012</v>
       </c>
@@ -42133,7 +42139,7 @@
       </c>
       <c r="T716" s="1"/>
     </row>
-    <row r="717" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="717" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A717" s="1" t="s">
         <v>1012</v>
       </c>
@@ -42183,7 +42189,7 @@
       </c>
       <c r="T717" s="1"/>
     </row>
-    <row r="718" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="718" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A718" s="1" t="s">
         <v>1012</v>
       </c>
@@ -42237,7 +42243,7 @@
       </c>
       <c r="T718" s="1"/>
     </row>
-    <row r="719" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="719" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A719" s="1" t="s">
         <v>1012</v>
       </c>
@@ -42287,7 +42293,7 @@
       </c>
       <c r="T719" s="1"/>
     </row>
-    <row r="720" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="720" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A720" s="1" t="s">
         <v>1012</v>
       </c>
@@ -42337,7 +42343,7 @@
       </c>
       <c r="T720" s="1"/>
     </row>
-    <row r="721" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="721" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A721" s="1" t="s">
         <v>1012</v>
       </c>
@@ -42389,7 +42395,7 @@
       </c>
       <c r="T721" s="1"/>
     </row>
-    <row r="722" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="722" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A722" s="1" t="s">
         <v>1012</v>
       </c>
@@ -42441,7 +42447,7 @@
       </c>
       <c r="T722" s="1"/>
     </row>
-    <row r="723" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="723" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A723" s="1" t="s">
         <v>1012</v>
       </c>
@@ -42493,7 +42499,7 @@
       </c>
       <c r="T723" s="1"/>
     </row>
-    <row r="724" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="724" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A724" s="1" t="s">
         <v>1012</v>
       </c>
@@ -42543,7 +42549,7 @@
       </c>
       <c r="T724" s="1"/>
     </row>
-    <row r="725" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="725" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A725" s="1" t="s">
         <v>1012</v>
       </c>
@@ -42593,7 +42599,7 @@
       </c>
       <c r="T725" s="1"/>
     </row>
-    <row r="726" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="726" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A726" s="1" t="s">
         <v>1012</v>
       </c>
@@ -42647,7 +42653,7 @@
       </c>
       <c r="T726" s="1"/>
     </row>
-    <row r="727" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="727" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A727" s="1" t="s">
         <v>1012</v>
       </c>
@@ -42701,7 +42707,7 @@
       </c>
       <c r="T727" s="1"/>
     </row>
-    <row r="728" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="728" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A728" s="1" t="s">
         <v>1012</v>
       </c>
@@ -42755,7 +42761,7 @@
       </c>
       <c r="T728" s="1"/>
     </row>
-    <row r="729" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="729" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A729" s="1" t="s">
         <v>1012</v>
       </c>
@@ -42809,7 +42815,7 @@
       </c>
       <c r="T729" s="1"/>
     </row>
-    <row r="730" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="730" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A730" s="1" t="s">
         <v>1012</v>
       </c>
@@ -42863,7 +42869,7 @@
       </c>
       <c r="T730" s="1"/>
     </row>
-    <row r="731" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="731" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A731" s="1" t="s">
         <v>1012</v>
       </c>
@@ -42917,7 +42923,7 @@
       </c>
       <c r="T731" s="1"/>
     </row>
-    <row r="732" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="732" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A732" s="1" t="s">
         <v>1012</v>
       </c>
@@ -42971,7 +42977,7 @@
       </c>
       <c r="T732" s="1"/>
     </row>
-    <row r="733" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="733" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A733" s="1" t="s">
         <v>1012</v>
       </c>
@@ -43021,7 +43027,7 @@
       </c>
       <c r="T733" s="1"/>
     </row>
-    <row r="734" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="734" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A734" s="1" t="s">
         <v>1012</v>
       </c>
@@ -43071,7 +43077,7 @@
       </c>
       <c r="T734" s="1"/>
     </row>
-    <row r="735" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="735" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A735" s="1" t="s">
         <v>1012</v>
       </c>
@@ -43121,7 +43127,7 @@
       </c>
       <c r="T735" s="1"/>
     </row>
-    <row r="736" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="736" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A736" s="1" t="s">
         <v>1012</v>
       </c>
@@ -43173,7 +43179,7 @@
       </c>
       <c r="T736" s="1"/>
     </row>
-    <row r="737" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="737" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A737" s="1" t="s">
         <v>1012</v>
       </c>
@@ -43225,7 +43231,7 @@
       </c>
       <c r="T737" s="1"/>
     </row>
-    <row r="738" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="738" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A738" s="1" t="s">
         <v>1012</v>
       </c>
@@ -43277,7 +43283,7 @@
       </c>
       <c r="T738" s="1"/>
     </row>
-    <row r="739" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="739" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A739" s="1" t="s">
         <v>1012</v>
       </c>
@@ -43327,7 +43333,7 @@
       </c>
       <c r="T739" s="1"/>
     </row>
-    <row r="740" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="740" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A740" s="1" t="s">
         <v>1012</v>
       </c>
@@ -43377,7 +43383,7 @@
       </c>
       <c r="T740" s="1"/>
     </row>
-    <row r="741" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="741" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A741" s="1" t="s">
         <v>1012</v>
       </c>
@@ -43427,7 +43433,7 @@
       </c>
       <c r="T741" s="1"/>
     </row>
-    <row r="742" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="742" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A742" s="1" t="s">
         <v>1012</v>
       </c>
@@ -43477,7 +43483,7 @@
       </c>
       <c r="T742" s="1"/>
     </row>
-    <row r="743" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="743" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A743" s="1" t="s">
         <v>1012</v>
       </c>
@@ -43527,7 +43533,7 @@
       </c>
       <c r="T743" s="1"/>
     </row>
-    <row r="744" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="744" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A744" s="1" t="s">
         <v>1012</v>
       </c>
@@ -43579,7 +43585,7 @@
       </c>
       <c r="T744" s="1"/>
     </row>
-    <row r="745" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="745" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A745" s="1" t="s">
         <v>1012</v>
       </c>
@@ -43629,7 +43635,7 @@
       </c>
       <c r="T745" s="1"/>
     </row>
-    <row r="746" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="746" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A746" s="1" t="s">
         <v>1012</v>
       </c>
@@ -43679,7 +43685,7 @@
       </c>
       <c r="T746" s="1"/>
     </row>
-    <row r="747" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="747" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A747" s="1" t="s">
         <v>1012</v>
       </c>
@@ -43731,7 +43737,7 @@
       </c>
       <c r="T747" s="1"/>
     </row>
-    <row r="748" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="748" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A748" s="1" t="s">
         <v>1012</v>
       </c>
@@ -43783,7 +43789,7 @@
       </c>
       <c r="T748" s="1"/>
     </row>
-    <row r="749" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="749" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A749" s="1" t="s">
         <v>1012</v>
       </c>
@@ -43835,7 +43841,7 @@
       </c>
       <c r="T749" s="1"/>
     </row>
-    <row r="750" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="750" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A750" s="1" t="s">
         <v>1012</v>
       </c>
@@ -43887,7 +43893,7 @@
       </c>
       <c r="T750" s="1"/>
     </row>
-    <row r="751" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="751" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A751" s="1" t="s">
         <v>1012</v>
       </c>
@@ -43939,7 +43945,7 @@
       </c>
       <c r="T751" s="1"/>
     </row>
-    <row r="752" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="752" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A752" s="1" t="s">
         <v>1012</v>
       </c>
@@ -43989,7 +43995,7 @@
       </c>
       <c r="T752" s="1"/>
     </row>
-    <row r="753" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="753" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A753" s="1" t="s">
         <v>1012</v>
       </c>
@@ -44039,7 +44045,7 @@
       </c>
       <c r="T753" s="1"/>
     </row>
-    <row r="754" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="754" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A754" s="1" t="s">
         <v>1012</v>
       </c>
@@ -44093,7 +44099,7 @@
       </c>
       <c r="T754" s="1"/>
     </row>
-    <row r="755" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="755" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A755" s="1" t="s">
         <v>1012</v>
       </c>
@@ -44147,7 +44153,7 @@
       </c>
       <c r="T755" s="1"/>
     </row>
-    <row r="756" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="756" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A756" s="1" t="s">
         <v>1012</v>
       </c>
@@ -44199,7 +44205,7 @@
       </c>
       <c r="T756" s="1"/>
     </row>
-    <row r="757" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="757" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A757" s="1" t="s">
         <v>1012</v>
       </c>
@@ -44249,7 +44255,7 @@
       </c>
       <c r="T757" s="1"/>
     </row>
-    <row r="758" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="758" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A758" s="1" t="s">
         <v>1012</v>
       </c>
@@ -44299,7 +44305,7 @@
       </c>
       <c r="T758" s="1"/>
     </row>
-    <row r="759" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="759" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A759" s="1" t="s">
         <v>1012</v>
       </c>
@@ -44349,7 +44355,7 @@
       </c>
       <c r="T759" s="1"/>
     </row>
-    <row r="760" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="760" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A760" s="1" t="s">
         <v>1012</v>
       </c>
@@ -44405,7 +44411,7 @@
         <v>1863</v>
       </c>
     </row>
-    <row r="761" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="761" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A761" s="1" t="s">
         <v>1012</v>
       </c>
@@ -44455,7 +44461,7 @@
       </c>
       <c r="T761" s="1"/>
     </row>
-    <row r="762" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="762" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A762" s="1" t="s">
         <v>1012</v>
       </c>
@@ -44505,7 +44511,7 @@
       </c>
       <c r="T762" s="1"/>
     </row>
-    <row r="763" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="763" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A763" s="1" t="s">
         <v>1012</v>
       </c>
@@ -44557,7 +44563,7 @@
       </c>
       <c r="T763" s="1"/>
     </row>
-    <row r="764" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="764" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A764" s="1" t="s">
         <v>1012</v>
       </c>
@@ -44607,7 +44613,7 @@
       </c>
       <c r="T764" s="1"/>
     </row>
-    <row r="765" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="765" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A765" s="1" t="s">
         <v>1012</v>
       </c>
@@ -44657,7 +44663,7 @@
       </c>
       <c r="T765" s="1"/>
     </row>
-    <row r="766" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="766" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A766" s="1" t="s">
         <v>1012</v>
       </c>
@@ -44707,7 +44713,7 @@
       </c>
       <c r="T766" s="1"/>
     </row>
-    <row r="767" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="767" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A767" s="1" t="s">
         <v>1012</v>
       </c>
@@ -44741,7 +44747,7 @@
       </c>
       <c r="T767" s="1"/>
     </row>
-    <row r="768" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="768" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A768" s="1" t="s">
         <v>1012</v>
       </c>
@@ -44791,7 +44797,7 @@
       </c>
       <c r="T768" s="1"/>
     </row>
-    <row r="769" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="769" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A769" s="1" t="s">
         <v>1012</v>
       </c>
@@ -44841,7 +44847,7 @@
       </c>
       <c r="T769" s="1"/>
     </row>
-    <row r="770" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="770" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A770" s="1" t="s">
         <v>1012</v>
       </c>
@@ -44877,7 +44883,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="771" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="771" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A771" s="1" t="s">
         <v>1012</v>
       </c>
@@ -44913,7 +44919,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="772" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="772" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A772" s="1" t="s">
         <v>1012</v>
       </c>
@@ -44963,7 +44969,7 @@
       </c>
       <c r="T772" s="1"/>
     </row>
-    <row r="773" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="773" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A773" s="1" t="s">
         <v>1012</v>
       </c>
@@ -45015,7 +45021,7 @@
       </c>
       <c r="T773" s="1"/>
     </row>
-    <row r="774" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="774" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A774" s="1" t="s">
         <v>1012</v>
       </c>
@@ -45065,7 +45071,7 @@
       </c>
       <c r="T774" s="1"/>
     </row>
-    <row r="775" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="775" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A775" s="1" t="s">
         <v>1012</v>
       </c>
@@ -45115,7 +45121,7 @@
       </c>
       <c r="T775" s="1"/>
     </row>
-    <row r="776" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="776" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A776" s="1" t="s">
         <v>1012</v>
       </c>
@@ -45165,7 +45171,7 @@
       </c>
       <c r="T776" s="1"/>
     </row>
-    <row r="777" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="777" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A777" s="1" t="s">
         <v>1012</v>
       </c>
@@ -45215,7 +45221,7 @@
       </c>
       <c r="T777" s="1"/>
     </row>
-    <row r="778" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="778" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A778" s="1" t="s">
         <v>1012</v>
       </c>
@@ -45265,7 +45271,7 @@
       </c>
       <c r="T778" s="1"/>
     </row>
-    <row r="779" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="779" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A779" s="1" t="s">
         <v>1012</v>
       </c>
@@ -45299,7 +45305,7 @@
       </c>
       <c r="T779" s="1"/>
     </row>
-    <row r="780" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="780" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A780" s="1" t="s">
         <v>1012</v>
       </c>
@@ -45349,7 +45355,7 @@
       </c>
       <c r="T780" s="1"/>
     </row>
-    <row r="781" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="781" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A781" s="1" t="s">
         <v>1012</v>
       </c>
@@ -45403,7 +45409,7 @@
       </c>
       <c r="T781" s="1"/>
     </row>
-    <row r="782" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="782" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A782" s="1" t="s">
         <v>1012</v>
       </c>
@@ -45457,7 +45463,7 @@
       </c>
       <c r="T782" s="1"/>
     </row>
-    <row r="783" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="783" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A783" s="1" t="s">
         <v>1012</v>
       </c>
@@ -45491,7 +45497,7 @@
       </c>
       <c r="T783" s="1"/>
     </row>
-    <row r="784" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="784" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A784" s="1" t="s">
         <v>1012</v>
       </c>
@@ -45541,7 +45547,7 @@
       </c>
       <c r="T784" s="1"/>
     </row>
-    <row r="785" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="785" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A785" s="1" t="s">
         <v>1012</v>
       </c>
@@ -45591,7 +45597,7 @@
       </c>
       <c r="T785" s="1"/>
     </row>
-    <row r="786" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="786" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A786" s="1" t="s">
         <v>1012</v>
       </c>
@@ -45645,7 +45651,7 @@
       </c>
       <c r="T786" s="1"/>
     </row>
-    <row r="787" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="787" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A787" s="1" t="s">
         <v>1012</v>
       </c>
@@ -45695,7 +45701,7 @@
       </c>
       <c r="T787" s="1"/>
     </row>
-    <row r="788" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="788" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A788" s="1" t="s">
         <v>1012</v>
       </c>
@@ -45745,7 +45751,7 @@
       </c>
       <c r="T788" s="1"/>
     </row>
-    <row r="789" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="789" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A789" s="1" t="s">
         <v>1012</v>
       </c>
@@ -45797,7 +45803,7 @@
       </c>
       <c r="T789" s="1"/>
     </row>
-    <row r="790" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="790" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A790" s="1" t="s">
         <v>1012</v>
       </c>
@@ -45847,7 +45853,7 @@
       </c>
       <c r="T790" s="1"/>
     </row>
-    <row r="791" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="791" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A791" s="1" t="s">
         <v>1012</v>
       </c>
@@ -45897,7 +45903,7 @@
       </c>
       <c r="T791" s="1"/>
     </row>
-    <row r="792" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="792" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A792" s="1" t="s">
         <v>1012</v>
       </c>
@@ -45951,7 +45957,7 @@
       </c>
       <c r="T792" s="1"/>
     </row>
-    <row r="793" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="793" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A793" s="1" t="s">
         <v>1012</v>
       </c>
@@ -46001,7 +46007,7 @@
       </c>
       <c r="T793" s="1"/>
     </row>
-    <row r="794" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="794" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A794" s="1" t="s">
         <v>1012</v>
       </c>
@@ -46053,7 +46059,7 @@
       </c>
       <c r="T794" s="1"/>
     </row>
-    <row r="795" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="795" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A795" s="1" t="s">
         <v>1012</v>
       </c>
@@ -46103,7 +46109,7 @@
       </c>
       <c r="T795" s="1"/>
     </row>
-    <row r="796" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="796" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A796" s="1" t="s">
         <v>1012</v>
       </c>
@@ -46153,7 +46159,7 @@
       </c>
       <c r="T796" s="1"/>
     </row>
-    <row r="797" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="797" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A797" s="1" t="s">
         <v>1012</v>
       </c>
@@ -46205,7 +46211,7 @@
       </c>
       <c r="T797" s="1"/>
     </row>
-    <row r="798" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="798" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A798" s="1" t="s">
         <v>1012</v>
       </c>
@@ -46255,7 +46261,7 @@
       </c>
       <c r="T798" s="1"/>
     </row>
-    <row r="799" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="799" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A799" s="1" t="s">
         <v>1012</v>
       </c>
@@ -46305,7 +46311,7 @@
       </c>
       <c r="T799" s="1"/>
     </row>
-    <row r="800" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="800" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A800" s="1" t="s">
         <v>1012</v>
       </c>
@@ -46339,7 +46345,7 @@
       </c>
       <c r="T800" s="1"/>
     </row>
-    <row r="801" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="801" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A801" s="1" t="s">
         <v>1012</v>
       </c>
@@ -46391,7 +46397,7 @@
       </c>
       <c r="T801" s="1"/>
     </row>
-    <row r="802" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="802" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A802" s="1" t="s">
         <v>1012</v>
       </c>
@@ -46443,7 +46449,7 @@
       </c>
       <c r="T802" s="1"/>
     </row>
-    <row r="803" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="803" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A803" s="1" t="s">
         <v>1012</v>
       </c>
@@ -46497,7 +46503,7 @@
       </c>
       <c r="T803" s="1"/>
     </row>
-    <row r="804" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="804" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A804" s="1" t="s">
         <v>1012</v>
       </c>
@@ -46549,7 +46555,7 @@
       </c>
       <c r="T804" s="1"/>
     </row>
-    <row r="805" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="805" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A805" s="1" t="s">
         <v>1012</v>
       </c>
@@ -46601,7 +46607,7 @@
       </c>
       <c r="T805" s="1"/>
     </row>
-    <row r="806" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="806" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A806" s="1" t="s">
         <v>1012</v>
       </c>
@@ -46653,7 +46659,7 @@
       </c>
       <c r="T806" s="1"/>
     </row>
-    <row r="807" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="807" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A807" s="1" t="s">
         <v>1012</v>
       </c>
@@ -46703,7 +46709,7 @@
       </c>
       <c r="T807" s="1"/>
     </row>
-    <row r="808" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="808" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A808" s="1" t="s">
         <v>1012</v>
       </c>
@@ -46753,7 +46759,7 @@
       </c>
       <c r="T808" s="1"/>
     </row>
-    <row r="809" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="809" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A809" s="1" t="s">
         <v>1012</v>
       </c>
@@ -46805,7 +46811,7 @@
       </c>
       <c r="T809" s="1"/>
     </row>
-    <row r="810" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="810" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A810" s="1" t="s">
         <v>1012</v>
       </c>
@@ -46859,7 +46865,7 @@
       </c>
       <c r="T810" s="1"/>
     </row>
-    <row r="811" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="811" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A811" s="1" t="s">
         <v>1012</v>
       </c>
@@ -46911,7 +46917,7 @@
       </c>
       <c r="T811" s="1"/>
     </row>
-    <row r="812" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="812" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A812" s="1" t="s">
         <v>1012</v>
       </c>
@@ -46963,7 +46969,7 @@
       </c>
       <c r="T812" s="1"/>
     </row>
-    <row r="813" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="813" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A813" s="1" t="s">
         <v>1012</v>
       </c>
@@ -47015,7 +47021,7 @@
       </c>
       <c r="T813" s="1"/>
     </row>
-    <row r="814" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="814" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A814" s="1" t="s">
         <v>1012</v>
       </c>
@@ -47067,7 +47073,7 @@
       </c>
       <c r="T814" s="1"/>
     </row>
-    <row r="815" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="815" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A815" s="1" t="s">
         <v>1012</v>
       </c>
@@ -47119,7 +47125,7 @@
       </c>
       <c r="T815" s="1"/>
     </row>
-    <row r="816" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="816" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A816" s="1" t="s">
         <v>1012</v>
       </c>
@@ -47169,7 +47175,7 @@
       </c>
       <c r="T816" s="1"/>
     </row>
-    <row r="817" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="817" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A817" s="1" t="s">
         <v>1012</v>
       </c>
@@ -47223,7 +47229,7 @@
       </c>
       <c r="T817" s="1"/>
     </row>
-    <row r="818" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="818" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A818" s="1" t="s">
         <v>1012</v>
       </c>
@@ -47275,7 +47281,7 @@
       </c>
       <c r="T818" s="1"/>
     </row>
-    <row r="819" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="819" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A819" s="1" t="s">
         <v>1012</v>
       </c>
@@ -47327,7 +47333,7 @@
       </c>
       <c r="T819" s="1"/>
     </row>
-    <row r="820" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="820" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A820" s="1" t="s">
         <v>1012</v>
       </c>
@@ -47379,7 +47385,7 @@
       </c>
       <c r="T820" s="1"/>
     </row>
-    <row r="821" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="821" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A821" s="1" t="s">
         <v>1012</v>
       </c>
@@ -47431,7 +47437,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="822" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="822" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A822" s="1" t="s">
         <v>1012</v>
       </c>
@@ -47485,7 +47491,7 @@
       </c>
       <c r="T822" s="1"/>
     </row>
-    <row r="823" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="823" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A823" s="1" t="s">
         <v>1012</v>
       </c>
@@ -47537,7 +47543,7 @@
       </c>
       <c r="T823" s="1"/>
     </row>
-    <row r="824" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="824" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A824" s="1" t="s">
         <v>1012</v>
       </c>
@@ -47591,7 +47597,7 @@
       </c>
       <c r="T824" s="1"/>
     </row>
-    <row r="825" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="825" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A825" s="1" t="s">
         <v>1012</v>
       </c>
@@ -47645,7 +47651,7 @@
       </c>
       <c r="T825" s="1"/>
     </row>
-    <row r="826" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="826" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A826" s="1" t="s">
         <v>1012</v>
       </c>
@@ -47699,7 +47705,7 @@
       </c>
       <c r="T826" s="1"/>
     </row>
-    <row r="827" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="827" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A827" s="1" t="s">
         <v>1012</v>
       </c>
@@ -47751,7 +47757,7 @@
       </c>
       <c r="T827" s="1"/>
     </row>
-    <row r="828" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="828" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A828" s="1" t="s">
         <v>1012</v>
       </c>
@@ -47803,7 +47809,7 @@
       </c>
       <c r="T828" s="1"/>
     </row>
-    <row r="829" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="829" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A829" s="1" t="s">
         <v>1012</v>
       </c>
@@ -47855,7 +47861,7 @@
       </c>
       <c r="T829" s="1"/>
     </row>
-    <row r="830" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="830" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A830" s="1" t="s">
         <v>1012</v>
       </c>
@@ -47907,7 +47913,7 @@
       </c>
       <c r="T830" s="1"/>
     </row>
-    <row r="831" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="831" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A831" s="1" t="s">
         <v>1012</v>
       </c>
@@ -47959,7 +47965,7 @@
       </c>
       <c r="T831" s="1"/>
     </row>
-    <row r="832" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="832" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A832" s="1" t="s">
         <v>1012</v>
       </c>
@@ -48011,7 +48017,7 @@
       </c>
       <c r="T832" s="1"/>
     </row>
-    <row r="833" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="833" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A833" s="1" t="s">
         <v>1012</v>
       </c>
@@ -48063,7 +48069,7 @@
       </c>
       <c r="T833" s="1"/>
     </row>
-    <row r="834" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="834" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A834" s="1" t="s">
         <v>1012</v>
       </c>
@@ -48117,7 +48123,7 @@
       </c>
       <c r="T834" s="1"/>
     </row>
-    <row r="835" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="835" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A835" s="1" t="s">
         <v>1012</v>
       </c>
@@ -48169,7 +48175,7 @@
       </c>
       <c r="T835" s="1"/>
     </row>
-    <row r="836" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="836" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A836" s="1" t="s">
         <v>1012</v>
       </c>
@@ -48221,7 +48227,7 @@
       </c>
       <c r="T836" s="1"/>
     </row>
-    <row r="837" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="837" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A837" s="1" t="s">
         <v>1012</v>
       </c>
@@ -48273,7 +48279,7 @@
       </c>
       <c r="T837" s="1"/>
     </row>
-    <row r="838" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="838" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A838" s="1" t="s">
         <v>1012</v>
       </c>
@@ -48325,7 +48331,7 @@
       </c>
       <c r="T838" s="1"/>
     </row>
-    <row r="839" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="839" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A839" s="1" t="s">
         <v>1012</v>
       </c>
@@ -48379,7 +48385,7 @@
       </c>
       <c r="T839" s="1"/>
     </row>
-    <row r="840" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="840" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A840" s="1" t="s">
         <v>1012</v>
       </c>
@@ -48431,7 +48437,7 @@
       </c>
       <c r="T840" s="1"/>
     </row>
-    <row r="841" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="841" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A841" s="1" t="s">
         <v>1012</v>
       </c>
@@ -48481,7 +48487,7 @@
       </c>
       <c r="T841" s="1"/>
     </row>
-    <row r="842" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="842" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A842" s="1" t="s">
         <v>1012</v>
       </c>
@@ -48537,7 +48543,7 @@
         <v>1863</v>
       </c>
     </row>
-    <row r="843" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="843" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A843" s="1" t="s">
         <v>1012</v>
       </c>
@@ -48593,7 +48599,7 @@
         <v>1863</v>
       </c>
     </row>
-    <row r="844" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="844" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A844" s="1" t="s">
         <v>1012</v>
       </c>
@@ -48647,7 +48653,7 @@
       </c>
       <c r="T844" s="1"/>
     </row>
-    <row r="845" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="845" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A845" s="1" t="s">
         <v>1012</v>
       </c>
@@ -48699,7 +48705,7 @@
       </c>
       <c r="T845" s="1"/>
     </row>
-    <row r="846" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="846" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A846" s="1" t="s">
         <v>1012</v>
       </c>
@@ -48751,7 +48757,7 @@
       </c>
       <c r="T846" s="1"/>
     </row>
-    <row r="847" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="847" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A847" s="1" t="s">
         <v>1012</v>
       </c>
@@ -48803,7 +48809,7 @@
       </c>
       <c r="T847" s="1"/>
     </row>
-    <row r="848" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="848" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A848" s="1" t="s">
         <v>1012</v>
       </c>
@@ -48853,7 +48859,7 @@
       </c>
       <c r="T848" s="1"/>
     </row>
-    <row r="849" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="849" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A849" s="1" t="s">
         <v>1012</v>
       </c>
@@ -48909,7 +48915,7 @@
         <v>1863</v>
       </c>
     </row>
-    <row r="850" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="850" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A850" s="1" t="s">
         <v>1012</v>
       </c>
@@ -48963,7 +48969,7 @@
       </c>
       <c r="T850" s="1"/>
     </row>
-    <row r="851" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="851" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A851" s="1" t="s">
         <v>1012</v>
       </c>
@@ -49013,7 +49019,7 @@
       </c>
       <c r="T851" s="1"/>
     </row>
-    <row r="852" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="852" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A852" s="1" t="s">
         <v>1012</v>
       </c>
@@ -49065,7 +49071,7 @@
       </c>
       <c r="T852" s="1"/>
     </row>
-    <row r="853" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="853" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A853" s="1" t="s">
         <v>1012</v>
       </c>
@@ -49117,7 +49123,7 @@
       </c>
       <c r="T853" s="1"/>
     </row>
-    <row r="854" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="854" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A854" s="1" t="s">
         <v>1012</v>
       </c>
@@ -49171,7 +49177,7 @@
       </c>
       <c r="T854" s="1"/>
     </row>
-    <row r="855" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="855" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A855" s="1" t="s">
         <v>1012</v>
       </c>
@@ -49223,7 +49229,7 @@
       </c>
       <c r="T855" s="1"/>
     </row>
-    <row r="856" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="856" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A856" s="1" t="s">
         <v>1012</v>
       </c>
@@ -49275,7 +49281,7 @@
       </c>
       <c r="T856" s="1"/>
     </row>
-    <row r="857" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="857" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A857" s="1" t="s">
         <v>1012</v>
       </c>
@@ -49331,7 +49337,7 @@
         <v>1863</v>
       </c>
     </row>
-    <row r="858" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="858" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A858" s="1" t="s">
         <v>1012</v>
       </c>
@@ -49385,7 +49391,7 @@
       </c>
       <c r="T858" s="1"/>
     </row>
-    <row r="859" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="859" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A859" s="1" t="s">
         <v>1012</v>
       </c>
@@ -49439,7 +49445,7 @@
       </c>
       <c r="T859" s="1"/>
     </row>
-    <row r="860" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="860" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A860" s="1" t="s">
         <v>1012</v>
       </c>
@@ -49491,7 +49497,7 @@
       </c>
       <c r="T860" s="1"/>
     </row>
-    <row r="861" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="861" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A861" s="1" t="s">
         <v>1012</v>
       </c>
@@ -49541,7 +49547,7 @@
       </c>
       <c r="T861" s="1"/>
     </row>
-    <row r="862" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="862" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A862" s="1" t="s">
         <v>1012</v>
       </c>
@@ -49591,7 +49597,7 @@
       </c>
       <c r="T862" s="1"/>
     </row>
-    <row r="863" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="863" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A863" s="1" t="s">
         <v>1012</v>
       </c>
@@ -49643,7 +49649,7 @@
       </c>
       <c r="T863" s="1"/>
     </row>
-    <row r="864" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="864" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A864" s="1" t="s">
         <v>1012</v>
       </c>
@@ -49695,7 +49701,7 @@
       </c>
       <c r="T864" s="1"/>
     </row>
-    <row r="865" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="865" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A865" s="1" t="s">
         <v>1012</v>
       </c>
@@ -49747,7 +49753,7 @@
       </c>
       <c r="T865" s="1"/>
     </row>
-    <row r="866" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="866" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A866" s="1" t="s">
         <v>1012</v>
       </c>
@@ -49801,7 +49807,7 @@
       </c>
       <c r="T866" s="1"/>
     </row>
-    <row r="867" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="867" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A867" s="1" t="s">
         <v>1012</v>
       </c>
@@ -49855,7 +49861,7 @@
       </c>
       <c r="T867" s="1"/>
     </row>
-    <row r="868" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="868" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A868" s="1" t="s">
         <v>1012</v>
       </c>
@@ -49909,7 +49915,7 @@
       </c>
       <c r="T868" s="1"/>
     </row>
-    <row r="869" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="869" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A869" s="1" t="s">
         <v>1012</v>
       </c>
@@ -49963,7 +49969,7 @@
       </c>
       <c r="T869" s="1"/>
     </row>
-    <row r="870" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="870" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A870" s="1" t="s">
         <v>1012</v>
       </c>
@@ -50015,7 +50021,7 @@
       </c>
       <c r="T870" s="1"/>
     </row>
-    <row r="871" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="871" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A871" s="1" t="s">
         <v>1012</v>
       </c>
@@ -50067,7 +50073,7 @@
       </c>
       <c r="T871" s="1"/>
     </row>
-    <row r="872" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="872" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A872" s="1" t="s">
         <v>1012</v>
       </c>
@@ -50119,7 +50125,7 @@
       </c>
       <c r="T872" s="1"/>
     </row>
-    <row r="873" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="873" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A873" s="1" t="s">
         <v>1012</v>
       </c>
@@ -50171,7 +50177,7 @@
       </c>
       <c r="T873" s="1"/>
     </row>
-    <row r="874" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="874" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A874" s="1" t="s">
         <v>1012</v>
       </c>
@@ -50221,7 +50227,7 @@
       </c>
       <c r="T874" s="1"/>
     </row>
-    <row r="875" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="875" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A875" s="1" t="s">
         <v>1012</v>
       </c>
@@ -50271,7 +50277,7 @@
       </c>
       <c r="T875" s="1"/>
     </row>
-    <row r="876" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="876" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A876" s="1" t="s">
         <v>1012</v>
       </c>
@@ -50323,7 +50329,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="877" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="877" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A877" s="1" t="s">
         <v>1012</v>
       </c>
@@ -50375,7 +50381,7 @@
       </c>
       <c r="T877" s="1"/>
     </row>
-    <row r="878" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="878" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A878" s="1" t="s">
         <v>1012</v>
       </c>
@@ -50429,7 +50435,7 @@
       </c>
       <c r="T878" s="1"/>
     </row>
-    <row r="879" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="879" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A879" s="1" t="s">
         <v>1012</v>
       </c>
@@ -50481,7 +50487,7 @@
       </c>
       <c r="T879" s="1"/>
     </row>
-    <row r="880" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="880" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A880" s="1" t="s">
         <v>1012</v>
       </c>
@@ -50533,7 +50539,7 @@
       </c>
       <c r="T880" s="1"/>
     </row>
-    <row r="881" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="881" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A881" s="1" t="s">
         <v>1012</v>
       </c>
@@ -50585,7 +50591,7 @@
       </c>
       <c r="T881" s="1"/>
     </row>
-    <row r="882" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="882" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A882" s="1" t="s">
         <v>1012</v>
       </c>
@@ -50637,7 +50643,7 @@
       </c>
       <c r="T882" s="1"/>
     </row>
-    <row r="883" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="883" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A883" s="1" t="s">
         <v>1012</v>
       </c>
@@ -50691,7 +50697,7 @@
       </c>
       <c r="T883" s="1"/>
     </row>
-    <row r="884" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="884" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A884" s="1" t="s">
         <v>1012</v>
       </c>
@@ -50743,7 +50749,7 @@
       </c>
       <c r="T884" s="1"/>
     </row>
-    <row r="885" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="885" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A885" s="1" t="s">
         <v>1012</v>
       </c>
@@ -50797,7 +50803,7 @@
       </c>
       <c r="T885" s="1"/>
     </row>
-    <row r="886" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="886" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A886" s="1" t="s">
         <v>1012</v>
       </c>
@@ -50851,7 +50857,7 @@
       </c>
       <c r="T886" s="1"/>
     </row>
-    <row r="887" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="887" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A887" s="1" t="s">
         <v>1012</v>
       </c>
@@ -50903,7 +50909,7 @@
       </c>
       <c r="T887" s="1"/>
     </row>
-    <row r="888" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="888" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A888" s="1" t="s">
         <v>1012</v>
       </c>
@@ -50955,7 +50961,7 @@
       </c>
       <c r="T888" s="1"/>
     </row>
-    <row r="889" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="889" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A889" s="1" t="s">
         <v>1012</v>
       </c>
@@ -51009,7 +51015,7 @@
       </c>
       <c r="T889" s="1"/>
     </row>
-    <row r="890" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="890" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A890" s="1" t="s">
         <v>1012</v>
       </c>
@@ -51063,7 +51069,7 @@
       </c>
       <c r="T890" s="1"/>
     </row>
-    <row r="891" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="891" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A891" s="1" t="s">
         <v>1012</v>
       </c>
@@ -51117,7 +51123,7 @@
       </c>
       <c r="T891" s="1"/>
     </row>
-    <row r="892" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="892" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A892" s="1" t="s">
         <v>1012</v>
       </c>
@@ -51169,7 +51175,7 @@
       </c>
       <c r="T892" s="1"/>
     </row>
-    <row r="893" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="893" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A893" s="1" t="s">
         <v>1012</v>
       </c>
@@ -51219,7 +51225,7 @@
       </c>
       <c r="T893" s="1"/>
     </row>
-    <row r="894" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="894" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A894" s="1" t="s">
         <v>1012</v>
       </c>
@@ -51269,7 +51275,7 @@
       </c>
       <c r="T894" s="1"/>
     </row>
-    <row r="895" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="895" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A895" s="1" t="s">
         <v>1012</v>
       </c>
@@ -51321,7 +51327,7 @@
       </c>
       <c r="T895" s="1"/>
     </row>
-    <row r="896" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="896" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A896" s="1" t="s">
         <v>1012</v>
       </c>
@@ -51373,7 +51379,7 @@
       </c>
       <c r="T896" s="1"/>
     </row>
-    <row r="897" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="897" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A897" s="1" t="s">
         <v>1012</v>
       </c>
@@ -51425,7 +51431,7 @@
       </c>
       <c r="T897" s="1"/>
     </row>
-    <row r="898" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="898" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A898" s="1" t="s">
         <v>1012</v>
       </c>
@@ -51479,7 +51485,7 @@
       </c>
       <c r="T898" s="1"/>
     </row>
-    <row r="899" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="899" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A899" s="1" t="s">
         <v>1012</v>
       </c>
@@ -51533,7 +51539,7 @@
       </c>
       <c r="T899" s="1"/>
     </row>
-    <row r="900" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="900" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A900" s="1" t="s">
         <v>1012</v>
       </c>
@@ -51585,7 +51591,7 @@
       </c>
       <c r="T900" s="1"/>
     </row>
-    <row r="901" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="901" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A901" s="1" t="s">
         <v>1012</v>
       </c>
@@ -51637,7 +51643,7 @@
       </c>
       <c r="T901" s="1"/>
     </row>
-    <row r="902" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="902" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A902" s="1" t="s">
         <v>1012</v>
       </c>
@@ -51689,7 +51695,7 @@
       </c>
       <c r="T902" s="1"/>
     </row>
-    <row r="903" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="903" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A903" s="1" t="s">
         <v>1012</v>
       </c>
@@ -51741,7 +51747,7 @@
       </c>
       <c r="T903" s="1"/>
     </row>
-    <row r="904" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="904" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A904" s="1" t="s">
         <v>1012</v>
       </c>
@@ -51793,7 +51799,7 @@
       </c>
       <c r="T904" s="1"/>
     </row>
-    <row r="905" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="905" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A905" s="1" t="s">
         <v>1012</v>
       </c>
@@ -51843,7 +51849,7 @@
       </c>
       <c r="T905" s="1"/>
     </row>
-    <row r="906" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="906" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A906" s="1" t="s">
         <v>1012</v>
       </c>
@@ -51893,7 +51899,7 @@
       </c>
       <c r="T906" s="1"/>
     </row>
-    <row r="907" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="907" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A907" s="1" t="s">
         <v>1012</v>
       </c>
@@ -51945,7 +51951,7 @@
       </c>
       <c r="T907" s="1"/>
     </row>
-    <row r="908" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="908" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A908" s="1" t="s">
         <v>1012</v>
       </c>
@@ -51997,7 +52003,7 @@
       </c>
       <c r="T908" s="1"/>
     </row>
-    <row r="909" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="909" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A909" s="1" t="s">
         <v>1012</v>
       </c>
@@ -52049,7 +52055,7 @@
       </c>
       <c r="T909" s="1"/>
     </row>
-    <row r="910" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="910" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A910" s="1" t="s">
         <v>1012</v>
       </c>
@@ -52101,7 +52107,7 @@
       </c>
       <c r="T910" s="1"/>
     </row>
-    <row r="911" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="911" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A911" s="1" t="s">
         <v>1012</v>
       </c>
@@ -52153,7 +52159,7 @@
       </c>
       <c r="T911" s="1"/>
     </row>
-    <row r="912" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="912" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A912" s="1" t="s">
         <v>1012</v>
       </c>
@@ -52205,7 +52211,7 @@
       </c>
       <c r="T912" s="1"/>
     </row>
-    <row r="913" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="913" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A913" s="1" t="s">
         <v>1012</v>
       </c>
@@ -52259,7 +52265,7 @@
       </c>
       <c r="T913" s="1"/>
     </row>
-    <row r="914" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="914" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A914" s="1" t="s">
         <v>1012</v>
       </c>
@@ -52311,7 +52317,7 @@
       </c>
       <c r="T914" s="1"/>
     </row>
-    <row r="915" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="915" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A915" s="1" t="s">
         <v>1012</v>
       </c>
@@ -52361,7 +52367,7 @@
       </c>
       <c r="T915" s="1"/>
     </row>
-    <row r="916" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="916" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A916" s="1" t="s">
         <v>1012</v>
       </c>
@@ -52411,7 +52417,7 @@
       </c>
       <c r="T916" s="1"/>
     </row>
-    <row r="917" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="917" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A917" s="1" t="s">
         <v>1012</v>
       </c>
@@ -52463,7 +52469,7 @@
       </c>
       <c r="T917" s="1"/>
     </row>
-    <row r="918" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="918" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A918" s="1" t="s">
         <v>1012</v>
       </c>
@@ -52513,7 +52519,7 @@
       </c>
       <c r="T918" s="1"/>
     </row>
-    <row r="919" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="919" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A919" s="1" t="s">
         <v>1012</v>
       </c>
@@ -52565,7 +52571,7 @@
       </c>
       <c r="T919" s="1"/>
     </row>
-    <row r="920" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="920" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A920" s="1" t="s">
         <v>1012</v>
       </c>
@@ -52617,7 +52623,7 @@
       </c>
       <c r="T920" s="1"/>
     </row>
-    <row r="921" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="921" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A921" s="1" t="s">
         <v>1012</v>
       </c>
@@ -52669,7 +52675,7 @@
       </c>
       <c r="T921" s="1"/>
     </row>
-    <row r="922" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="922" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A922" s="1" t="s">
         <v>1012</v>
       </c>
@@ -52721,7 +52727,7 @@
       </c>
       <c r="T922" s="1"/>
     </row>
-    <row r="923" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="923" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A923" s="1" t="s">
         <v>1012</v>
       </c>
@@ -52771,7 +52777,7 @@
       </c>
       <c r="T923" s="1"/>
     </row>
-    <row r="924" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="924" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A924" s="1" t="s">
         <v>1012</v>
       </c>
@@ -52821,7 +52827,7 @@
       </c>
       <c r="T924" s="1"/>
     </row>
-    <row r="925" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="925" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A925" s="1" t="s">
         <v>1012</v>
       </c>
@@ -52871,7 +52877,7 @@
       </c>
       <c r="T925" s="1"/>
     </row>
-    <row r="926" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="926" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A926" s="1" t="s">
         <v>1012</v>
       </c>
@@ -52921,7 +52927,7 @@
       </c>
       <c r="T926" s="1"/>
     </row>
-    <row r="927" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="927" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A927" s="1" t="s">
         <v>906</v>
       </c>
@@ -52971,7 +52977,7 @@
       </c>
       <c r="T927" s="1"/>
     </row>
-    <row r="928" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="928" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A928" s="1" t="s">
         <v>906</v>
       </c>
@@ -53003,7 +53009,7 @@
       </c>
       <c r="T928" s="1"/>
     </row>
-    <row r="929" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="929" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A929" s="1" t="s">
         <v>906</v>
       </c>
@@ -53035,7 +53041,7 @@
       </c>
       <c r="T929" s="1"/>
     </row>
-    <row r="930" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="930" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A930" s="1" t="s">
         <v>906</v>
       </c>
@@ -53067,7 +53073,7 @@
       </c>
       <c r="T930" s="1"/>
     </row>
-    <row r="931" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="931" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A931" s="1" t="s">
         <v>906</v>
       </c>
@@ -53119,7 +53125,7 @@
       </c>
       <c r="T931" s="1"/>
     </row>
-    <row r="932" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="932" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A932" s="1" t="s">
         <v>906</v>
       </c>
@@ -53171,7 +53177,7 @@
       </c>
       <c r="T932" s="1"/>
     </row>
-    <row r="933" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="933" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A933" s="1" t="s">
         <v>906</v>
       </c>
@@ -53223,7 +53229,7 @@
       </c>
       <c r="T933" s="1"/>
     </row>
-    <row r="934" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="934" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A934" s="1" t="s">
         <v>906</v>
       </c>
@@ -53273,7 +53279,7 @@
       </c>
       <c r="T934" s="1"/>
     </row>
-    <row r="935" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="935" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A935" s="1" t="s">
         <v>906</v>
       </c>
@@ -53323,7 +53329,7 @@
       </c>
       <c r="T935" s="1"/>
     </row>
-    <row r="936" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="936" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A936" s="1" t="s">
         <v>906</v>
       </c>
@@ -53373,7 +53379,7 @@
       </c>
       <c r="T936" s="1"/>
     </row>
-    <row r="937" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="937" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A937" s="1" t="s">
         <v>906</v>
       </c>
@@ -53423,7 +53429,7 @@
       </c>
       <c r="T937" s="1"/>
     </row>
-    <row r="938" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="938" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A938" s="1" t="s">
         <v>906</v>
       </c>
@@ -53473,7 +53479,7 @@
       </c>
       <c r="T938" s="1"/>
     </row>
-    <row r="939" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="939" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A939" s="1" t="s">
         <v>906</v>
       </c>
@@ -53523,7 +53529,7 @@
       </c>
       <c r="T939" s="1"/>
     </row>
-    <row r="940" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="940" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A940" s="1" t="s">
         <v>906</v>
       </c>
@@ -53573,7 +53579,7 @@
       </c>
       <c r="T940" s="1"/>
     </row>
-    <row r="941" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="941" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A941" s="1" t="s">
         <v>906</v>
       </c>
@@ -53623,7 +53629,7 @@
       </c>
       <c r="T941" s="1"/>
     </row>
-    <row r="942" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="942" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A942" s="1" t="s">
         <v>906</v>
       </c>
@@ -53673,7 +53679,7 @@
       </c>
       <c r="T942" s="1"/>
     </row>
-    <row r="943" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="943" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A943" s="1" t="s">
         <v>906</v>
       </c>
@@ -53723,7 +53729,7 @@
       </c>
       <c r="T943" s="1"/>
     </row>
-    <row r="944" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="944" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A944" s="1" t="s">
         <v>906</v>
       </c>
@@ -53773,7 +53779,7 @@
       </c>
       <c r="T944" s="1"/>
     </row>
-    <row r="945" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="945" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A945" s="1" t="s">
         <v>906</v>
       </c>
@@ -53823,7 +53829,7 @@
       </c>
       <c r="T945" s="1"/>
     </row>
-    <row r="946" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="946" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A946" s="1" t="s">
         <v>906</v>
       </c>
@@ -53877,7 +53883,7 @@
       </c>
       <c r="T946" s="1"/>
     </row>
-    <row r="947" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="947" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A947" s="1" t="s">
         <v>906</v>
       </c>
@@ -53927,7 +53933,7 @@
       </c>
       <c r="T947" s="1"/>
     </row>
-    <row r="948" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="948" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A948" s="1" t="s">
         <v>906</v>
       </c>
@@ -53977,7 +53983,7 @@
       </c>
       <c r="T948" s="1"/>
     </row>
-    <row r="949" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="949" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A949" s="1" t="s">
         <v>906</v>
       </c>
@@ -54027,7 +54033,7 @@
       </c>
       <c r="T949" s="1"/>
     </row>
-    <row r="950" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="950" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A950" s="1" t="s">
         <v>906</v>
       </c>
@@ -54077,7 +54083,7 @@
       </c>
       <c r="T950" s="1"/>
     </row>
-    <row r="951" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="951" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A951" s="1" t="s">
         <v>906</v>
       </c>
@@ -54127,7 +54133,7 @@
       </c>
       <c r="T951" s="1"/>
     </row>
-    <row r="952" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="952" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A952" s="1" t="s">
         <v>906</v>
       </c>
@@ -54181,7 +54187,7 @@
       </c>
       <c r="T952" s="1"/>
     </row>
-    <row r="953" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="953" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A953" s="1" t="s">
         <v>906</v>
       </c>
@@ -54231,7 +54237,7 @@
       </c>
       <c r="T953" s="1"/>
     </row>
-    <row r="954" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="954" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A954" s="1" t="s">
         <v>906</v>
       </c>
@@ -54281,7 +54287,7 @@
       </c>
       <c r="T954" s="1"/>
     </row>
-    <row r="955" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="955" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A955" s="1" t="s">
         <v>906</v>
       </c>
@@ -54331,7 +54337,7 @@
       </c>
       <c r="T955" s="1"/>
     </row>
-    <row r="956" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="956" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A956" s="1" t="s">
         <v>906</v>
       </c>
@@ -54381,7 +54387,7 @@
       </c>
       <c r="T956" s="1"/>
     </row>
-    <row r="957" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="957" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A957" s="1" t="s">
         <v>906</v>
       </c>
@@ -54431,7 +54437,7 @@
       </c>
       <c r="T957" s="1"/>
     </row>
-    <row r="958" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="958" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A958" s="1" t="s">
         <v>906</v>
       </c>
@@ -54485,7 +54491,7 @@
       </c>
       <c r="T958" s="1"/>
     </row>
-    <row r="959" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="959" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A959" s="1" t="s">
         <v>906</v>
       </c>
@@ -54535,7 +54541,7 @@
       </c>
       <c r="T959" s="1"/>
     </row>
-    <row r="960" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="960" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A960" s="1" t="s">
         <v>906</v>
       </c>
@@ -54585,7 +54591,7 @@
       </c>
       <c r="T960" s="1"/>
     </row>
-    <row r="961" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="961" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A961" s="1" t="s">
         <v>906</v>
       </c>
@@ -54635,7 +54641,7 @@
       </c>
       <c r="T961" s="1"/>
     </row>
-    <row r="962" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="962" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A962" s="1" t="s">
         <v>906</v>
       </c>
@@ -54685,7 +54691,7 @@
       </c>
       <c r="T962" s="1"/>
     </row>
-    <row r="963" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="963" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A963" s="1" t="s">
         <v>906</v>
       </c>
@@ -54735,7 +54741,7 @@
       </c>
       <c r="T963" s="1"/>
     </row>
-    <row r="964" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="964" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A964" s="1" t="s">
         <v>906</v>
       </c>
@@ -54789,7 +54795,7 @@
       </c>
       <c r="T964" s="1"/>
     </row>
-    <row r="965" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="965" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A965" s="1" t="s">
         <v>906</v>
       </c>
@@ -54843,7 +54849,7 @@
       </c>
       <c r="T965" s="1"/>
     </row>
-    <row r="966" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="966" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A966" s="1" t="s">
         <v>906</v>
       </c>
@@ -54893,7 +54899,7 @@
       </c>
       <c r="T966" s="1"/>
     </row>
-    <row r="967" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="967" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A967" s="1" t="s">
         <v>906</v>
       </c>
@@ -54943,7 +54949,7 @@
       </c>
       <c r="T967" s="1"/>
     </row>
-    <row r="968" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="968" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A968" s="1" t="s">
         <v>906</v>
       </c>
@@ -54993,7 +54999,7 @@
       </c>
       <c r="T968" s="1"/>
     </row>
-    <row r="969" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="969" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A969" s="1" t="s">
         <v>906</v>
       </c>
@@ -55047,7 +55053,7 @@
       </c>
       <c r="T969" s="1"/>
     </row>
-    <row r="970" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="970" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A970" s="1" t="s">
         <v>906</v>
       </c>
@@ -55097,7 +55103,7 @@
       </c>
       <c r="T970" s="1"/>
     </row>
-    <row r="971" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="971" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A971" s="1" t="s">
         <v>906</v>
       </c>
@@ -55147,7 +55153,7 @@
       </c>
       <c r="T971" s="1"/>
     </row>
-    <row r="972" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="972" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A972" s="1" t="s">
         <v>906</v>
       </c>
@@ -55197,7 +55203,7 @@
       </c>
       <c r="T972" s="1"/>
     </row>
-    <row r="973" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="973" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A973" s="1" t="s">
         <v>906</v>
       </c>
@@ -55247,7 +55253,7 @@
       </c>
       <c r="T973" s="1"/>
     </row>
-    <row r="974" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="974" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A974" s="1" t="s">
         <v>906</v>
       </c>
@@ -55297,7 +55303,7 @@
       </c>
       <c r="T974" s="1"/>
     </row>
-    <row r="975" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="975" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A975" s="1" t="s">
         <v>1733</v>
       </c>
@@ -55349,7 +55355,7 @@
       </c>
       <c r="T975" s="1"/>
     </row>
-    <row r="976" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="976" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A976" s="1" t="s">
         <v>1733</v>
       </c>
@@ -55401,7 +55407,7 @@
       </c>
       <c r="T976" s="1"/>
     </row>
-    <row r="977" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="977" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A977" s="1" t="s">
         <v>1733</v>
       </c>
@@ -55453,7 +55459,7 @@
       </c>
       <c r="T977" s="1"/>
     </row>
-    <row r="978" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="978" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A978" s="1" t="s">
         <v>1733</v>
       </c>
@@ -55505,7 +55511,7 @@
       </c>
       <c r="T978" s="1"/>
     </row>
-    <row r="979" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="979" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A979" s="1" t="s">
         <v>1733</v>
       </c>
@@ -55555,7 +55561,7 @@
       </c>
       <c r="T979" s="1"/>
     </row>
-    <row r="980" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="980" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A980" s="1" t="s">
         <v>1733</v>
       </c>
@@ -55607,7 +55613,7 @@
       </c>
       <c r="T980" s="1"/>
     </row>
-    <row r="981" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="981" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A981" s="1" t="s">
         <v>1733</v>
       </c>
@@ -55659,7 +55665,7 @@
       </c>
       <c r="T981" s="1"/>
     </row>
-    <row r="982" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="982" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A982" s="1" t="s">
         <v>1733</v>
       </c>
@@ -55711,7 +55717,7 @@
       </c>
       <c r="T982" s="1"/>
     </row>
-    <row r="983" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="983" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A983" s="1" t="s">
         <v>1733</v>
       </c>
@@ -55763,7 +55769,7 @@
       </c>
       <c r="T983" s="1"/>
     </row>
-    <row r="984" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="984" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A984" s="1" t="s">
         <v>1733</v>
       </c>
@@ -55815,7 +55821,7 @@
       </c>
       <c r="T984" s="1"/>
     </row>
-    <row r="985" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="985" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A985" s="1" t="s">
         <v>1733</v>
       </c>
@@ -55867,7 +55873,7 @@
       </c>
       <c r="T985" s="1"/>
     </row>
-    <row r="986" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="986" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A986" s="1" t="s">
         <v>1733</v>
       </c>
@@ -55919,7 +55925,7 @@
       </c>
       <c r="T986" s="1"/>
     </row>
-    <row r="987" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="987" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A987" s="1" t="s">
         <v>1733</v>
       </c>
@@ -55971,7 +55977,7 @@
       </c>
       <c r="T987" s="1"/>
     </row>
-    <row r="988" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="988" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A988" s="1" t="s">
         <v>1733</v>
       </c>
@@ -56021,7 +56027,7 @@
       </c>
       <c r="T988" s="1"/>
     </row>
-    <row r="989" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="989" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A989" s="1" t="s">
         <v>1733</v>
       </c>
@@ -56073,7 +56079,7 @@
       </c>
       <c r="T989" s="1"/>
     </row>
-    <row r="990" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="990" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A990" s="1" t="s">
         <v>1733</v>
       </c>
@@ -56123,7 +56129,7 @@
       </c>
       <c r="T990" s="1"/>
     </row>
-    <row r="991" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="991" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A991" s="1" t="s">
         <v>1733</v>
       </c>
@@ -56173,7 +56179,7 @@
       </c>
       <c r="T991" s="1"/>
     </row>
-    <row r="992" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="992" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A992" s="1" t="s">
         <v>1733</v>
       </c>
@@ -56223,7 +56229,7 @@
       </c>
       <c r="T992" s="1"/>
     </row>
-    <row r="993" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="993" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A993" s="1" t="s">
         <v>1733</v>
       </c>
@@ -56273,7 +56279,7 @@
       </c>
       <c r="T993" s="1"/>
     </row>
-    <row r="994" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="994" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A994" s="1" t="s">
         <v>1733</v>
       </c>
@@ -56323,7 +56329,7 @@
       </c>
       <c r="T994" s="1"/>
     </row>
-    <row r="995" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="995" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A995" s="1" t="s">
         <v>1733</v>
       </c>
@@ -56373,7 +56379,7 @@
       </c>
       <c r="T995" s="1"/>
     </row>
-    <row r="996" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="996" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A996" s="1" t="s">
         <v>1760</v>
       </c>
@@ -56423,7 +56429,7 @@
       </c>
       <c r="T996" s="1"/>
     </row>
-    <row r="997" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="997" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A997" s="1" t="s">
         <v>1760</v>
       </c>
@@ -56473,7 +56479,7 @@
       </c>
       <c r="T997" s="1"/>
     </row>
-    <row r="998" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="998" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A998" s="1" t="s">
         <v>1760</v>
       </c>
@@ -56523,7 +56529,7 @@
       </c>
       <c r="T998" s="1"/>
     </row>
-    <row r="999" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="999" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A999" s="1" t="s">
         <v>1760</v>
       </c>
@@ -56573,7 +56579,7 @@
       </c>
       <c r="T999" s="1"/>
     </row>
-    <row r="1000" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="1000" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A1000" s="1" t="s">
         <v>1760</v>
       </c>
@@ -56623,7 +56629,7 @@
       </c>
       <c r="T1000" s="1"/>
     </row>
-    <row r="1001" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="1001" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A1001" s="1" t="s">
         <v>1760</v>
       </c>
@@ -56673,7 +56679,7 @@
       </c>
       <c r="T1001" s="1"/>
     </row>
-    <row r="1002" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="1002" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A1002" s="1" t="s">
         <v>1760</v>
       </c>
@@ -56723,7 +56729,7 @@
       </c>
       <c r="T1002" s="1"/>
     </row>
-    <row r="1003" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="1003" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A1003" s="1" t="s">
         <v>1760</v>
       </c>
@@ -56773,7 +56779,7 @@
       </c>
       <c r="T1003" s="1"/>
     </row>
-    <row r="1004" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="1004" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A1004" s="1" t="s">
         <v>1760</v>
       </c>
@@ -56823,7 +56829,7 @@
       </c>
       <c r="T1004" s="1"/>
     </row>
-    <row r="1005" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="1005" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A1005" s="1" t="s">
         <v>1760</v>
       </c>
@@ -56873,7 +56879,7 @@
       </c>
       <c r="T1005" s="1"/>
     </row>
-    <row r="1006" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="1006" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A1006" s="1" t="s">
         <v>1760</v>
       </c>
@@ -56923,7 +56929,7 @@
       </c>
       <c r="T1006" s="1"/>
     </row>
-    <row r="1007" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="1007" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A1007" s="1" t="s">
         <v>1760</v>
       </c>
@@ -56973,7 +56979,7 @@
       </c>
       <c r="T1007" s="1"/>
     </row>
-    <row r="1008" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="1008" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A1008" s="1" t="s">
         <v>1760</v>
       </c>
@@ -57023,7 +57029,7 @@
       </c>
       <c r="T1008" s="1"/>
     </row>
-    <row r="1009" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="1009" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A1009" s="1" t="s">
         <v>1760</v>
       </c>
@@ -57073,7 +57079,7 @@
       </c>
       <c r="T1009" s="1"/>
     </row>
-    <row r="1010" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="1010" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A1010" s="1" t="s">
         <v>1760</v>
       </c>
@@ -57123,7 +57129,7 @@
       </c>
       <c r="T1010" s="1"/>
     </row>
-    <row r="1011" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="1011" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A1011" s="1" t="s">
         <v>1760</v>
       </c>
@@ -57173,7 +57179,7 @@
       </c>
       <c r="T1011" s="1"/>
     </row>
-    <row r="1012" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="1012" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A1012" s="1" t="s">
         <v>1760</v>
       </c>
@@ -57223,7 +57229,7 @@
       </c>
       <c r="T1012" s="1"/>
     </row>
-    <row r="1013" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="1013" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A1013" s="1" t="s">
         <v>1760</v>
       </c>
@@ -57273,7 +57279,7 @@
       </c>
       <c r="T1013" s="1"/>
     </row>
-    <row r="1014" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="1014" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A1014" s="1" t="s">
         <v>1760</v>
       </c>
@@ -57323,7 +57329,7 @@
       </c>
       <c r="T1014" s="1"/>
     </row>
-    <row r="1015" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="1015" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A1015" s="1" t="s">
         <v>1760</v>
       </c>
@@ -57373,7 +57379,7 @@
       </c>
       <c r="T1015" s="1"/>
     </row>
-    <row r="1016" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="1016" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A1016" s="1" t="s">
         <v>1760</v>
       </c>
@@ -57423,7 +57429,7 @@
       </c>
       <c r="T1016" s="1"/>
     </row>
-    <row r="1017" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="1017" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A1017" s="1" t="s">
         <v>1760</v>
       </c>
@@ -57473,7 +57479,7 @@
       </c>
       <c r="T1017" s="1"/>
     </row>
-    <row r="1018" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="1018" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A1018" s="1" t="s">
         <v>1760</v>
       </c>
@@ -57523,7 +57529,7 @@
       </c>
       <c r="T1018" s="1"/>
     </row>
-    <row r="1019" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="1019" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A1019" s="1" t="s">
         <v>1760</v>
       </c>
@@ -57573,7 +57579,7 @@
       </c>
       <c r="T1019" s="1"/>
     </row>
-    <row r="1020" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="1020" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A1020" s="1" t="s">
         <v>1760</v>
       </c>
@@ -57623,7 +57629,7 @@
       </c>
       <c r="T1020" s="1"/>
     </row>
-    <row r="1021" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="1021" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A1021" s="1" t="s">
         <v>1760</v>
       </c>
@@ -57673,7 +57679,7 @@
       </c>
       <c r="T1021" s="1"/>
     </row>
-    <row r="1022" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="1022" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A1022" s="1" t="s">
         <v>1760</v>
       </c>
@@ -57723,7 +57729,7 @@
       </c>
       <c r="T1022" s="1"/>
     </row>
-    <row r="1023" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="1023" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A1023" s="1" t="s">
         <v>1760</v>
       </c>
@@ -57773,7 +57779,7 @@
       </c>
       <c r="T1023" s="1"/>
     </row>
-    <row r="1024" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="1024" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A1024" s="1" t="s">
         <v>1760</v>
       </c>
@@ -57823,7 +57829,7 @@
       </c>
       <c r="T1024" s="1"/>
     </row>
-    <row r="1025" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="1025" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A1025" s="1" t="s">
         <v>1760</v>
       </c>
@@ -57873,7 +57879,7 @@
       </c>
       <c r="T1025" s="1"/>
     </row>
-    <row r="1026" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="1026" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A1026" s="1" t="s">
         <v>1760</v>
       </c>
@@ -57923,7 +57929,7 @@
       </c>
       <c r="T1026" s="1"/>
     </row>
-    <row r="1027" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="1027" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A1027" s="1" t="s">
         <v>1760</v>
       </c>
@@ -57973,7 +57979,7 @@
       </c>
       <c r="T1027" s="1"/>
     </row>
-    <row r="1028" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="1028" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A1028" s="1" t="s">
         <v>1760</v>
       </c>
@@ -58007,7 +58013,7 @@
       </c>
       <c r="T1028" s="1"/>
     </row>
-    <row r="1029" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="1029" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A1029" s="1" t="s">
         <v>1760</v>
       </c>
@@ -58041,7 +58047,7 @@
       </c>
       <c r="T1029" s="1"/>
     </row>
-    <row r="1030" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="1030" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A1030" s="1" t="s">
         <v>1760</v>
       </c>
@@ -58075,7 +58081,7 @@
       </c>
       <c r="T1030" s="1"/>
     </row>
-    <row r="1031" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="1031" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A1031" s="1" t="s">
         <v>1760</v>
       </c>
@@ -58109,7 +58115,7 @@
       </c>
       <c r="T1031" s="1"/>
     </row>
-    <row r="1032" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="1032" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A1032" s="1" t="s">
         <v>1760</v>
       </c>
@@ -58143,7 +58149,7 @@
       </c>
       <c r="T1032" s="1"/>
     </row>
-    <row r="1033" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="1033" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A1033" s="1" t="s">
         <v>1760</v>
       </c>
@@ -58177,7 +58183,7 @@
       </c>
       <c r="T1033" s="1"/>
     </row>
-    <row r="1034" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="1034" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A1034" s="1" t="s">
         <v>1760</v>
       </c>
@@ -58211,7 +58217,7 @@
       </c>
       <c r="T1034" s="1"/>
     </row>
-    <row r="1035" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="1035" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A1035" s="1" t="s">
         <v>1760</v>
       </c>
@@ -58245,7 +58251,7 @@
       </c>
       <c r="T1035" s="1"/>
     </row>
-    <row r="1036" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="1036" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A1036" s="1" t="s">
         <v>1760</v>
       </c>
@@ -58279,7 +58285,7 @@
       </c>
       <c r="T1036" s="1"/>
     </row>
-    <row r="1037" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="1037" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A1037" s="1" t="s">
         <v>1760</v>
       </c>
@@ -58313,7 +58319,7 @@
       </c>
       <c r="T1037" s="1"/>
     </row>
-    <row r="1038" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="1038" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A1038" s="1" t="s">
         <v>1760</v>
       </c>
@@ -58347,7 +58353,7 @@
       </c>
       <c r="T1038" s="1"/>
     </row>
-    <row r="1039" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="1039" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A1039" s="1" t="s">
         <v>1760</v>
       </c>
@@ -58381,7 +58387,7 @@
       </c>
       <c r="T1039" s="1"/>
     </row>
-    <row r="1040" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="1040" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A1040" s="1" t="s">
         <v>1760</v>
       </c>
@@ -58415,7 +58421,7 @@
       </c>
       <c r="T1040" s="1"/>
     </row>
-    <row r="1041" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="1041" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A1041" s="1" t="s">
         <v>1760</v>
       </c>
@@ -58449,7 +58455,7 @@
       </c>
       <c r="T1041" s="1"/>
     </row>
-    <row r="1042" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="1042" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A1042" s="1" t="s">
         <v>1760</v>
       </c>
@@ -58483,7 +58489,7 @@
       </c>
       <c r="T1042" s="1"/>
     </row>
-    <row r="1043" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="1043" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A1043" s="1" t="s">
         <v>1790</v>
       </c>
@@ -58533,7 +58539,7 @@
       </c>
       <c r="T1043" s="1"/>
     </row>
-    <row r="1044" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="1044" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A1044" s="1" t="s">
         <v>1790</v>
       </c>
@@ -58583,7 +58589,7 @@
       </c>
       <c r="T1044" s="1"/>
     </row>
-    <row r="1045" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="1045" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A1045" s="1" t="s">
         <v>1790</v>
       </c>
@@ -58633,7 +58639,7 @@
       </c>
       <c r="T1045" s="1"/>
     </row>
-    <row r="1046" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="1046" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A1046" s="1" t="s">
         <v>1790</v>
       </c>
@@ -58685,7 +58691,7 @@
       </c>
       <c r="T1046" s="1"/>
     </row>
-    <row r="1047" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="1047" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A1047" s="1" t="s">
         <v>1790</v>
       </c>
@@ -58737,7 +58743,7 @@
       </c>
       <c r="T1047" s="1"/>
     </row>
-    <row r="1048" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="1048" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A1048" s="1" t="s">
         <v>1790</v>
       </c>
@@ -58789,7 +58795,7 @@
       </c>
       <c r="T1048" s="1"/>
     </row>
-    <row r="1049" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="1049" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A1049" s="1" t="s">
         <v>1790</v>
       </c>
@@ -58839,7 +58845,7 @@
       </c>
       <c r="T1049" s="1"/>
     </row>
-    <row r="1050" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="1050" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A1050" s="1" t="s">
         <v>1790</v>
       </c>
@@ -58889,7 +58895,7 @@
       </c>
       <c r="T1050" s="1"/>
     </row>
-    <row r="1051" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="1051" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A1051" s="1" t="s">
         <v>1790</v>
       </c>
@@ -58941,7 +58947,7 @@
       </c>
       <c r="T1051" s="1"/>
     </row>
-    <row r="1052" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="1052" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A1052" s="1" t="s">
         <v>1790</v>
       </c>
@@ -58993,7 +58999,7 @@
       </c>
       <c r="T1052" s="1"/>
     </row>
-    <row r="1053" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="1053" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A1053" s="1" t="s">
         <v>1790</v>
       </c>
@@ -59043,7 +59049,7 @@
       </c>
       <c r="T1053" s="1"/>
     </row>
-    <row r="1054" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="1054" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A1054" s="1" t="s">
         <v>1790</v>
       </c>
@@ -59093,7 +59099,7 @@
       </c>
       <c r="T1054" s="1"/>
     </row>
-    <row r="1055" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="1055" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A1055" s="1" t="s">
         <v>1790</v>
       </c>
@@ -59143,7 +59149,7 @@
       </c>
       <c r="T1055" s="1"/>
     </row>
-    <row r="1056" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="1056" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A1056" s="1" t="s">
         <v>1795</v>
       </c>
@@ -59197,7 +59203,7 @@
       </c>
       <c r="T1056" s="1"/>
     </row>
-    <row r="1057" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="1057" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A1057" s="1" t="s">
         <v>1795</v>
       </c>
@@ -59251,7 +59257,7 @@
       </c>
       <c r="T1057" s="1"/>
     </row>
-    <row r="1058" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="1058" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A1058" s="1" t="s">
         <v>1795</v>
       </c>
@@ -59305,7 +59311,7 @@
       </c>
       <c r="T1058" s="1"/>
     </row>
-    <row r="1059" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="1059" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A1059" s="1" t="s">
         <v>1795</v>
       </c>
@@ -59355,7 +59361,7 @@
       </c>
       <c r="T1059" s="1"/>
     </row>
-    <row r="1060" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="1060" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A1060" s="1" t="s">
         <v>1795</v>
       </c>
@@ -59409,7 +59415,7 @@
       </c>
       <c r="T1060" s="1"/>
     </row>
-    <row r="1061" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="1061" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A1061" s="1" t="s">
         <v>1795</v>
       </c>
@@ -59459,7 +59465,7 @@
       </c>
       <c r="T1061" s="1"/>
     </row>
-    <row r="1062" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="1062" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A1062" s="1" t="s">
         <v>1795</v>
       </c>
@@ -59509,7 +59515,7 @@
       </c>
       <c r="T1062" s="1"/>
     </row>
-    <row r="1063" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="1063" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A1063" s="1" t="s">
         <v>1795</v>
       </c>
@@ -59559,7 +59565,7 @@
       </c>
       <c r="T1063" s="1"/>
     </row>
-    <row r="1064" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="1064" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A1064" s="1" t="s">
         <v>1795</v>
       </c>
@@ -59609,7 +59615,7 @@
       </c>
       <c r="T1064" s="1"/>
     </row>
-    <row r="1065" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="1065" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A1065" s="1" t="s">
         <v>1795</v>
       </c>
@@ -59659,7 +59665,7 @@
       </c>
       <c r="T1065" s="1"/>
     </row>
-    <row r="1066" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="1066" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A1066" s="1" t="s">
         <v>1795</v>
       </c>
@@ -59713,7 +59719,7 @@
       </c>
       <c r="T1066" s="1"/>
     </row>
-    <row r="1067" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="1067" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A1067" s="1" t="s">
         <v>1795</v>
       </c>
@@ -59763,7 +59769,7 @@
       </c>
       <c r="T1067" s="1"/>
     </row>
-    <row r="1068" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="1068" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A1068" s="1" t="s">
         <v>1795</v>
       </c>
@@ -59813,7 +59819,7 @@
       </c>
       <c r="T1068" s="1"/>
     </row>
-    <row r="1069" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="1069" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A1069" s="1" t="s">
         <v>1795</v>
       </c>
@@ -59863,7 +59869,7 @@
       </c>
       <c r="T1069" s="1"/>
     </row>
-    <row r="1070" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="1070" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A1070" s="1" t="s">
         <v>1795</v>
       </c>
@@ -59897,7 +59903,7 @@
       </c>
       <c r="T1070" s="1"/>
     </row>
-    <row r="1071" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="1071" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A1071" s="1" t="s">
         <v>1795</v>
       </c>
@@ -59947,7 +59953,7 @@
       </c>
       <c r="T1071" s="1"/>
     </row>
-    <row r="1072" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="1072" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A1072" s="1" t="s">
         <v>1795</v>
       </c>
